--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9451</v>
+        <v>2.9257</v>
       </c>
       <c r="F2" t="n">
-        <v>2178.461019</v>
+        <v>2164.111033</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>308.2288230000004</v>
+        <v>293.8788370000002</v>
       </c>
       <c r="J2" t="n">
-        <v>16.48</v>
+        <v>15.71</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9117</v>
+        <v>2.9008</v>
       </c>
       <c r="F3" t="n">
-        <v>944.322544</v>
+        <v>940.7874559999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-55.62088000000006</v>
+        <v>-59.15596800000014</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.56</v>
+        <v>-5.92</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2356</v>
+        <v>1.2286</v>
       </c>
       <c r="F4" t="n">
-        <v>7042.92</v>
+        <v>7003.02</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1622.22</v>
+        <v>1582.32</v>
       </c>
       <c r="J4" t="n">
-        <v>29.93</v>
+        <v>29.19</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9656</v>
+        <v>1.9785</v>
       </c>
       <c r="F5" t="n">
-        <v>2331.064008</v>
+        <v>2346.362505</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-68.90253299999949</v>
+        <v>-53.60403599999972</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.87</v>
+        <v>-2.23</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3464</v>
+        <v>1.3404</v>
       </c>
       <c r="F6" t="n">
-        <v>2285.231256</v>
+        <v>2275.047516</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-214.7071849999998</v>
+        <v>-224.8909249999997</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.59</v>
+        <v>-9</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3464</v>
+        <v>1.3404</v>
       </c>
       <c r="F7" t="n">
-        <v>4839.09624</v>
+        <v>4817.53164</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-480.8905800000002</v>
+        <v>-502.4551799999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-9.039999999999999</v>
+        <v>-9.44</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1782</v>
+        <v>2.1647</v>
       </c>
       <c r="F8" t="n">
-        <v>28098.78</v>
+        <v>27924.63</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8800.379999999997</v>
+        <v>8626.229999999996</v>
       </c>
       <c r="J8" t="n">
-        <v>45.6</v>
+        <v>44.7</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1179</v>
+        <v>3.1424</v>
       </c>
       <c r="F9" t="n">
-        <v>944.131299</v>
+        <v>951.5501439999999</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>195.191326</v>
+        <v>202.6101709999999</v>
       </c>
       <c r="J9" t="n">
-        <v>26.06</v>
+        <v>27.05</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2345</v>
+        <v>2.2511</v>
       </c>
       <c r="F10" t="n">
-        <v>2324.840835</v>
+        <v>2342.111973</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>324.8222460000004</v>
+        <v>342.093384</v>
       </c>
       <c r="J10" t="n">
-        <v>16.24</v>
+        <v>17.1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6882</v>
+        <v>1.7012</v>
       </c>
       <c r="F11" t="n">
-        <v>6984.471685999999</v>
+        <v>7038.255676</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1005.346889999999</v>
+        <v>1059.13088</v>
       </c>
       <c r="J11" t="n">
-        <v>16.81</v>
+        <v>17.71</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6882</v>
+        <v>1.7012</v>
       </c>
       <c r="F12" t="n">
-        <v>10152.952974</v>
+        <v>10231.135884</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1053.063657000001</v>
+        <v>1131.246567</v>
       </c>
       <c r="J12" t="n">
-        <v>11.57</v>
+        <v>12.43</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.434</v>
+        <v>2.4542</v>
       </c>
       <c r="F15" t="n">
-        <v>22636.2</v>
+        <v>22824.06</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3189.900000000001</v>
+        <v>3377.760000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>16.4</v>
+        <v>17.37</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.1</v>
+        <v>28.42</v>
       </c>
       <c r="F16" t="n">
-        <v>14050</v>
+        <v>14210</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>235</v>
+        <v>395</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7</v>
+        <v>2.86</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.08</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>18160</v>
+        <v>18100</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="J17" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0443</v>
+        <v>1.0501</v>
       </c>
       <c r="F18" t="n">
-        <v>4102.208817</v>
+        <v>4124.992319</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-204.2658799999999</v>
+        <v>-181.4823779999997</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.74</v>
+        <v>-4.21</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5839</v>
+        <v>1.5806</v>
       </c>
       <c r="F19" t="n">
-        <v>13779.93</v>
+        <v>13751.22</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>321.0300000000007</v>
+        <v>292.3199999999997</v>
       </c>
       <c r="J19" t="n">
-        <v>2.39</v>
+        <v>2.17</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1722</v>
+        <v>1.1728</v>
       </c>
       <c r="F20" t="n">
-        <v>9290.693092</v>
+        <v>9295.448608000001</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-709.3644700000004</v>
+        <v>-704.6089539999994</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.09</v>
+        <v>-7.05</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2033</v>
+        <v>1.2077</v>
       </c>
       <c r="F21" t="n">
-        <v>13597.29</v>
+        <v>13647.01</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>963.8900000000012</v>
+        <v>1013.610000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>7.63</v>
+        <v>8.02</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7303</v>
+        <v>1.7445</v>
       </c>
       <c r="F22" t="n">
-        <v>923.789867</v>
+        <v>931.3711049999999</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>194.656294</v>
+        <v>202.237532</v>
       </c>
       <c r="J22" t="n">
-        <v>26.7</v>
+        <v>27.74</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7303</v>
+        <v>1.7445</v>
       </c>
       <c r="F23" t="n">
-        <v>22358.486722</v>
+        <v>22541.97543</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3158.073255999996</v>
+        <v>3341.561963999997</v>
       </c>
       <c r="J23" t="n">
-        <v>16.45</v>
+        <v>17.4</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.554</v>
+        <v>1.5667</v>
       </c>
       <c r="F24" t="n">
-        <v>1016.81328</v>
+        <v>1025.123144</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>216.8416480000001</v>
+        <v>225.1515120000001</v>
       </c>
       <c r="J24" t="n">
-        <v>27.11</v>
+        <v>28.14</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.2164</v>
+        <v>6.2705</v>
       </c>
       <c r="F26" t="n">
-        <v>2581.919576</v>
+        <v>2604.38947</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>481.9190019999996</v>
+        <v>504.3888959999999</v>
       </c>
       <c r="J26" t="n">
-        <v>22.95</v>
+        <v>24.02</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0093</v>
+        <v>2.0259</v>
       </c>
       <c r="F28" t="n">
-        <v>7753.48684</v>
+        <v>7817.542920000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1453.609960000001</v>
+        <v>1517.666040000001</v>
       </c>
       <c r="J28" t="n">
-        <v>23.07</v>
+        <v>24.09</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0093</v>
+        <v>2.0259</v>
       </c>
       <c r="F29" t="n">
-        <v>17499.576397</v>
+        <v>17644.150611</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2499.56623</v>
+        <v>2644.140444000001</v>
       </c>
       <c r="J29" t="n">
-        <v>16.66</v>
+        <v>17.63</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0917</v>
+        <v>2.1091</v>
       </c>
       <c r="F30" t="n">
-        <v>10998.346853</v>
+        <v>11089.837619</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2117.958651999999</v>
+        <v>2209.449418000002</v>
       </c>
       <c r="J30" t="n">
-        <v>23.85</v>
+        <v>24.88</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.0917</v>
+        <v>2.1091</v>
       </c>
       <c r="F31" t="n">
-        <v>1410.370559</v>
+        <v>1422.102857</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>210.3722399999999</v>
+        <v>222.104538</v>
       </c>
       <c r="J31" t="n">
-        <v>17.53</v>
+        <v>18.51</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4299</v>
+        <v>2.4532</v>
       </c>
       <c r="F33" t="n">
-        <v>14822.39</v>
+        <v>14964.52</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2549.189999999999</v>
+        <v>2691.319999999998</v>
       </c>
       <c r="J33" t="n">
-        <v>20.77</v>
+        <v>21.93</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9659</v>
+        <v>1.9831</v>
       </c>
       <c r="F34" t="n">
-        <v>37548.69</v>
+        <v>37877.21</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6377.490000000002</v>
+        <v>6706.009999999998</v>
       </c>
       <c r="J34" t="n">
-        <v>20.46</v>
+        <v>21.51</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.7305</v>
+        <v>6.7984</v>
       </c>
       <c r="F35" t="n">
-        <v>40964.38059</v>
+        <v>41377.645792</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>7764.394966</v>
+        <v>8177.660168000002</v>
       </c>
       <c r="J35" t="n">
-        <v>23.39</v>
+        <v>24.63</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.7305</v>
+        <v>6.7984</v>
       </c>
       <c r="F36" t="n">
-        <v>13911.00123</v>
+        <v>14051.341024</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2611.064238000001</v>
+        <v>2751.404032</v>
       </c>
       <c r="J36" t="n">
-        <v>23.11</v>
+        <v>24.35</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.7305</v>
+        <v>6.7984</v>
       </c>
       <c r="F37" t="n">
-        <v>100957.5</v>
+        <v>101976</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>17662.5</v>
+        <v>18681</v>
       </c>
       <c r="J37" t="n">
-        <v>21.2</v>
+        <v>22.43</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.8701</v>
+        <v>2.893</v>
       </c>
       <c r="F38" t="n">
-        <v>20875.414041</v>
+        <v>21041.97513</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>5075.385498</v>
+        <v>5241.946586999999</v>
       </c>
       <c r="J38" t="n">
-        <v>32.12</v>
+        <v>33.18</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.8701</v>
+        <v>2.893</v>
       </c>
       <c r="F39" t="n">
-        <v>29929.144491</v>
+        <v>30167.94363</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>6929.346194999998</v>
+        <v>7168.145333999997</v>
       </c>
       <c r="J39" t="n">
-        <v>30.13</v>
+        <v>31.17</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.256</v>
+        <v>2.2751</v>
       </c>
       <c r="F40" t="n">
-        <v>15115.2</v>
+        <v>15243.17</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4663.199999999999</v>
+        <v>4791.17</v>
       </c>
       <c r="J40" t="n">
-        <v>44.62</v>
+        <v>45.84</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.130000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>8130.000000000001</v>
+        <v>8119.999999999999</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1021.000000000001</v>
+        <v>1010.999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>14.36</v>
+        <v>14.22</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>6.98</v>
+        <v>6.97</v>
       </c>
       <c r="F42" t="n">
-        <v>7678.000000000001</v>
+        <v>7667</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1093.400000000001</v>
+        <v>1082.4</v>
       </c>
       <c r="J42" t="n">
-        <v>16.61</v>
+        <v>16.44</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>41.75</v>
+        <v>41.34</v>
       </c>
       <c r="F43" t="n">
-        <v>62625</v>
+        <v>62010.00000000001</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-1830</v>
+        <v>-2444.999999999993</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.84</v>
+        <v>-3.79</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9257</v>
+        <v>2.9101</v>
       </c>
       <c r="F2" t="n">
-        <v>2164.111033</v>
+        <v>2152.571869</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>293.8788370000002</v>
+        <v>282.3396729999999</v>
       </c>
       <c r="J2" t="n">
-        <v>15.71</v>
+        <v>15.1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9008</v>
+        <v>2.8722</v>
       </c>
       <c r="F3" t="n">
-        <v>940.7874559999999</v>
+        <v>931.511904</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-59.15596800000014</v>
+        <v>-68.43152000000009</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.92</v>
+        <v>-6.84</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2286</v>
+        <v>1.222</v>
       </c>
       <c r="F4" t="n">
-        <v>7003.02</v>
+        <v>6965.4</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1582.32</v>
+        <v>1544.7</v>
       </c>
       <c r="J4" t="n">
-        <v>29.19</v>
+        <v>28.5</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9785</v>
+        <v>1.9642</v>
       </c>
       <c r="F5" t="n">
-        <v>2346.362505</v>
+        <v>2329.403706</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-53.60403599999972</v>
+        <v>-70.56283499999972</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.23</v>
+        <v>-2.94</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3404</v>
+        <v>1.3394</v>
       </c>
       <c r="F6" t="n">
-        <v>2275.047516</v>
+        <v>2273.350226</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-224.8909249999997</v>
+        <v>-226.5882149999998</v>
       </c>
       <c r="J6" t="n">
-        <v>-9</v>
+        <v>-9.06</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3404</v>
+        <v>1.3394</v>
       </c>
       <c r="F7" t="n">
-        <v>4817.53164</v>
+        <v>4813.93754</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-502.4551799999999</v>
+        <v>-506.0492800000002</v>
       </c>
       <c r="J7" t="n">
-        <v>-9.44</v>
+        <v>-9.51</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1647</v>
+        <v>2.1549</v>
       </c>
       <c r="F8" t="n">
-        <v>27924.63</v>
+        <v>27798.21</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8626.229999999996</v>
+        <v>8499.809999999998</v>
       </c>
       <c r="J8" t="n">
-        <v>44.7</v>
+        <v>44.04</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1424</v>
+        <v>3.1259</v>
       </c>
       <c r="F9" t="n">
-        <v>951.5501439999999</v>
+        <v>946.5537790000001</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>202.6101709999999</v>
+        <v>197.6138060000001</v>
       </c>
       <c r="J9" t="n">
-        <v>27.05</v>
+        <v>26.39</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2511</v>
+        <v>2.2401</v>
       </c>
       <c r="F10" t="n">
-        <v>2342.111973</v>
+        <v>2330.667243</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>342.093384</v>
+        <v>330.6486540000003</v>
       </c>
       <c r="J10" t="n">
-        <v>17.1</v>
+        <v>16.53</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7012</v>
+        <v>1.6925</v>
       </c>
       <c r="F11" t="n">
-        <v>7038.255676</v>
+        <v>7002.261774999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1059.13088</v>
+        <v>1023.136978999999</v>
       </c>
       <c r="J11" t="n">
-        <v>17.71</v>
+        <v>17.11</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7012</v>
+        <v>1.6925</v>
       </c>
       <c r="F12" t="n">
-        <v>10231.135884</v>
+        <v>10178.813475</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1131.246567</v>
+        <v>1078.924158</v>
       </c>
       <c r="J12" t="n">
-        <v>12.43</v>
+        <v>11.86</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4542</v>
+        <v>2.4407</v>
       </c>
       <c r="F15" t="n">
-        <v>22824.06</v>
+        <v>22698.51</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3377.760000000002</v>
+        <v>3252.210000000003</v>
       </c>
       <c r="J15" t="n">
-        <v>17.37</v>
+        <v>16.72</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.42</v>
+        <v>28.63</v>
       </c>
       <c r="F16" t="n">
-        <v>14210</v>
+        <v>14315</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="J16" t="n">
-        <v>2.86</v>
+        <v>3.62</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.050000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="F17" t="n">
-        <v>18100</v>
+        <v>18120</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="J17" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0501</v>
+        <v>1.0444</v>
       </c>
       <c r="F18" t="n">
-        <v>4124.992319</v>
+        <v>4102.601636</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-181.4823779999997</v>
+        <v>-203.8730609999993</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.21</v>
+        <v>-4.73</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5806</v>
+        <v>1.5712</v>
       </c>
       <c r="F19" t="n">
-        <v>13751.22</v>
+        <v>13669.44</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>292.3199999999997</v>
+        <v>210.5399999999991</v>
       </c>
       <c r="J19" t="n">
-        <v>2.17</v>
+        <v>1.56</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1728</v>
+        <v>1.1618</v>
       </c>
       <c r="F20" t="n">
-        <v>9295.448608000001</v>
+        <v>9208.264147999998</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-704.6089539999994</v>
+        <v>-791.7934140000016</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.05</v>
+        <v>-7.92</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2077</v>
+        <v>1.1979</v>
       </c>
       <c r="F21" t="n">
-        <v>13647.01</v>
+        <v>13536.27</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1013.610000000001</v>
+        <v>902.8700000000008</v>
       </c>
       <c r="J21" t="n">
-        <v>8.02</v>
+        <v>7.15</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7445</v>
+        <v>1.7299</v>
       </c>
       <c r="F22" t="n">
-        <v>931.3711049999999</v>
+        <v>923.5763109999999</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>202.237532</v>
+        <v>194.442738</v>
       </c>
       <c r="J22" t="n">
-        <v>27.74</v>
+        <v>26.67</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7445</v>
+        <v>1.7299</v>
       </c>
       <c r="F23" t="n">
-        <v>22541.97543</v>
+        <v>22353.318026</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3341.561963999997</v>
+        <v>3152.904559999999</v>
       </c>
       <c r="J23" t="n">
-        <v>17.4</v>
+        <v>16.42</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5667</v>
+        <v>1.5537</v>
       </c>
       <c r="F24" t="n">
-        <v>1025.123144</v>
+        <v>1016.616984</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>225.1515120000001</v>
+        <v>216.6453520000001</v>
       </c>
       <c r="J24" t="n">
-        <v>28.14</v>
+        <v>27.08</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.2705</v>
+        <v>6.2136</v>
       </c>
       <c r="F26" t="n">
-        <v>2604.38947</v>
+        <v>2580.756624</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>504.3888959999999</v>
+        <v>480.7560499999995</v>
       </c>
       <c r="J26" t="n">
-        <v>24.02</v>
+        <v>22.89</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0259</v>
+        <v>2.0089</v>
       </c>
       <c r="F28" t="n">
-        <v>7817.542920000001</v>
+        <v>7751.943320000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1517.666040000001</v>
+        <v>1452.066440000001</v>
       </c>
       <c r="J28" t="n">
-        <v>24.09</v>
+        <v>23.05</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0259</v>
+        <v>2.0089</v>
       </c>
       <c r="F29" t="n">
-        <v>17644.150611</v>
+        <v>17496.092681</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2644.140444000001</v>
+        <v>2496.082514000002</v>
       </c>
       <c r="J29" t="n">
-        <v>17.63</v>
+        <v>16.64</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1091</v>
+        <v>2.0912</v>
       </c>
       <c r="F30" t="n">
-        <v>11089.837619</v>
+        <v>10995.717808</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2209.449418000002</v>
+        <v>2115.329607000001</v>
       </c>
       <c r="J30" t="n">
-        <v>24.88</v>
+        <v>23.82</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1091</v>
+        <v>2.0912</v>
       </c>
       <c r="F31" t="n">
-        <v>1422.102857</v>
+        <v>1410.033424</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>222.104538</v>
+        <v>210.0351049999999</v>
       </c>
       <c r="J31" t="n">
-        <v>18.51</v>
+        <v>17.5</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4532</v>
+        <v>2.4322</v>
       </c>
       <c r="F33" t="n">
-        <v>14964.52</v>
+        <v>14836.42</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2691.319999999998</v>
+        <v>2563.219999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>21.93</v>
+        <v>20.88</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9831</v>
+        <v>1.9655</v>
       </c>
       <c r="F34" t="n">
-        <v>37877.21</v>
+        <v>37541.05</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6706.009999999998</v>
+        <v>6369.850000000002</v>
       </c>
       <c r="J34" t="n">
-        <v>21.51</v>
+        <v>20.44</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.7984</v>
+        <v>6.6876</v>
       </c>
       <c r="F35" t="n">
-        <v>41377.645792</v>
+        <v>40703.274888</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>8177.660168000002</v>
+        <v>7503.289263999999</v>
       </c>
       <c r="J35" t="n">
-        <v>24.63</v>
+        <v>22.6</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.7984</v>
+        <v>6.6876</v>
       </c>
       <c r="F36" t="n">
-        <v>14051.341024</v>
+        <v>13822.332936</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2751.404032</v>
+        <v>2522.395944</v>
       </c>
       <c r="J36" t="n">
-        <v>24.35</v>
+        <v>22.32</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.7984</v>
+        <v>6.6876</v>
       </c>
       <c r="F37" t="n">
-        <v>101976</v>
+        <v>100314</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>18681</v>
+        <v>17019</v>
       </c>
       <c r="J37" t="n">
-        <v>22.43</v>
+        <v>20.43</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.893</v>
+        <v>2.8717</v>
       </c>
       <c r="F38" t="n">
-        <v>21041.97513</v>
+        <v>20887.051497</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>5241.946586999999</v>
+        <v>5087.022954</v>
       </c>
       <c r="J38" t="n">
-        <v>33.18</v>
+        <v>32.2</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.893</v>
+        <v>2.8717</v>
       </c>
       <c r="F39" t="n">
-        <v>30167.94363</v>
+        <v>29945.829147</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>7168.145333999997</v>
+        <v>6946.030851</v>
       </c>
       <c r="J39" t="n">
-        <v>31.17</v>
+        <v>30.2</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.2751</v>
+        <v>2.2571</v>
       </c>
       <c r="F40" t="n">
-        <v>15243.17</v>
+        <v>15122.57</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4791.17</v>
+        <v>4670.57</v>
       </c>
       <c r="J40" t="n">
-        <v>45.84</v>
+        <v>44.69</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.119999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>8119.999999999999</v>
+        <v>8210</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1010.999999999999</v>
+        <v>1101</v>
       </c>
       <c r="J41" t="n">
-        <v>14.22</v>
+        <v>15.49</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>6.97</v>
+        <v>7</v>
       </c>
       <c r="F42" t="n">
-        <v>7667</v>
+        <v>7700</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1082.4</v>
+        <v>1115.4</v>
       </c>
       <c r="J42" t="n">
-        <v>16.44</v>
+        <v>16.94</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>41.34</v>
+        <v>41.78</v>
       </c>
       <c r="F43" t="n">
-        <v>62010.00000000001</v>
+        <v>62670</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-2444.999999999993</v>
+        <v>-1785</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.79</v>
+        <v>-2.77</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9101</v>
+        <v>2.9354</v>
       </c>
       <c r="F2" t="n">
-        <v>2152.571869</v>
+        <v>2171.286026</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>282.3396729999999</v>
+        <v>301.0538300000003</v>
       </c>
       <c r="J2" t="n">
-        <v>15.1</v>
+        <v>16.1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8722</v>
+        <v>2.8438</v>
       </c>
       <c r="F3" t="n">
-        <v>931.511904</v>
+        <v>922.301216</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-68.43152000000009</v>
+        <v>-77.6422080000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-6.84</v>
+        <v>-7.76</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.222</v>
+        <v>1.234</v>
       </c>
       <c r="F4" t="n">
-        <v>6965.4</v>
+        <v>7033.8</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1544.7</v>
+        <v>1613.1</v>
       </c>
       <c r="J4" t="n">
-        <v>28.5</v>
+        <v>29.76</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9642</v>
+        <v>1.9537</v>
       </c>
       <c r="F5" t="n">
-        <v>2329.403706</v>
+        <v>2316.951441</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-70.56283499999972</v>
+        <v>-83.01509999999962</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.94</v>
+        <v>-3.46</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3394</v>
+        <v>1.3125</v>
       </c>
       <c r="F6" t="n">
-        <v>2273.350226</v>
+        <v>2227.693125</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-226.5882149999998</v>
+        <v>-272.245316</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.06</v>
+        <v>-10.89</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3394</v>
+        <v>1.3125</v>
       </c>
       <c r="F7" t="n">
-        <v>4813.93754</v>
+        <v>4717.256249999999</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-506.0492800000002</v>
+        <v>-602.7305700000006</v>
       </c>
       <c r="J7" t="n">
-        <v>-9.51</v>
+        <v>-11.33</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1549</v>
+        <v>2.1596</v>
       </c>
       <c r="F8" t="n">
-        <v>27798.21</v>
+        <v>27858.84</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8499.809999999998</v>
+        <v>8560.440000000002</v>
       </c>
       <c r="J8" t="n">
-        <v>44.04</v>
+        <v>44.36</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1259</v>
+        <v>3.1117</v>
       </c>
       <c r="F9" t="n">
-        <v>946.5537790000001</v>
+        <v>942.253877</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>197.6138060000001</v>
+        <v>193.313904</v>
       </c>
       <c r="J9" t="n">
-        <v>26.39</v>
+        <v>25.81</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2401</v>
+        <v>2.2298</v>
       </c>
       <c r="F10" t="n">
-        <v>2330.667243</v>
+        <v>2319.950814</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>330.6486540000003</v>
+        <v>319.9322250000002</v>
       </c>
       <c r="J10" t="n">
-        <v>16.53</v>
+        <v>16</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6925</v>
+        <v>1.6848</v>
       </c>
       <c r="F11" t="n">
-        <v>7002.261774999999</v>
+        <v>6970.405103999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1023.136978999999</v>
+        <v>991.2803079999994</v>
       </c>
       <c r="J11" t="n">
-        <v>17.11</v>
+        <v>16.58</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6925</v>
+        <v>1.6848</v>
       </c>
       <c r="F12" t="n">
-        <v>10178.813475</v>
+        <v>10132.505136</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1078.924158</v>
+        <v>1032.615819000001</v>
       </c>
       <c r="J12" t="n">
-        <v>11.86</v>
+        <v>11.35</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4407</v>
+        <v>2.4289</v>
       </c>
       <c r="F15" t="n">
-        <v>22698.51</v>
+        <v>22588.77</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3252.210000000003</v>
+        <v>3142.470000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>16.72</v>
+        <v>16.16</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.63</v>
+        <v>28.46</v>
       </c>
       <c r="F16" t="n">
-        <v>14315</v>
+        <v>14230</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>500</v>
+        <v>415</v>
       </c>
       <c r="J16" t="n">
-        <v>3.62</v>
+        <v>3</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.06</v>
+        <v>9.02</v>
       </c>
       <c r="F17" t="n">
-        <v>18120</v>
+        <v>18040</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>360</v>
+        <v>280</v>
       </c>
       <c r="J17" t="n">
-        <v>2.03</v>
+        <v>1.58</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0444</v>
+        <v>1.0381</v>
       </c>
       <c r="F18" t="n">
-        <v>4102.601636</v>
+        <v>4077.854039</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-203.8730609999993</v>
+        <v>-228.6206579999994</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.73</v>
+        <v>-5.31</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5712</v>
+        <v>1.5483</v>
       </c>
       <c r="F19" t="n">
-        <v>13669.44</v>
+        <v>13470.21</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>210.5399999999991</v>
+        <v>11.31000000000131</v>
       </c>
       <c r="J19" t="n">
-        <v>1.56</v>
+        <v>0.08</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1618</v>
+        <v>1.1642</v>
       </c>
       <c r="F20" t="n">
-        <v>9208.264147999998</v>
+        <v>9227.286211999999</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-791.7934140000016</v>
+        <v>-772.7713500000009</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.92</v>
+        <v>-7.73</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1979</v>
+        <v>1.189</v>
       </c>
       <c r="F21" t="n">
-        <v>13536.27</v>
+        <v>13435.7</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>902.8700000000008</v>
+        <v>802.3000000000011</v>
       </c>
       <c r="J21" t="n">
-        <v>7.15</v>
+        <v>6.35</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7299</v>
+        <v>1.7187</v>
       </c>
       <c r="F22" t="n">
-        <v>923.5763109999999</v>
+        <v>917.5967429999999</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>194.442738</v>
+        <v>188.46317</v>
       </c>
       <c r="J22" t="n">
-        <v>26.67</v>
+        <v>25.85</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7299</v>
+        <v>1.7187</v>
       </c>
       <c r="F23" t="n">
-        <v>22353.318026</v>
+        <v>22208.594538</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3152.904559999999</v>
+        <v>3008.181071999996</v>
       </c>
       <c r="J23" t="n">
-        <v>16.42</v>
+        <v>15.67</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5537</v>
+        <v>1.5438</v>
       </c>
       <c r="F24" t="n">
-        <v>1016.616984</v>
+        <v>1010.139216</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>216.6453520000001</v>
+        <v>210.1675840000001</v>
       </c>
       <c r="J24" t="n">
-        <v>27.08</v>
+        <v>26.27</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.2136</v>
+        <v>6.1706</v>
       </c>
       <c r="F26" t="n">
-        <v>2580.756624</v>
+        <v>2562.897004</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>480.7560499999995</v>
+        <v>462.8964299999998</v>
       </c>
       <c r="J26" t="n">
-        <v>22.89</v>
+        <v>22.04</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0089</v>
+        <v>1.9959</v>
       </c>
       <c r="F28" t="n">
-        <v>7751.943320000001</v>
+        <v>7701.778920000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1452.066440000001</v>
+        <v>1401.902040000001</v>
       </c>
       <c r="J28" t="n">
-        <v>23.05</v>
+        <v>22.25</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0089</v>
+        <v>1.9959</v>
       </c>
       <c r="F29" t="n">
-        <v>17496.092681</v>
+        <v>17382.871911</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2496.082514000002</v>
+        <v>2382.861744000002</v>
       </c>
       <c r="J29" t="n">
-        <v>16.64</v>
+        <v>15.89</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0912</v>
+        <v>2.0776</v>
       </c>
       <c r="F30" t="n">
-        <v>10995.717808</v>
+        <v>10924.207784</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2115.329607000001</v>
+        <v>2043.819583</v>
       </c>
       <c r="J30" t="n">
-        <v>23.82</v>
+        <v>23.01</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.0912</v>
+        <v>2.0776</v>
       </c>
       <c r="F31" t="n">
-        <v>1410.033424</v>
+        <v>1400.863352</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>210.0351049999999</v>
+        <v>200.8650329999998</v>
       </c>
       <c r="J31" t="n">
-        <v>17.5</v>
+        <v>16.74</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4322</v>
+        <v>2.4184</v>
       </c>
       <c r="F33" t="n">
-        <v>14836.42</v>
+        <v>14752.24</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2563.219999999999</v>
+        <v>2479.039999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>20.88</v>
+        <v>20.2</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9655</v>
+        <v>1.952</v>
       </c>
       <c r="F34" t="n">
-        <v>37541.05</v>
+        <v>37283.2</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6369.850000000002</v>
+        <v>6111.999999999996</v>
       </c>
       <c r="J34" t="n">
-        <v>20.44</v>
+        <v>19.61</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.6876</v>
+        <v>6.6628</v>
       </c>
       <c r="F35" t="n">
-        <v>40703.274888</v>
+        <v>40552.332664</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>7503.289263999999</v>
+        <v>7352.347040000001</v>
       </c>
       <c r="J35" t="n">
-        <v>22.6</v>
+        <v>22.15</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.6876</v>
+        <v>6.6628</v>
       </c>
       <c r="F36" t="n">
-        <v>13822.332936</v>
+        <v>13771.074808</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2522.395944</v>
+        <v>2471.137816</v>
       </c>
       <c r="J36" t="n">
-        <v>22.32</v>
+        <v>21.87</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.6876</v>
+        <v>6.6628</v>
       </c>
       <c r="F37" t="n">
-        <v>100314</v>
+        <v>99942</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>17019</v>
+        <v>16647</v>
       </c>
       <c r="J37" t="n">
-        <v>20.43</v>
+        <v>19.99</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.8717</v>
+        <v>2.8587</v>
       </c>
       <c r="F38" t="n">
-        <v>20887.051497</v>
+        <v>20792.497167</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>5087.022954</v>
+        <v>4992.468623999997</v>
       </c>
       <c r="J38" t="n">
-        <v>32.2</v>
+        <v>31.6</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.8717</v>
+        <v>2.8587</v>
       </c>
       <c r="F39" t="n">
-        <v>29945.829147</v>
+        <v>29810.266317</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>6946.030851</v>
+        <v>6810.468020999997</v>
       </c>
       <c r="J39" t="n">
-        <v>30.2</v>
+        <v>29.61</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.2571</v>
+        <v>2.2461</v>
       </c>
       <c r="F40" t="n">
-        <v>15122.57</v>
+        <v>15048.87</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4670.57</v>
+        <v>4596.870000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>44.69</v>
+        <v>43.98</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.210000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>8210</v>
+        <v>8119.999999999999</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1101</v>
+        <v>1010.999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>15.49</v>
+        <v>14.22</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7</v>
+        <v>6.88</v>
       </c>
       <c r="F42" t="n">
-        <v>7700</v>
+        <v>7568</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1115.4</v>
+        <v>983.3999999999996</v>
       </c>
       <c r="J42" t="n">
-        <v>16.94</v>
+        <v>14.93</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>41.78</v>
+        <v>41.15</v>
       </c>
       <c r="F43" t="n">
-        <v>62670</v>
+        <v>61725</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-1785</v>
+        <v>-2730</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.77</v>
+        <v>-4.24</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9354</v>
+        <v>2.9295</v>
       </c>
       <c r="F2" t="n">
-        <v>2171.286026</v>
+        <v>2166.921855</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>301.0538300000003</v>
+        <v>296.6896590000001</v>
       </c>
       <c r="J2" t="n">
-        <v>16.1</v>
+        <v>15.86</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8438</v>
+        <v>2.877</v>
       </c>
       <c r="F3" t="n">
-        <v>922.301216</v>
+        <v>933.06864</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-77.6422080000001</v>
+        <v>-66.87478400000009</v>
       </c>
       <c r="J3" t="n">
-        <v>-7.76</v>
+        <v>-6.69</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.234</v>
+        <v>1.2292</v>
       </c>
       <c r="F4" t="n">
-        <v>7033.8</v>
+        <v>7006.440000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1613.1</v>
+        <v>1585.740000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>29.76</v>
+        <v>29.25</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9537</v>
+        <v>1.9621</v>
       </c>
       <c r="F5" t="n">
-        <v>2316.951441</v>
+        <v>2326.913253</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-83.01509999999962</v>
+        <v>-73.05328799999961</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.46</v>
+        <v>-3.04</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3125</v>
+        <v>1.3144</v>
       </c>
       <c r="F6" t="n">
-        <v>2227.693125</v>
+        <v>2230.917976</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-272.245316</v>
+        <v>-269.0204649999996</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.89</v>
+        <v>-10.76</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3125</v>
+        <v>1.3144</v>
       </c>
       <c r="F7" t="n">
-        <v>4717.256249999999</v>
+        <v>4724.08504</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-602.7305700000006</v>
+        <v>-595.9017800000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-11.33</v>
+        <v>-11.2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1596</v>
+        <v>2.1604</v>
       </c>
       <c r="F8" t="n">
-        <v>27858.84</v>
+        <v>27869.16</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8560.440000000002</v>
+        <v>8570.759999999998</v>
       </c>
       <c r="J8" t="n">
-        <v>44.36</v>
+        <v>44.41</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1117</v>
+        <v>3.0967</v>
       </c>
       <c r="F9" t="n">
-        <v>942.253877</v>
+        <v>937.711727</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>193.313904</v>
+        <v>188.771754</v>
       </c>
       <c r="J9" t="n">
-        <v>25.81</v>
+        <v>25.21</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2298</v>
+        <v>2.222</v>
       </c>
       <c r="F10" t="n">
-        <v>2319.950814</v>
+        <v>2311.83546</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>319.9322250000002</v>
+        <v>311.8168710000002</v>
       </c>
       <c r="J10" t="n">
-        <v>16</v>
+        <v>15.59</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6848</v>
+        <v>1.677</v>
       </c>
       <c r="F11" t="n">
-        <v>6970.405103999999</v>
+        <v>6938.134709999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>991.2803079999994</v>
+        <v>959.0099139999993</v>
       </c>
       <c r="J11" t="n">
-        <v>16.58</v>
+        <v>16.04</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6848</v>
+        <v>1.677</v>
       </c>
       <c r="F12" t="n">
-        <v>10132.505136</v>
+        <v>10085.59539</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1032.615819000001</v>
+        <v>985.7060730000012</v>
       </c>
       <c r="J12" t="n">
-        <v>11.35</v>
+        <v>10.83</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4289</v>
+        <v>2.4165</v>
       </c>
       <c r="F15" t="n">
-        <v>22588.77</v>
+        <v>22473.45</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3142.470000000001</v>
+        <v>3027.150000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>16.16</v>
+        <v>15.57</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.46</v>
+        <v>28.44</v>
       </c>
       <c r="F16" t="n">
-        <v>14230</v>
+        <v>14220</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.02</v>
+        <v>9.08</v>
       </c>
       <c r="F17" t="n">
-        <v>18040</v>
+        <v>18160</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>280</v>
+        <v>400</v>
       </c>
       <c r="J17" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0381</v>
+        <v>1.0367</v>
       </c>
       <c r="F18" t="n">
-        <v>4077.854039</v>
+        <v>4072.354573</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-228.6206579999994</v>
+        <v>-234.1201239999996</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.31</v>
+        <v>-5.44</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5483</v>
+        <v>1.5399</v>
       </c>
       <c r="F19" t="n">
-        <v>13470.21</v>
+        <v>13397.13</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>11.31000000000131</v>
+        <v>-61.76999999999862</v>
       </c>
       <c r="J19" t="n">
-        <v>0.08</v>
+        <v>-0.46</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1642</v>
+        <v>1.1574</v>
       </c>
       <c r="F20" t="n">
-        <v>9227.286211999999</v>
+        <v>9173.390363999999</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-772.7713500000009</v>
+        <v>-826.667198000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.73</v>
+        <v>-8.27</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.189</v>
+        <v>1.1844</v>
       </c>
       <c r="F21" t="n">
-        <v>13435.7</v>
+        <v>13383.72</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>802.3000000000011</v>
+        <v>750.3199999999997</v>
       </c>
       <c r="J21" t="n">
-        <v>6.35</v>
+        <v>5.94</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7187</v>
+        <v>1.7181</v>
       </c>
       <c r="F22" t="n">
-        <v>917.5967429999999</v>
+        <v>917.2764089999999</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>188.46317</v>
+        <v>188.142836</v>
       </c>
       <c r="J22" t="n">
-        <v>25.85</v>
+        <v>25.8</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7187</v>
+        <v>1.7181</v>
       </c>
       <c r="F23" t="n">
-        <v>22208.594538</v>
+        <v>22200.841494</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3008.181071999996</v>
+        <v>3000.428027999998</v>
       </c>
       <c r="J23" t="n">
-        <v>15.67</v>
+        <v>15.63</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5438</v>
+        <v>1.5433</v>
       </c>
       <c r="F24" t="n">
-        <v>1010.139216</v>
+        <v>1009.812056</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>210.1675840000001</v>
+        <v>209.840424</v>
       </c>
       <c r="J24" t="n">
-        <v>26.27</v>
+        <v>26.23</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.1706</v>
+        <v>6.1689</v>
       </c>
       <c r="F26" t="n">
-        <v>2562.897004</v>
+        <v>2562.190926</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>462.8964299999998</v>
+        <v>462.1903519999996</v>
       </c>
       <c r="J26" t="n">
-        <v>22.04</v>
+        <v>22.01</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9959</v>
+        <v>1.9952</v>
       </c>
       <c r="F28" t="n">
-        <v>7701.778920000001</v>
+        <v>7699.077760000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1401.902040000001</v>
+        <v>1399.200880000001</v>
       </c>
       <c r="J28" t="n">
-        <v>22.25</v>
+        <v>22.21</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9959</v>
+        <v>1.9952</v>
       </c>
       <c r="F29" t="n">
-        <v>17382.871911</v>
+        <v>17376.775408</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2382.861744000002</v>
+        <v>2376.765241000001</v>
       </c>
       <c r="J29" t="n">
-        <v>15.89</v>
+        <v>15.85</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0776</v>
+        <v>2.0769</v>
       </c>
       <c r="F30" t="n">
-        <v>10924.207784</v>
+        <v>10920.527121</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2043.819583</v>
+        <v>2040.138920000001</v>
       </c>
       <c r="J30" t="n">
-        <v>23.01</v>
+        <v>22.97</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.0776</v>
+        <v>2.0769</v>
       </c>
       <c r="F31" t="n">
-        <v>1400.863352</v>
+        <v>1400.391363</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>200.8650329999998</v>
+        <v>200.3930440000001</v>
       </c>
       <c r="J31" t="n">
-        <v>16.74</v>
+        <v>16.7</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4184</v>
+        <v>2.4168</v>
       </c>
       <c r="F33" t="n">
-        <v>14752.24</v>
+        <v>14742.48</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2479.039999999999</v>
+        <v>2469.279999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>20.2</v>
+        <v>20.12</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.952</v>
+        <v>1.9513</v>
       </c>
       <c r="F34" t="n">
-        <v>37283.2</v>
+        <v>37269.83</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6111.999999999996</v>
+        <v>6098.630000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>19.61</v>
+        <v>19.56</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.6628</v>
+        <v>6.665</v>
       </c>
       <c r="F35" t="n">
-        <v>40552.332664</v>
+        <v>40565.7227</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>7352.347040000001</v>
+        <v>7365.737075999998</v>
       </c>
       <c r="J35" t="n">
-        <v>22.15</v>
+        <v>22.19</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.6628</v>
+        <v>6.665</v>
       </c>
       <c r="F36" t="n">
-        <v>13771.074808</v>
+        <v>13775.6219</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2471.137816</v>
+        <v>2475.684907999999</v>
       </c>
       <c r="J36" t="n">
-        <v>21.87</v>
+        <v>21.91</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.6628</v>
+        <v>6.665</v>
       </c>
       <c r="F37" t="n">
-        <v>99942</v>
+        <v>99975</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>16647</v>
+        <v>16680</v>
       </c>
       <c r="J37" t="n">
-        <v>19.99</v>
+        <v>20.03</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.8587</v>
+        <v>2.8592</v>
       </c>
       <c r="F38" t="n">
-        <v>20792.497167</v>
+        <v>20796.133872</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>4992.468623999997</v>
+        <v>4996.105328999998</v>
       </c>
       <c r="J38" t="n">
-        <v>31.6</v>
+        <v>31.62</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.8587</v>
+        <v>2.8592</v>
       </c>
       <c r="F39" t="n">
-        <v>29810.266317</v>
+        <v>29815.480272</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>6810.468020999997</v>
+        <v>6815.681976</v>
       </c>
       <c r="J39" t="n">
-        <v>29.61</v>
+        <v>29.63</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.2461</v>
+        <v>2.2463</v>
       </c>
       <c r="F40" t="n">
-        <v>15048.87</v>
+        <v>15050.21</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4596.870000000001</v>
+        <v>4598.210000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>43.98</v>
+        <v>43.99</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.119999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="F41" t="n">
-        <v>8119.999999999999</v>
+        <v>8100</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1010.999999999999</v>
+        <v>991</v>
       </c>
       <c r="J41" t="n">
-        <v>14.22</v>
+        <v>13.94</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>6.88</v>
+        <v>6.87</v>
       </c>
       <c r="F42" t="n">
-        <v>7568</v>
+        <v>7557</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>983.3999999999996</v>
+        <v>972.3999999999996</v>
       </c>
       <c r="J42" t="n">
-        <v>14.93</v>
+        <v>14.77</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>41.15</v>
+        <v>40.9</v>
       </c>
       <c r="F43" t="n">
-        <v>61725</v>
+        <v>61350</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-2730</v>
+        <v>-3105</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.24</v>
+        <v>-4.82</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9295</v>
+        <v>2.9669</v>
       </c>
       <c r="F2" t="n">
-        <v>2166.921855</v>
+        <v>2194.586261</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>296.6896590000001</v>
+        <v>324.354065</v>
       </c>
       <c r="J2" t="n">
-        <v>15.86</v>
+        <v>17.34</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.877</v>
+        <v>2.8646</v>
       </c>
       <c r="F3" t="n">
-        <v>933.06864</v>
+        <v>929.047072</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-66.87478400000009</v>
+        <v>-70.89635200000009</v>
       </c>
       <c r="J3" t="n">
-        <v>-6.69</v>
+        <v>-7.09</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2292</v>
+        <v>1.2451</v>
       </c>
       <c r="F4" t="n">
-        <v>7006.440000000001</v>
+        <v>7097.070000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1585.740000000001</v>
+        <v>1676.370000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>29.25</v>
+        <v>30.93</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9621</v>
+        <v>1.9653</v>
       </c>
       <c r="F5" t="n">
-        <v>2326.913253</v>
+        <v>2330.708229</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-73.05328799999961</v>
+        <v>-69.25831199999948</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.04</v>
+        <v>-2.89</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3144</v>
+        <v>1.3172</v>
       </c>
       <c r="F6" t="n">
-        <v>2230.917976</v>
+        <v>2235.670388</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-269.0204649999996</v>
+        <v>-264.2680529999998</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.76</v>
+        <v>-10.57</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3144</v>
+        <v>1.3172</v>
       </c>
       <c r="F7" t="n">
-        <v>4724.08504</v>
+        <v>4734.14852</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-595.9017800000001</v>
+        <v>-585.8383000000003</v>
       </c>
       <c r="J7" t="n">
-        <v>-11.2</v>
+        <v>-11.01</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1604</v>
+        <v>2.1675</v>
       </c>
       <c r="F8" t="n">
-        <v>27869.16</v>
+        <v>27960.75</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8570.759999999998</v>
+        <v>8662.349999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>44.41</v>
+        <v>44.89</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0967</v>
+        <v>3.128</v>
       </c>
       <c r="F9" t="n">
-        <v>937.711727</v>
+        <v>947.1896800000001</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>188.771754</v>
+        <v>198.2497070000001</v>
       </c>
       <c r="J9" t="n">
-        <v>25.21</v>
+        <v>26.47</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.222</v>
+        <v>2.2411</v>
       </c>
       <c r="F10" t="n">
-        <v>2311.83546</v>
+        <v>2331.707673</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>311.8168710000002</v>
+        <v>331.6890839999999</v>
       </c>
       <c r="J10" t="n">
-        <v>15.59</v>
+        <v>16.58</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.677</v>
+        <v>1.6939</v>
       </c>
       <c r="F11" t="n">
-        <v>6938.134709999999</v>
+        <v>7008.053896999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>959.0099139999993</v>
+        <v>1028.929100999999</v>
       </c>
       <c r="J11" t="n">
-        <v>16.04</v>
+        <v>17.21</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.677</v>
+        <v>1.6939</v>
       </c>
       <c r="F12" t="n">
-        <v>10085.59539</v>
+        <v>10187.233173</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>985.7060730000012</v>
+        <v>1087.343856</v>
       </c>
       <c r="J12" t="n">
-        <v>10.83</v>
+        <v>11.95</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4165</v>
+        <v>2.4425</v>
       </c>
       <c r="F15" t="n">
-        <v>22473.45</v>
+        <v>22715.25</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3027.150000000001</v>
+        <v>3268.950000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>15.57</v>
+        <v>16.81</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.44</v>
+        <v>28.33</v>
       </c>
       <c r="F16" t="n">
-        <v>14220</v>
+        <v>14165</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>405</v>
+        <v>350</v>
       </c>
       <c r="J16" t="n">
-        <v>2.93</v>
+        <v>2.53</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.08</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
-        <v>18160</v>
+        <v>18000</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>400</v>
+        <v>240</v>
       </c>
       <c r="J17" t="n">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0367</v>
+        <v>1.0344</v>
       </c>
       <c r="F18" t="n">
-        <v>4072.354573</v>
+        <v>4063.319736</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-234.1201239999996</v>
+        <v>-243.1549609999997</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.44</v>
+        <v>-5.65</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5399</v>
+        <v>1.5375</v>
       </c>
       <c r="F19" t="n">
-        <v>13397.13</v>
+        <v>13376.25</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-61.76999999999862</v>
+        <v>-82.64999999999964</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.46</v>
+        <v>-0.61</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1574</v>
+        <v>1.1533</v>
       </c>
       <c r="F20" t="n">
-        <v>9173.390363999999</v>
+        <v>9140.894338</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-826.667198000001</v>
+        <v>-859.1632239999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.27</v>
+        <v>-8.59</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1844</v>
+        <v>1.1833</v>
       </c>
       <c r="F21" t="n">
-        <v>13383.72</v>
+        <v>13371.29</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>750.3199999999997</v>
+        <v>737.8900000000012</v>
       </c>
       <c r="J21" t="n">
-        <v>5.94</v>
+        <v>5.84</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7181</v>
+        <v>1.7449</v>
       </c>
       <c r="F22" t="n">
-        <v>917.2764089999999</v>
+        <v>931.5846609999999</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>188.142836</v>
+        <v>202.4510879999999</v>
       </c>
       <c r="J22" t="n">
-        <v>25.8</v>
+        <v>27.77</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7181</v>
+        <v>1.7449</v>
       </c>
       <c r="F23" t="n">
-        <v>22200.841494</v>
+        <v>22547.144126</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3000.428027999998</v>
+        <v>3346.730659999997</v>
       </c>
       <c r="J23" t="n">
-        <v>15.63</v>
+        <v>17.43</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5433</v>
+        <v>1.567</v>
       </c>
       <c r="F24" t="n">
-        <v>1009.812056</v>
+        <v>1025.31944</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>209.840424</v>
+        <v>225.347808</v>
       </c>
       <c r="J24" t="n">
-        <v>26.23</v>
+        <v>28.17</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.1689</v>
+        <v>6.2704</v>
       </c>
       <c r="F26" t="n">
-        <v>2562.190926</v>
+        <v>2604.347936</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>462.1903519999996</v>
+        <v>504.347362</v>
       </c>
       <c r="J26" t="n">
-        <v>22.01</v>
+        <v>24.02</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9952</v>
+        <v>2.0265</v>
       </c>
       <c r="F28" t="n">
-        <v>7699.077760000001</v>
+        <v>7819.858200000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1399.200880000001</v>
+        <v>1519.981320000001</v>
       </c>
       <c r="J28" t="n">
-        <v>22.21</v>
+        <v>24.13</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9952</v>
+        <v>2.0265</v>
       </c>
       <c r="F29" t="n">
-        <v>17376.775408</v>
+        <v>17649.376185</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2376.765241000001</v>
+        <v>2649.366018000001</v>
       </c>
       <c r="J29" t="n">
-        <v>15.85</v>
+        <v>17.66</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0769</v>
+        <v>2.1094</v>
       </c>
       <c r="F30" t="n">
-        <v>10920.527121</v>
+        <v>11091.415046</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2040.138920000001</v>
+        <v>2211.026845</v>
       </c>
       <c r="J30" t="n">
-        <v>22.97</v>
+        <v>24.9</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.0769</v>
+        <v>2.1094</v>
       </c>
       <c r="F31" t="n">
-        <v>1400.391363</v>
+        <v>1422.305138</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>200.3930440000001</v>
+        <v>222.3068189999999</v>
       </c>
       <c r="J31" t="n">
-        <v>16.7</v>
+        <v>18.53</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4168</v>
+        <v>2.4589</v>
       </c>
       <c r="F33" t="n">
-        <v>14742.48</v>
+        <v>14999.29</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2469.279999999999</v>
+        <v>2726.089999999998</v>
       </c>
       <c r="J33" t="n">
-        <v>20.12</v>
+        <v>22.21</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9513</v>
+        <v>1.9836</v>
       </c>
       <c r="F34" t="n">
-        <v>37269.83</v>
+        <v>37886.76</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6098.630000000001</v>
+        <v>6715.560000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>19.56</v>
+        <v>21.54</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.665</v>
+        <v>6.7982</v>
       </c>
       <c r="F35" t="n">
-        <v>40565.7227</v>
+        <v>41376.428516</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>7365.737075999998</v>
+        <v>8176.442891999999</v>
       </c>
       <c r="J35" t="n">
-        <v>22.19</v>
+        <v>24.63</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.665</v>
+        <v>6.7982</v>
       </c>
       <c r="F36" t="n">
-        <v>13775.6219</v>
+        <v>14050.927652</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2475.684907999999</v>
+        <v>2750.990659999999</v>
       </c>
       <c r="J36" t="n">
-        <v>21.91</v>
+        <v>24.35</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.665</v>
+        <v>6.7982</v>
       </c>
       <c r="F37" t="n">
-        <v>99975</v>
+        <v>101973</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>16680</v>
+        <v>18678</v>
       </c>
       <c r="J37" t="n">
-        <v>20.03</v>
+        <v>22.42</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.8592</v>
+        <v>2.9132</v>
       </c>
       <c r="F38" t="n">
-        <v>20796.133872</v>
+        <v>21188.898012</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>4996.105328999998</v>
+        <v>5388.869468999997</v>
       </c>
       <c r="J38" t="n">
-        <v>31.62</v>
+        <v>34.11</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.8592</v>
+        <v>2.9132</v>
       </c>
       <c r="F39" t="n">
-        <v>29815.480272</v>
+        <v>30378.587412</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>6815.681976</v>
+        <v>7378.789115999996</v>
       </c>
       <c r="J39" t="n">
-        <v>29.63</v>
+        <v>32.08</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.2463</v>
+        <v>2.2913</v>
       </c>
       <c r="F40" t="n">
-        <v>15050.21</v>
+        <v>15351.71</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4598.210000000001</v>
+        <v>4899.710000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>43.99</v>
+        <v>46.88</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.1</v>
+        <v>8.09</v>
       </c>
       <c r="F41" t="n">
-        <v>8100</v>
+        <v>8090</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="J41" t="n">
-        <v>13.94</v>
+        <v>13.8</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>6.87</v>
+        <v>6.83</v>
       </c>
       <c r="F42" t="n">
-        <v>7557</v>
+        <v>7513</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>972.3999999999996</v>
+        <v>928.3999999999996</v>
       </c>
       <c r="J42" t="n">
-        <v>14.77</v>
+        <v>14.1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>40.9</v>
+        <v>40.53</v>
       </c>
       <c r="F43" t="n">
-        <v>61350</v>
+        <v>60795</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-3105</v>
+        <v>-3660</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.82</v>
+        <v>-5.68</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9669</v>
+        <v>2.941</v>
       </c>
       <c r="F2" t="n">
-        <v>2194.586261</v>
+        <v>2175.42829</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>324.354065</v>
+        <v>305.1960939999999</v>
       </c>
       <c r="J2" t="n">
-        <v>17.34</v>
+        <v>16.32</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8646</v>
+        <v>2.8982</v>
       </c>
       <c r="F3" t="n">
-        <v>929.047072</v>
+        <v>939.944224</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-70.89635200000009</v>
+        <v>-59.99920000000009</v>
       </c>
       <c r="J3" t="n">
-        <v>-7.09</v>
+        <v>-6</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2451</v>
+        <v>1.2542</v>
       </c>
       <c r="F4" t="n">
-        <v>7097.070000000001</v>
+        <v>7148.94</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1676.370000000001</v>
+        <v>1728.24</v>
       </c>
       <c r="J4" t="n">
-        <v>30.93</v>
+        <v>31.88</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9653</v>
+        <v>1.933</v>
       </c>
       <c r="F5" t="n">
-        <v>2330.708229</v>
+        <v>2292.40269</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-69.25831199999948</v>
+        <v>-107.5638509999994</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.89</v>
+        <v>-4.48</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3172</v>
+        <v>1.3288</v>
       </c>
       <c r="F6" t="n">
-        <v>2235.670388</v>
+        <v>2255.358952</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-264.2680529999998</v>
+        <v>-244.5794889999997</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.57</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3172</v>
+        <v>1.3288</v>
       </c>
       <c r="F7" t="n">
-        <v>4734.14852</v>
+        <v>4775.84008</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-585.8383000000003</v>
+        <v>-544.1467400000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-11.01</v>
+        <v>-10.23</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1675</v>
+        <v>2.1687</v>
       </c>
       <c r="F8" t="n">
-        <v>27960.75</v>
+        <v>27976.23</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8662.349999999999</v>
+        <v>8677.829999999998</v>
       </c>
       <c r="J8" t="n">
-        <v>44.89</v>
+        <v>44.97</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.128</v>
+        <v>3.1302</v>
       </c>
       <c r="F9" t="n">
-        <v>947.1896800000001</v>
+        <v>947.855862</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>198.2497070000001</v>
+        <v>198.915889</v>
       </c>
       <c r="J9" t="n">
-        <v>26.47</v>
+        <v>26.56</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2411</v>
+        <v>2.2412</v>
       </c>
       <c r="F10" t="n">
-        <v>2331.707673</v>
+        <v>2331.811716</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>331.6890839999999</v>
+        <v>331.7931270000001</v>
       </c>
       <c r="J10" t="n">
-        <v>16.58</v>
+        <v>16.59</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6939</v>
+        <v>1.6952</v>
       </c>
       <c r="F11" t="n">
-        <v>7008.053896999999</v>
+        <v>7013.432295999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1028.929100999999</v>
+        <v>1034.307499999999</v>
       </c>
       <c r="J11" t="n">
-        <v>17.21</v>
+        <v>17.3</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6939</v>
+        <v>1.6952</v>
       </c>
       <c r="F12" t="n">
-        <v>10187.233173</v>
+        <v>10195.051464</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1087.343856</v>
+        <v>1095.162147000001</v>
       </c>
       <c r="J12" t="n">
-        <v>11.95</v>
+        <v>12.03</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4425</v>
+        <v>2.4444</v>
       </c>
       <c r="F15" t="n">
-        <v>22715.25</v>
+        <v>22732.92</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3268.950000000001</v>
+        <v>3286.619999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>16.81</v>
+        <v>16.9</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.33</v>
+        <v>28.16</v>
       </c>
       <c r="F16" t="n">
-        <v>14165</v>
+        <v>14080</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>350</v>
+        <v>265</v>
       </c>
       <c r="J16" t="n">
-        <v>2.53</v>
+        <v>1.92</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>8.93</v>
       </c>
       <c r="F17" t="n">
-        <v>18000</v>
+        <v>17860</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="J17" t="n">
-        <v>1.35</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5375</v>
+        <v>1.556</v>
       </c>
       <c r="F19" t="n">
-        <v>13376.25</v>
+        <v>13537.2</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-82.64999999999964</v>
+        <v>78.30000000000109</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.61</v>
+        <v>0.58</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1533</v>
+        <v>1.1599</v>
       </c>
       <c r="F20" t="n">
-        <v>9140.894338</v>
+        <v>9193.205013999999</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-859.1632239999999</v>
+        <v>-806.8525480000008</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.59</v>
+        <v>-8.07</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1833</v>
+        <v>1.1858</v>
       </c>
       <c r="F21" t="n">
-        <v>13371.29</v>
+        <v>13399.54</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>737.8900000000012</v>
+        <v>766.1399999999994</v>
       </c>
       <c r="J21" t="n">
-        <v>5.84</v>
+        <v>6.06</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7449</v>
+        <v>1.7544</v>
       </c>
       <c r="F22" t="n">
-        <v>931.5846609999999</v>
+        <v>936.656616</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>202.4510879999999</v>
+        <v>207.523043</v>
       </c>
       <c r="J22" t="n">
-        <v>27.77</v>
+        <v>28.46</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7449</v>
+        <v>1.7544</v>
       </c>
       <c r="F23" t="n">
-        <v>22547.144126</v>
+        <v>22669.900656</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3346.730659999997</v>
+        <v>3469.487189999996</v>
       </c>
       <c r="J23" t="n">
-        <v>17.43</v>
+        <v>18.07</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.567</v>
+        <v>1.5755</v>
       </c>
       <c r="F24" t="n">
-        <v>1025.31944</v>
+        <v>1030.88116</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>225.347808</v>
+        <v>230.9095279999999</v>
       </c>
       <c r="J24" t="n">
-        <v>28.17</v>
+        <v>28.86</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.2704</v>
+        <v>6.306</v>
       </c>
       <c r="F26" t="n">
-        <v>2604.347936</v>
+        <v>2619.13404</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>504.347362</v>
+        <v>519.1334659999998</v>
       </c>
       <c r="J26" t="n">
-        <v>24.02</v>
+        <v>24.72</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0265</v>
+        <v>2.0377</v>
       </c>
       <c r="F28" t="n">
-        <v>7819.858200000001</v>
+        <v>7863.076760000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1519.981320000001</v>
+        <v>1563.199880000001</v>
       </c>
       <c r="J28" t="n">
-        <v>24.13</v>
+        <v>24.81</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0265</v>
+        <v>2.0377</v>
       </c>
       <c r="F29" t="n">
-        <v>17649.376185</v>
+        <v>17746.920233</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2649.366018000001</v>
+        <v>2746.910066</v>
       </c>
       <c r="J29" t="n">
-        <v>17.66</v>
+        <v>18.31</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1094</v>
+        <v>2.1216</v>
       </c>
       <c r="F30" t="n">
-        <v>11091.415046</v>
+        <v>11155.563744</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2211.026845</v>
+        <v>2275.175542999999</v>
       </c>
       <c r="J30" t="n">
-        <v>24.9</v>
+        <v>25.62</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1094</v>
+        <v>2.1216</v>
       </c>
       <c r="F31" t="n">
-        <v>1422.305138</v>
+        <v>1430.531232</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>222.3068189999999</v>
+        <v>230.5329129999998</v>
       </c>
       <c r="J31" t="n">
-        <v>18.53</v>
+        <v>19.21</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4589</v>
+        <v>2.4716</v>
       </c>
       <c r="F33" t="n">
-        <v>14999.29</v>
+        <v>15076.76</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2726.089999999998</v>
+        <v>2803.559999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>22.21</v>
+        <v>22.84</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9836</v>
+        <v>1.9949</v>
       </c>
       <c r="F34" t="n">
-        <v>37886.76</v>
+        <v>38102.59</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6715.560000000001</v>
+        <v>6931.389999999996</v>
       </c>
       <c r="J34" t="n">
-        <v>21.54</v>
+        <v>22.24</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.7982</v>
+        <v>6.8439</v>
       </c>
       <c r="F35" t="n">
-        <v>41376.428516</v>
+        <v>41654.576082</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>8176.442891999999</v>
+        <v>8454.590457999999</v>
       </c>
       <c r="J35" t="n">
-        <v>24.63</v>
+        <v>25.47</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.7982</v>
+        <v>6.8439</v>
       </c>
       <c r="F36" t="n">
-        <v>14050.927652</v>
+        <v>14145.383154</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2750.990659999999</v>
+        <v>2845.446162</v>
       </c>
       <c r="J36" t="n">
-        <v>24.35</v>
+        <v>25.18</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.7982</v>
+        <v>6.8439</v>
       </c>
       <c r="F37" t="n">
-        <v>101973</v>
+        <v>102658.5</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>18678</v>
+        <v>19363.5</v>
       </c>
       <c r="J37" t="n">
-        <v>22.42</v>
+        <v>23.25</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.9132</v>
+        <v>2.9329</v>
       </c>
       <c r="F38" t="n">
-        <v>21188.898012</v>
+        <v>21332.184189</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>5388.869468999997</v>
+        <v>5532.155645999999</v>
       </c>
       <c r="J38" t="n">
-        <v>34.11</v>
+        <v>35.01</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9132</v>
+        <v>2.9329</v>
       </c>
       <c r="F39" t="n">
-        <v>30378.587412</v>
+        <v>30584.017239</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>7378.789115999996</v>
+        <v>7584.218943</v>
       </c>
       <c r="J39" t="n">
-        <v>32.08</v>
+        <v>32.98</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.2913</v>
+        <v>2.3086</v>
       </c>
       <c r="F40" t="n">
-        <v>15351.71</v>
+        <v>15467.62</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4899.710000000001</v>
+        <v>5015.620000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>46.88</v>
+        <v>47.99</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.09</v>
+        <v>8.06</v>
       </c>
       <c r="F41" t="n">
-        <v>8090</v>
+        <v>8060.000000000001</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>981</v>
+        <v>951.0000000000009</v>
       </c>
       <c r="J41" t="n">
-        <v>13.8</v>
+        <v>13.38</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>6.83</v>
+        <v>6.79</v>
       </c>
       <c r="F42" t="n">
-        <v>7513</v>
+        <v>7469</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>928.3999999999996</v>
+        <v>884.3999999999996</v>
       </c>
       <c r="J42" t="n">
-        <v>14.1</v>
+        <v>13.43</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>40.53</v>
+        <v>40.65</v>
       </c>
       <c r="F43" t="n">
-        <v>60795</v>
+        <v>60975</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-3660</v>
+        <v>-3480</v>
       </c>
       <c r="J43" t="n">
-        <v>-5.68</v>
+        <v>-5.4</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.941</v>
+        <v>2.9222</v>
       </c>
       <c r="F2" t="n">
-        <v>2175.42829</v>
+        <v>2161.522118</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>305.1960939999999</v>
+        <v>291.2899220000004</v>
       </c>
       <c r="J2" t="n">
-        <v>16.32</v>
+        <v>15.58</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8982</v>
+        <v>2.9311</v>
       </c>
       <c r="F3" t="n">
-        <v>939.944224</v>
+        <v>950.6143519999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-59.99920000000009</v>
+        <v>-49.32907200000011</v>
       </c>
       <c r="J3" t="n">
-        <v>-6</v>
+        <v>-4.93</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2542</v>
+        <v>1.2555</v>
       </c>
       <c r="F4" t="n">
-        <v>7148.94</v>
+        <v>7156.35</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1728.24</v>
+        <v>1735.650000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>31.88</v>
+        <v>32.02</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.933</v>
+        <v>1.9505</v>
       </c>
       <c r="F5" t="n">
-        <v>2292.40269</v>
+        <v>2313.156465</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-107.5638509999994</v>
+        <v>-86.81007599999975</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.48</v>
+        <v>-3.62</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3288</v>
+        <v>1.3277</v>
       </c>
       <c r="F6" t="n">
-        <v>2255.358952</v>
+        <v>2253.491933</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-244.5794889999997</v>
+        <v>-246.4465079999995</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.779999999999999</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3288</v>
+        <v>1.3277</v>
       </c>
       <c r="F7" t="n">
-        <v>4775.84008</v>
+        <v>4771.886570000001</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-544.1467400000001</v>
+        <v>-548.1002499999995</v>
       </c>
       <c r="J7" t="n">
-        <v>-10.23</v>
+        <v>-10.3</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1687</v>
+        <v>2.1632</v>
       </c>
       <c r="F8" t="n">
-        <v>27976.23</v>
+        <v>27905.28</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8677.829999999998</v>
+        <v>8606.879999999997</v>
       </c>
       <c r="J8" t="n">
-        <v>44.97</v>
+        <v>44.6</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1302</v>
+        <v>3.1731</v>
       </c>
       <c r="F9" t="n">
-        <v>947.855862</v>
+        <v>960.846411</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>198.915889</v>
+        <v>211.906438</v>
       </c>
       <c r="J9" t="n">
-        <v>26.56</v>
+        <v>28.29</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2412</v>
+        <v>2.2714</v>
       </c>
       <c r="F10" t="n">
-        <v>2331.811716</v>
+        <v>2363.232702</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>331.7931270000001</v>
+        <v>363.2141129999998</v>
       </c>
       <c r="J10" t="n">
-        <v>16.59</v>
+        <v>18.16</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6952</v>
+        <v>1.7181</v>
       </c>
       <c r="F11" t="n">
-        <v>7013.432295999999</v>
+        <v>7108.174862999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1034.307499999999</v>
+        <v>1129.050066999999</v>
       </c>
       <c r="J11" t="n">
-        <v>17.3</v>
+        <v>18.88</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6952</v>
+        <v>1.7181</v>
       </c>
       <c r="F12" t="n">
-        <v>10195.051464</v>
+        <v>10332.773667</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1095.162147000001</v>
+        <v>1232.88435</v>
       </c>
       <c r="J12" t="n">
-        <v>12.03</v>
+        <v>13.55</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4444</v>
+        <v>2.4796</v>
       </c>
       <c r="F15" t="n">
-        <v>22732.92</v>
+        <v>23060.28</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3286.619999999999</v>
+        <v>3613.98</v>
       </c>
       <c r="J15" t="n">
-        <v>16.9</v>
+        <v>18.58</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.16</v>
+        <v>28.03</v>
       </c>
       <c r="F16" t="n">
-        <v>14080</v>
+        <v>14015</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>265</v>
+        <v>200</v>
       </c>
       <c r="J16" t="n">
-        <v>1.92</v>
+        <v>1.45</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>8.93</v>
+        <v>8.9</v>
       </c>
       <c r="F17" t="n">
-        <v>17860</v>
+        <v>17800</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0344</v>
+        <v>1.0349</v>
       </c>
       <c r="F18" t="n">
-        <v>4063.319736</v>
+        <v>4065.283831</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-243.1549609999997</v>
+        <v>-241.1908659999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.65</v>
+        <v>-5.6</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.556</v>
+        <v>1.5562</v>
       </c>
       <c r="F19" t="n">
-        <v>13537.2</v>
+        <v>13538.94</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>78.30000000000109</v>
+        <v>80.04000000000087</v>
       </c>
       <c r="J19" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1599</v>
+        <v>1.1497</v>
       </c>
       <c r="F20" t="n">
-        <v>9193.205013999999</v>
+        <v>9112.361241999999</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-806.8525480000008</v>
+        <v>-887.6963200000009</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.07</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1858</v>
+        <v>1.1861</v>
       </c>
       <c r="F21" t="n">
-        <v>13399.54</v>
+        <v>13402.93</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>766.1399999999994</v>
+        <v>769.5299999999988</v>
       </c>
       <c r="J21" t="n">
-        <v>6.06</v>
+        <v>6.09</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7544</v>
+        <v>1.7999</v>
       </c>
       <c r="F22" t="n">
-        <v>936.656616</v>
+        <v>960.948611</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>207.523043</v>
+        <v>231.8150380000001</v>
       </c>
       <c r="J22" t="n">
-        <v>28.46</v>
+        <v>31.79</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7544</v>
+        <v>1.7999</v>
       </c>
       <c r="F23" t="n">
-        <v>22669.900656</v>
+        <v>23257.839826</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3469.487189999996</v>
+        <v>4057.426359999998</v>
       </c>
       <c r="J23" t="n">
-        <v>18.07</v>
+        <v>21.13</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5755</v>
+        <v>1.6165</v>
       </c>
       <c r="F24" t="n">
-        <v>1030.88116</v>
+        <v>1057.70828</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>230.9095279999999</v>
+        <v>257.7366480000001</v>
       </c>
       <c r="J24" t="n">
-        <v>28.86</v>
+        <v>32.22</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.306</v>
+        <v>6.4674</v>
       </c>
       <c r="F26" t="n">
-        <v>2619.13404</v>
+        <v>2686.169916</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>519.1334659999998</v>
+        <v>586.1693419999997</v>
       </c>
       <c r="J26" t="n">
-        <v>24.72</v>
+        <v>27.91</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0377</v>
+        <v>2.0911</v>
       </c>
       <c r="F28" t="n">
-        <v>7863.076760000001</v>
+        <v>8069.136680000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1563.199880000001</v>
+        <v>1769.259800000001</v>
       </c>
       <c r="J28" t="n">
-        <v>24.81</v>
+        <v>28.08</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0377</v>
+        <v>2.0911</v>
       </c>
       <c r="F29" t="n">
-        <v>17746.920233</v>
+        <v>18211.996319</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2746.910066</v>
+        <v>3211.986152000001</v>
       </c>
       <c r="J29" t="n">
-        <v>18.31</v>
+        <v>21.41</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1216</v>
+        <v>2.1779</v>
       </c>
       <c r="F30" t="n">
-        <v>11155.563744</v>
+        <v>11451.594211</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2275.175542999999</v>
+        <v>2571.206010000002</v>
       </c>
       <c r="J30" t="n">
-        <v>25.62</v>
+        <v>28.95</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1216</v>
+        <v>2.1779</v>
       </c>
       <c r="F31" t="n">
-        <v>1430.531232</v>
+        <v>1468.492633</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>230.5329129999998</v>
+        <v>268.494314</v>
       </c>
       <c r="J31" t="n">
-        <v>19.21</v>
+        <v>22.37</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4716</v>
+        <v>2.5409</v>
       </c>
       <c r="F33" t="n">
-        <v>15076.76</v>
+        <v>15499.49</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2803.559999999999</v>
+        <v>3226.290000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>22.84</v>
+        <v>26.29</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9949</v>
+        <v>2.0503</v>
       </c>
       <c r="F34" t="n">
-        <v>38102.59</v>
+        <v>39160.73</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6931.389999999996</v>
+        <v>7989.530000000002</v>
       </c>
       <c r="J34" t="n">
-        <v>22.24</v>
+        <v>25.63</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.8439</v>
+        <v>7.0021</v>
       </c>
       <c r="F35" t="n">
-        <v>41654.576082</v>
+        <v>42617.441398</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>8454.590457999999</v>
+        <v>9417.455774000002</v>
       </c>
       <c r="J35" t="n">
-        <v>25.47</v>
+        <v>28.37</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.8439</v>
+        <v>7.0021</v>
       </c>
       <c r="F36" t="n">
-        <v>14145.383154</v>
+        <v>14472.360406</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2845.446162</v>
+        <v>3172.423414000001</v>
       </c>
       <c r="J36" t="n">
-        <v>25.18</v>
+        <v>28.07</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.8439</v>
+        <v>7.0021</v>
       </c>
       <c r="F37" t="n">
-        <v>102658.5</v>
+        <v>105031.5</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>19363.5</v>
+        <v>21736.5</v>
       </c>
       <c r="J37" t="n">
-        <v>23.25</v>
+        <v>26.1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.9329</v>
+        <v>3.0094</v>
       </c>
       <c r="F38" t="n">
-        <v>21332.184189</v>
+        <v>21888.600054</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>5532.155645999999</v>
+        <v>6088.571510999998</v>
       </c>
       <c r="J38" t="n">
-        <v>35.01</v>
+        <v>38.54</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9329</v>
+        <v>3.0094</v>
       </c>
       <c r="F39" t="n">
-        <v>30584.017239</v>
+        <v>31381.752354</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>7584.218943</v>
+        <v>8381.954057999996</v>
       </c>
       <c r="J39" t="n">
-        <v>32.98</v>
+        <v>36.44</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.3086</v>
+        <v>2.3833</v>
       </c>
       <c r="F40" t="n">
-        <v>15467.62</v>
+        <v>15968.11</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>5015.620000000001</v>
+        <v>5516.110000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>47.99</v>
+        <v>52.78</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.06</v>
+        <v>8.08</v>
       </c>
       <c r="F41" t="n">
-        <v>8060.000000000001</v>
+        <v>8080</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>951.0000000000009</v>
+        <v>971</v>
       </c>
       <c r="J41" t="n">
-        <v>13.38</v>
+        <v>13.66</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>6.79</v>
+        <v>6.86</v>
       </c>
       <c r="F42" t="n">
-        <v>7469</v>
+        <v>7546</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>884.3999999999996</v>
+        <v>961.3999999999996</v>
       </c>
       <c r="J42" t="n">
-        <v>13.43</v>
+        <v>14.6</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>40.65</v>
+        <v>40.97</v>
       </c>
       <c r="F43" t="n">
-        <v>60975</v>
+        <v>61455</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-3480</v>
+        <v>-3000</v>
       </c>
       <c r="J43" t="n">
-        <v>-5.4</v>
+        <v>-4.65</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9222</v>
+        <v>2.928</v>
       </c>
       <c r="F2" t="n">
-        <v>2161.522118</v>
+        <v>2165.81232</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>291.2899220000004</v>
+        <v>295.5801240000001</v>
       </c>
       <c r="J2" t="n">
-        <v>15.58</v>
+        <v>15.8</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9311</v>
+        <v>2.9123</v>
       </c>
       <c r="F3" t="n">
-        <v>950.6143519999999</v>
+        <v>944.5171360000001</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-49.32907200000011</v>
+        <v>-55.426288</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.93</v>
+        <v>-5.54</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2555</v>
+        <v>1.2481</v>
       </c>
       <c r="F4" t="n">
-        <v>7156.35</v>
+        <v>7114.17</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1735.650000000001</v>
+        <v>1693.47</v>
       </c>
       <c r="J4" t="n">
-        <v>32.02</v>
+        <v>31.24</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9505</v>
+        <v>1.9475</v>
       </c>
       <c r="F5" t="n">
-        <v>2313.156465</v>
+        <v>2309.598675</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-86.81007599999975</v>
+        <v>-90.36786599999959</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.62</v>
+        <v>-3.77</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3277</v>
+        <v>1.3279</v>
       </c>
       <c r="F6" t="n">
-        <v>2253.491933</v>
+        <v>2253.831391</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-246.4465079999995</v>
+        <v>-246.1070499999996</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.859999999999999</v>
+        <v>-9.84</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3277</v>
+        <v>1.3279</v>
       </c>
       <c r="F7" t="n">
-        <v>4771.886570000001</v>
+        <v>4772.60539</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-548.1002499999995</v>
+        <v>-547.3814300000004</v>
       </c>
       <c r="J7" t="n">
-        <v>-10.3</v>
+        <v>-10.29</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1632</v>
+        <v>2.1647</v>
       </c>
       <c r="F8" t="n">
-        <v>27905.28</v>
+        <v>27924.63</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8606.879999999997</v>
+        <v>8626.229999999996</v>
       </c>
       <c r="J8" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1731</v>
+        <v>3.1718</v>
       </c>
       <c r="F9" t="n">
-        <v>960.846411</v>
+        <v>960.452758</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>211.906438</v>
+        <v>211.512785</v>
       </c>
       <c r="J9" t="n">
-        <v>28.29</v>
+        <v>28.24</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2714</v>
+        <v>2.2715</v>
       </c>
       <c r="F10" t="n">
-        <v>2363.232702</v>
+        <v>2363.336745</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>363.2141129999998</v>
+        <v>363.318156</v>
       </c>
       <c r="J10" t="n">
-        <v>18.16</v>
+        <v>18.17</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7181</v>
+        <v>1.7179</v>
       </c>
       <c r="F11" t="n">
-        <v>7108.174862999999</v>
+        <v>7107.347416999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1129.050066999999</v>
+        <v>1128.222620999999</v>
       </c>
       <c r="J11" t="n">
-        <v>18.88</v>
+        <v>18.87</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7181</v>
+        <v>1.7179</v>
       </c>
       <c r="F12" t="n">
-        <v>10332.773667</v>
+        <v>10331.570853</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1232.88435</v>
+        <v>1231.681536</v>
       </c>
       <c r="J12" t="n">
-        <v>13.55</v>
+        <v>13.54</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4796</v>
+        <v>2.4788</v>
       </c>
       <c r="F15" t="n">
-        <v>23060.28</v>
+        <v>23052.84</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3613.98</v>
+        <v>3606.540000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>18.58</v>
+        <v>18.55</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.03</v>
+        <v>28.01</v>
       </c>
       <c r="F16" t="n">
-        <v>14015</v>
+        <v>14005</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="J16" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>8.9</v>
+        <v>8.85</v>
       </c>
       <c r="F17" t="n">
-        <v>17800</v>
+        <v>17700</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>40</v>
+        <v>-60</v>
       </c>
       <c r="J17" t="n">
-        <v>0.23</v>
+        <v>-0.34</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0349</v>
+        <v>1.0335</v>
       </c>
       <c r="F18" t="n">
-        <v>4065.283831</v>
+        <v>4059.784365</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-241.1908659999999</v>
+        <v>-246.6903319999992</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.6</v>
+        <v>-5.73</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5562</v>
+        <v>1.5438</v>
       </c>
       <c r="F19" t="n">
-        <v>13538.94</v>
+        <v>13431.06</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>80.04000000000087</v>
+        <v>-27.83999999999833</v>
       </c>
       <c r="J19" t="n">
-        <v>0.59</v>
+        <v>-0.21</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1497</v>
+        <v>1.1425</v>
       </c>
       <c r="F20" t="n">
-        <v>9112.361241999999</v>
+        <v>9055.295050000001</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-887.6963200000009</v>
+        <v>-944.7625119999993</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.880000000000001</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1861</v>
+        <v>1.1807</v>
       </c>
       <c r="F21" t="n">
-        <v>13402.93</v>
+        <v>13341.91</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>769.5299999999988</v>
+        <v>708.510000000002</v>
       </c>
       <c r="J21" t="n">
-        <v>6.09</v>
+        <v>5.61</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7999</v>
+        <v>1.813</v>
       </c>
       <c r="F22" t="n">
-        <v>960.948611</v>
+        <v>967.9425699999999</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>231.8150380000001</v>
+        <v>238.808997</v>
       </c>
       <c r="J22" t="n">
-        <v>31.79</v>
+        <v>32.75</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7999</v>
+        <v>1.813</v>
       </c>
       <c r="F23" t="n">
-        <v>23257.839826</v>
+        <v>23427.11462</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>4057.426359999998</v>
+        <v>4226.701153999998</v>
       </c>
       <c r="J23" t="n">
-        <v>21.13</v>
+        <v>22.01</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6165</v>
+        <v>1.6279</v>
       </c>
       <c r="F24" t="n">
-        <v>1057.70828</v>
+        <v>1065.167528</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>257.7366480000001</v>
+        <v>265.1958959999999</v>
       </c>
       <c r="J24" t="n">
-        <v>32.22</v>
+        <v>33.15</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.4674</v>
+        <v>6.5167</v>
       </c>
       <c r="F26" t="n">
-        <v>2686.169916</v>
+        <v>2706.646178</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>586.1693419999997</v>
+        <v>606.6456039999998</v>
       </c>
       <c r="J26" t="n">
-        <v>27.91</v>
+        <v>28.89</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0911</v>
+        <v>2.1066</v>
       </c>
       <c r="F28" t="n">
-        <v>8069.136680000001</v>
+        <v>8128.948079999999</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1769.259800000001</v>
+        <v>1829.071199999999</v>
       </c>
       <c r="J28" t="n">
-        <v>28.08</v>
+        <v>29.03</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0911</v>
+        <v>2.1066</v>
       </c>
       <c r="F29" t="n">
-        <v>18211.996319</v>
+        <v>18346.990314</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>3211.986152000001</v>
+        <v>3346.980146999998</v>
       </c>
       <c r="J29" t="n">
-        <v>21.41</v>
+        <v>22.31</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1779</v>
+        <v>2.1941</v>
       </c>
       <c r="F30" t="n">
-        <v>11451.594211</v>
+        <v>11536.775269</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2571.206010000002</v>
+        <v>2656.387068000002</v>
       </c>
       <c r="J30" t="n">
-        <v>28.95</v>
+        <v>29.91</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1779</v>
+        <v>2.1941</v>
       </c>
       <c r="F31" t="n">
-        <v>1468.492633</v>
+        <v>1479.415807</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>268.494314</v>
+        <v>279.417488</v>
       </c>
       <c r="J31" t="n">
-        <v>22.37</v>
+        <v>23.28</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.5409</v>
+        <v>2.5631</v>
       </c>
       <c r="F33" t="n">
-        <v>15499.49</v>
+        <v>15634.91</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3226.290000000001</v>
+        <v>3361.709999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>26.29</v>
+        <v>27.39</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0503</v>
+        <v>2.066</v>
       </c>
       <c r="F34" t="n">
-        <v>39160.73</v>
+        <v>39460.6</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>7989.530000000002</v>
+        <v>8289.399999999998</v>
       </c>
       <c r="J34" t="n">
-        <v>25.63</v>
+        <v>26.59</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>7.0021</v>
+        <v>7.0415</v>
       </c>
       <c r="F35" t="n">
-        <v>42617.441398</v>
+        <v>42857.24477</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>9417.455774000002</v>
+        <v>9657.259146000004</v>
       </c>
       <c r="J35" t="n">
-        <v>28.37</v>
+        <v>29.09</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>7.0021</v>
+        <v>7.0415</v>
       </c>
       <c r="F36" t="n">
-        <v>14472.360406</v>
+        <v>14553.79469</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>3172.423414000001</v>
+        <v>3253.857698</v>
       </c>
       <c r="J36" t="n">
-        <v>28.07</v>
+        <v>28.8</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>7.0021</v>
+        <v>7.0415</v>
       </c>
       <c r="F37" t="n">
-        <v>105031.5</v>
+        <v>105622.5</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>21736.5</v>
+        <v>22327.5</v>
       </c>
       <c r="J37" t="n">
-        <v>26.1</v>
+        <v>26.81</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>3.0094</v>
+        <v>3.019</v>
       </c>
       <c r="F38" t="n">
-        <v>21888.600054</v>
+        <v>21958.42479</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>6088.571510999998</v>
+        <v>6158.396247000001</v>
       </c>
       <c r="J38" t="n">
-        <v>38.54</v>
+        <v>38.98</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>3.0094</v>
+        <v>3.019</v>
       </c>
       <c r="F39" t="n">
-        <v>31381.752354</v>
+        <v>31481.86029</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>8381.954057999996</v>
+        <v>8482.061994</v>
       </c>
       <c r="J39" t="n">
-        <v>36.44</v>
+        <v>36.88</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.3833</v>
+        <v>2.398</v>
       </c>
       <c r="F40" t="n">
-        <v>15968.11</v>
+        <v>16066.6</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>5516.110000000001</v>
+        <v>5614.6</v>
       </c>
       <c r="J40" t="n">
-        <v>52.78</v>
+        <v>53.72</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.08</v>
+        <v>8.09</v>
       </c>
       <c r="F41" t="n">
-        <v>8080</v>
+        <v>8090</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>971</v>
+        <v>981</v>
       </c>
       <c r="J41" t="n">
-        <v>13.66</v>
+        <v>13.8</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>6.86</v>
+        <v>6.87</v>
       </c>
       <c r="F42" t="n">
-        <v>7546</v>
+        <v>7557</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>961.3999999999996</v>
+        <v>972.3999999999996</v>
       </c>
       <c r="J42" t="n">
-        <v>14.6</v>
+        <v>14.77</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>40.97</v>
+        <v>40.83</v>
       </c>
       <c r="F43" t="n">
-        <v>61455</v>
+        <v>61245</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-3000</v>
+        <v>-3210</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.65</v>
+        <v>-4.98</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.928</v>
+        <v>2.9031</v>
       </c>
       <c r="F2" t="n">
-        <v>2165.81232</v>
+        <v>2147.394039</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>295.5801240000001</v>
+        <v>277.1618429999999</v>
       </c>
       <c r="J2" t="n">
-        <v>15.8</v>
+        <v>14.82</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9123</v>
+        <v>2.9004</v>
       </c>
       <c r="F3" t="n">
-        <v>944.5171360000001</v>
+        <v>940.6577279999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-55.426288</v>
+        <v>-59.28569600000014</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.54</v>
+        <v>-5.93</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2481</v>
+        <v>1.2238</v>
       </c>
       <c r="F4" t="n">
-        <v>7114.17</v>
+        <v>6975.66</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1693.47</v>
+        <v>1554.96</v>
       </c>
       <c r="J4" t="n">
-        <v>31.24</v>
+        <v>28.69</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9475</v>
+        <v>1.9325</v>
       </c>
       <c r="F5" t="n">
-        <v>2309.598675</v>
+        <v>2291.809725</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-90.36786599999959</v>
+        <v>-108.1568159999997</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.77</v>
+        <v>-4.51</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3279</v>
+        <v>1.3339</v>
       </c>
       <c r="F6" t="n">
-        <v>2253.831391</v>
+        <v>2264.015131</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-246.1070499999996</v>
+        <v>-235.9233099999997</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.84</v>
+        <v>-9.44</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3279</v>
+        <v>1.3339</v>
       </c>
       <c r="F7" t="n">
-        <v>4772.60539</v>
+        <v>4794.16999</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-547.3814300000004</v>
+        <v>-525.8168299999998</v>
       </c>
       <c r="J7" t="n">
-        <v>-10.29</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1647</v>
+        <v>2.1737</v>
       </c>
       <c r="F8" t="n">
-        <v>27924.63</v>
+        <v>28040.73</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8626.229999999996</v>
+        <v>8742.330000000002</v>
       </c>
       <c r="J8" t="n">
-        <v>44.7</v>
+        <v>45.3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1718</v>
+        <v>3.1494</v>
       </c>
       <c r="F9" t="n">
-        <v>960.452758</v>
+        <v>953.669814</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>211.512785</v>
+        <v>204.729841</v>
       </c>
       <c r="J9" t="n">
-        <v>28.24</v>
+        <v>27.34</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2715</v>
+        <v>2.257</v>
       </c>
       <c r="F10" t="n">
-        <v>2363.336745</v>
+        <v>2348.25051</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>363.318156</v>
+        <v>348.2319210000003</v>
       </c>
       <c r="J10" t="n">
-        <v>18.17</v>
+        <v>17.41</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7179</v>
+        <v>1.7059</v>
       </c>
       <c r="F11" t="n">
-        <v>7107.347416999999</v>
+        <v>7057.700656999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1128.222620999999</v>
+        <v>1078.575860999999</v>
       </c>
       <c r="J11" t="n">
-        <v>18.87</v>
+        <v>18.04</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7179</v>
+        <v>1.7059</v>
       </c>
       <c r="F12" t="n">
-        <v>10331.570853</v>
+        <v>10259.402013</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1231.681536</v>
+        <v>1159.512696</v>
       </c>
       <c r="J12" t="n">
-        <v>13.54</v>
+        <v>12.74</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4788</v>
+        <v>2.4602</v>
       </c>
       <c r="F15" t="n">
-        <v>23052.84</v>
+        <v>22879.86</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3606.540000000001</v>
+        <v>3433.560000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>18.55</v>
+        <v>17.66</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.01</v>
+        <v>28.1</v>
       </c>
       <c r="F16" t="n">
-        <v>14005</v>
+        <v>14050</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>190</v>
+        <v>235</v>
       </c>
       <c r="J16" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0335</v>
+        <v>1.0354</v>
       </c>
       <c r="F18" t="n">
-        <v>4059.784365</v>
+        <v>4067.247926</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-246.6903319999992</v>
+        <v>-239.2267709999992</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.73</v>
+        <v>-5.56</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5438</v>
+        <v>1.5403</v>
       </c>
       <c r="F19" t="n">
-        <v>13431.06</v>
+        <v>13400.61</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-27.83999999999833</v>
+        <v>-58.28999999999905</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.21</v>
+        <v>-0.43</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1425</v>
+        <v>1.1463</v>
       </c>
       <c r="F20" t="n">
-        <v>9055.295050000001</v>
+        <v>9085.413318000001</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-944.7625119999993</v>
+        <v>-914.6442439999992</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.15</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1807</v>
+        <v>1.1831</v>
       </c>
       <c r="F21" t="n">
-        <v>13341.91</v>
+        <v>13369.03</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>708.510000000002</v>
+        <v>735.630000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>5.61</v>
+        <v>5.82</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.813</v>
+        <v>1.7987</v>
       </c>
       <c r="F22" t="n">
-        <v>967.9425699999999</v>
+        <v>960.3079429999999</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>238.808997</v>
+        <v>231.17437</v>
       </c>
       <c r="J22" t="n">
-        <v>32.75</v>
+        <v>31.71</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.813</v>
+        <v>1.7987</v>
       </c>
       <c r="F23" t="n">
-        <v>23427.11462</v>
+        <v>23242.333738</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>4226.701153999998</v>
+        <v>4041.920271999996</v>
       </c>
       <c r="J23" t="n">
-        <v>22.01</v>
+        <v>21.05</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6279</v>
+        <v>1.6157</v>
       </c>
       <c r="F24" t="n">
-        <v>1065.167528</v>
+        <v>1057.184824</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>265.1958959999999</v>
+        <v>257.2131919999999</v>
       </c>
       <c r="J24" t="n">
-        <v>33.15</v>
+        <v>32.15</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.5167</v>
+        <v>6.4621</v>
       </c>
       <c r="F26" t="n">
-        <v>2706.646178</v>
+        <v>2683.968614</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>606.6456039999998</v>
+        <v>583.9680399999997</v>
       </c>
       <c r="J26" t="n">
-        <v>28.89</v>
+        <v>27.81</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.1066</v>
+        <v>2.0897</v>
       </c>
       <c r="F28" t="n">
-        <v>8128.948079999999</v>
+        <v>8063.73436</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1829.071199999999</v>
+        <v>1763.857480000001</v>
       </c>
       <c r="J28" t="n">
-        <v>29.03</v>
+        <v>28</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.1066</v>
+        <v>2.0897</v>
       </c>
       <c r="F29" t="n">
-        <v>18346.990314</v>
+        <v>18199.803313</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>3346.980146999998</v>
+        <v>3199.793146000004</v>
       </c>
       <c r="J29" t="n">
-        <v>22.31</v>
+        <v>21.33</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1941</v>
+        <v>2.1767</v>
       </c>
       <c r="F30" t="n">
-        <v>11536.775269</v>
+        <v>11445.284503</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2656.387068000002</v>
+        <v>2564.896301999999</v>
       </c>
       <c r="J30" t="n">
-        <v>29.91</v>
+        <v>28.88</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1941</v>
+        <v>2.1767</v>
       </c>
       <c r="F31" t="n">
-        <v>1479.415807</v>
+        <v>1467.683509</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>279.417488</v>
+        <v>267.6851899999999</v>
       </c>
       <c r="J31" t="n">
-        <v>23.28</v>
+        <v>22.31</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.5631</v>
+        <v>2.544</v>
       </c>
       <c r="F33" t="n">
-        <v>15634.91</v>
+        <v>15518.4</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3361.709999999999</v>
+        <v>3245.199999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>27.39</v>
+        <v>26.44</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>2.066</v>
+        <v>2.0487</v>
       </c>
       <c r="F34" t="n">
-        <v>39460.6</v>
+        <v>39130.17000000001</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>8289.399999999998</v>
+        <v>7958.970000000005</v>
       </c>
       <c r="J34" t="n">
-        <v>26.59</v>
+        <v>25.53</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>7.0415</v>
+        <v>6.9979</v>
       </c>
       <c r="F35" t="n">
-        <v>42857.24477</v>
+        <v>42591.878602</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>9657.259146000004</v>
+        <v>9391.892977999996</v>
       </c>
       <c r="J35" t="n">
-        <v>29.09</v>
+        <v>28.29</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>7.0415</v>
+        <v>6.9979</v>
       </c>
       <c r="F36" t="n">
-        <v>14553.79469</v>
+        <v>14463.679594</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>3253.857698</v>
+        <v>3163.742601999998</v>
       </c>
       <c r="J36" t="n">
-        <v>28.8</v>
+        <v>28</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>7.0415</v>
+        <v>6.9979</v>
       </c>
       <c r="F37" t="n">
-        <v>105622.5</v>
+        <v>104968.5</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>22327.5</v>
+        <v>21673.5</v>
       </c>
       <c r="J37" t="n">
-        <v>26.81</v>
+        <v>26.02</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>3.019</v>
+        <v>2.9937</v>
       </c>
       <c r="F38" t="n">
-        <v>21958.42479</v>
+        <v>21774.407517</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>6158.396247000001</v>
+        <v>5974.378973999999</v>
       </c>
       <c r="J38" t="n">
-        <v>38.98</v>
+        <v>37.81</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>3.019</v>
+        <v>2.9937</v>
       </c>
       <c r="F39" t="n">
-        <v>31481.86029</v>
+        <v>31218.034167</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>8482.061994</v>
+        <v>8218.235871000001</v>
       </c>
       <c r="J39" t="n">
-        <v>36.88</v>
+        <v>35.73</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.398</v>
+        <v>2.3765</v>
       </c>
       <c r="F40" t="n">
-        <v>16066.6</v>
+        <v>15922.55</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>5614.6</v>
+        <v>5470.550000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>53.72</v>
+        <v>52.34</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.09</v>
+        <v>8.1</v>
       </c>
       <c r="F41" t="n">
-        <v>8090</v>
+        <v>8100</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>981</v>
+        <v>991</v>
       </c>
       <c r="J41" t="n">
-        <v>13.8</v>
+        <v>13.94</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>6.87</v>
+        <v>6.83</v>
       </c>
       <c r="F42" t="n">
-        <v>7557</v>
+        <v>7513</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>972.3999999999996</v>
+        <v>928.3999999999996</v>
       </c>
       <c r="J42" t="n">
-        <v>14.77</v>
+        <v>14.1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>40.83</v>
+        <v>40.6</v>
       </c>
       <c r="F43" t="n">
-        <v>61245</v>
+        <v>60900</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-3210</v>
+        <v>-3555</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.98</v>
+        <v>-5.52</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9031</v>
+        <v>2.827</v>
       </c>
       <c r="F2" t="n">
-        <v>2147.394039</v>
+        <v>2091.10363</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>277.1618429999999</v>
+        <v>220.8714340000001</v>
       </c>
       <c r="J2" t="n">
-        <v>14.82</v>
+        <v>11.81</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9004</v>
+        <v>2.8662</v>
       </c>
       <c r="F3" t="n">
-        <v>940.6577279999999</v>
+        <v>929.565984</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-59.28569600000014</v>
+        <v>-70.37744000000009</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.93</v>
+        <v>-7.04</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2238</v>
+        <v>1.1932</v>
       </c>
       <c r="F4" t="n">
-        <v>6975.66</v>
+        <v>6801.24</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1554.96</v>
+        <v>1380.54</v>
       </c>
       <c r="J4" t="n">
-        <v>28.69</v>
+        <v>25.47</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9325</v>
+        <v>1.915</v>
       </c>
       <c r="F5" t="n">
-        <v>2291.809725</v>
+        <v>2271.05595</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-108.1568159999997</v>
+        <v>-128.9105909999998</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.51</v>
+        <v>-5.37</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3339</v>
+        <v>1.3166</v>
       </c>
       <c r="F6" t="n">
-        <v>2264.015131</v>
+        <v>2234.652014</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-235.9233099999997</v>
+        <v>-265.286427</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.44</v>
+        <v>-10.61</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3339</v>
+        <v>1.3166</v>
       </c>
       <c r="F7" t="n">
-        <v>4794.16999</v>
+        <v>4731.99206</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-525.8168299999998</v>
+        <v>-587.9947600000005</v>
       </c>
       <c r="J7" t="n">
-        <v>-9.880000000000001</v>
+        <v>-11.05</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1737</v>
+        <v>2.1917</v>
       </c>
       <c r="F8" t="n">
-        <v>28040.73</v>
+        <v>28272.93</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8742.330000000002</v>
+        <v>8974.529999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>45.3</v>
+        <v>46.5</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.257</v>
+        <v>2.2543</v>
       </c>
       <c r="F10" t="n">
-        <v>2348.25051</v>
+        <v>2345.441349</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>348.2319210000003</v>
+        <v>345.4227600000002</v>
       </c>
       <c r="J10" t="n">
-        <v>17.41</v>
+        <v>17.27</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4602</v>
+        <v>2.4605</v>
       </c>
       <c r="F15" t="n">
-        <v>22879.86</v>
+        <v>22882.65</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3433.560000000001</v>
+        <v>3436.350000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>17.66</v>
+        <v>17.67</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.1</v>
+        <v>28.35</v>
       </c>
       <c r="F16" t="n">
-        <v>14050</v>
+        <v>14175</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>235</v>
+        <v>360</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7</v>
+        <v>2.61</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>8.85</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>17700</v>
+        <v>17780</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>-60</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.34</v>
+        <v>0.11</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0354</v>
+        <v>1.0375</v>
       </c>
       <c r="F18" t="n">
-        <v>4067.247926</v>
+        <v>4075.497125</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-239.2267709999992</v>
+        <v>-230.9775719999993</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.56</v>
+        <v>-5.36</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5403</v>
+        <v>1.532</v>
       </c>
       <c r="F19" t="n">
-        <v>13400.61</v>
+        <v>13328.4</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-58.28999999999905</v>
+        <v>-130.5</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.43</v>
+        <v>-0.97</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1463</v>
+        <v>1.1483</v>
       </c>
       <c r="F20" t="n">
-        <v>9085.413318000001</v>
+        <v>9101.265038</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-914.6442439999992</v>
+        <v>-898.7925240000004</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.15</v>
+        <v>-8.99</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1831</v>
+        <v>1.1807</v>
       </c>
       <c r="F21" t="n">
-        <v>13369.03</v>
+        <v>13341.91</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>735.630000000001</v>
+        <v>708.510000000002</v>
       </c>
       <c r="J21" t="n">
-        <v>5.82</v>
+        <v>5.61</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7987</v>
+        <v>1.7997</v>
       </c>
       <c r="F22" t="n">
-        <v>960.3079429999999</v>
+        <v>960.8418330000001</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>231.17437</v>
+        <v>231.7082600000001</v>
       </c>
       <c r="J22" t="n">
-        <v>31.71</v>
+        <v>31.78</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7987</v>
+        <v>1.7997</v>
       </c>
       <c r="F23" t="n">
-        <v>23242.333738</v>
+        <v>23255.255478</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>4041.920271999996</v>
+        <v>4054.842011999997</v>
       </c>
       <c r="J23" t="n">
-        <v>21.05</v>
+        <v>21.12</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6157</v>
+        <v>1.6166</v>
       </c>
       <c r="F24" t="n">
-        <v>1057.184824</v>
+        <v>1057.773712</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>257.2131919999999</v>
+        <v>257.8020800000002</v>
       </c>
       <c r="J24" t="n">
-        <v>32.15</v>
+        <v>32.23</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.4621</v>
+        <v>6.4652</v>
       </c>
       <c r="F26" t="n">
-        <v>2683.968614</v>
+        <v>2685.256168</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>583.9680399999997</v>
+        <v>585.2555939999997</v>
       </c>
       <c r="J26" t="n">
-        <v>27.81</v>
+        <v>27.87</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0897</v>
+        <v>2.0909</v>
       </c>
       <c r="F28" t="n">
-        <v>8063.73436</v>
+        <v>8068.36492</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1763.857480000001</v>
+        <v>1768.48804</v>
       </c>
       <c r="J28" t="n">
-        <v>28</v>
+        <v>28.07</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0897</v>
+        <v>2.0909</v>
       </c>
       <c r="F29" t="n">
-        <v>18199.803313</v>
+        <v>18210.254461</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>3199.793146000004</v>
+        <v>3210.244294</v>
       </c>
       <c r="J29" t="n">
-        <v>21.33</v>
+        <v>21.4</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1767</v>
+        <v>2.1779</v>
       </c>
       <c r="F30" t="n">
-        <v>11445.284503</v>
+        <v>11451.594211</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2564.896301999999</v>
+        <v>2571.206010000002</v>
       </c>
       <c r="J30" t="n">
-        <v>28.88</v>
+        <v>28.95</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1767</v>
+        <v>2.1779</v>
       </c>
       <c r="F31" t="n">
-        <v>1467.683509</v>
+        <v>1468.492633</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>267.6851899999999</v>
+        <v>268.494314</v>
       </c>
       <c r="J31" t="n">
-        <v>22.31</v>
+        <v>22.37</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.544</v>
+        <v>2.5464</v>
       </c>
       <c r="F33" t="n">
-        <v>15518.4</v>
+        <v>15533.04</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3245.199999999999</v>
+        <v>3259.84</v>
       </c>
       <c r="J33" t="n">
-        <v>26.44</v>
+        <v>26.56</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0487</v>
+        <v>2.0498</v>
       </c>
       <c r="F34" t="n">
-        <v>39130.17000000001</v>
+        <v>39151.18</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>7958.970000000005</v>
+        <v>7979.98</v>
       </c>
       <c r="J34" t="n">
-        <v>25.53</v>
+        <v>25.6</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.9979</v>
+        <v>6.9792</v>
       </c>
       <c r="F35" t="n">
-        <v>42591.878602</v>
+        <v>42478.063296</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>9391.892977999996</v>
+        <v>9278.077671999999</v>
       </c>
       <c r="J35" t="n">
-        <v>28.29</v>
+        <v>27.95</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.9979</v>
+        <v>6.9792</v>
       </c>
       <c r="F36" t="n">
-        <v>14463.679594</v>
+        <v>14425.029312</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>3163.742601999998</v>
+        <v>3125.09232</v>
       </c>
       <c r="J36" t="n">
-        <v>28</v>
+        <v>27.66</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.9979</v>
+        <v>6.9792</v>
       </c>
       <c r="F37" t="n">
-        <v>104968.5</v>
+        <v>104688</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>21673.5</v>
+        <v>21393</v>
       </c>
       <c r="J37" t="n">
-        <v>26.02</v>
+        <v>25.68</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.9937</v>
+        <v>2.9986</v>
       </c>
       <c r="F38" t="n">
-        <v>21774.407517</v>
+        <v>21810.047226</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>5974.378973999999</v>
+        <v>6010.018683000002</v>
       </c>
       <c r="J38" t="n">
-        <v>37.81</v>
+        <v>38.04</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9937</v>
+        <v>2.9986</v>
       </c>
       <c r="F39" t="n">
-        <v>31218.034167</v>
+        <v>31269.130926</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>8218.235871000001</v>
+        <v>8269.332630000001</v>
       </c>
       <c r="J39" t="n">
-        <v>35.73</v>
+        <v>35.95</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.3765</v>
+        <v>2.3844</v>
       </c>
       <c r="F40" t="n">
-        <v>15922.55</v>
+        <v>15975.48</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>5470.550000000001</v>
+        <v>5523.48</v>
       </c>
       <c r="J40" t="n">
-        <v>52.34</v>
+        <v>52.85</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.1</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>8100</v>
+        <v>8119.999999999999</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>991</v>
+        <v>1010.999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>13.94</v>
+        <v>14.22</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>6.83</v>
+        <v>6.88</v>
       </c>
       <c r="F42" t="n">
-        <v>7513</v>
+        <v>7568</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>928.3999999999996</v>
+        <v>983.3999999999996</v>
       </c>
       <c r="J42" t="n">
-        <v>14.1</v>
+        <v>14.93</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>40.6</v>
+        <v>40.67</v>
       </c>
       <c r="F43" t="n">
-        <v>60900</v>
+        <v>61005</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-3555</v>
+        <v>-3450</v>
       </c>
       <c r="J43" t="n">
-        <v>-5.52</v>
+        <v>-5.35</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.827</v>
+        <v>2.814</v>
       </c>
       <c r="F2" t="n">
-        <v>2091.10363</v>
+        <v>2081.48766</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>220.8714340000001</v>
+        <v>211.2554640000003</v>
       </c>
       <c r="J2" t="n">
-        <v>11.81</v>
+        <v>11.3</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8662</v>
+        <v>2.8036</v>
       </c>
       <c r="F3" t="n">
-        <v>929.565984</v>
+        <v>909.2635519999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-70.37744000000009</v>
+        <v>-90.67987200000016</v>
       </c>
       <c r="J3" t="n">
-        <v>-7.04</v>
+        <v>-9.07</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1932</v>
+        <v>1.1961</v>
       </c>
       <c r="F4" t="n">
-        <v>6801.24</v>
+        <v>6817.77</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1380.54</v>
+        <v>1397.07</v>
       </c>
       <c r="J4" t="n">
-        <v>25.47</v>
+        <v>25.77</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.915</v>
+        <v>1.921</v>
       </c>
       <c r="F5" t="n">
-        <v>2271.05595</v>
+        <v>2278.17153</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-128.9105909999998</v>
+        <v>-121.7950109999997</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.37</v>
+        <v>-5.07</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3166</v>
+        <v>1.2999</v>
       </c>
       <c r="F6" t="n">
-        <v>2234.652014</v>
+        <v>2206.307271</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-265.286427</v>
+        <v>-293.6311699999997</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.61</v>
+        <v>-11.75</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3166</v>
+        <v>1.2999</v>
       </c>
       <c r="F7" t="n">
-        <v>4731.99206</v>
+        <v>4671.97059</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-587.9947600000005</v>
+        <v>-648.0162300000002</v>
       </c>
       <c r="J7" t="n">
-        <v>-11.05</v>
+        <v>-12.18</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1917</v>
+        <v>2.1922</v>
       </c>
       <c r="F8" t="n">
-        <v>28272.93</v>
+        <v>28279.38</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8974.529999999999</v>
+        <v>8980.98</v>
       </c>
       <c r="J8" t="n">
-        <v>46.5</v>
+        <v>46.54</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1494</v>
+        <v>3.1374</v>
       </c>
       <c r="F9" t="n">
-        <v>953.669814</v>
+        <v>950.036094</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>204.729841</v>
+        <v>201.096121</v>
       </c>
       <c r="J9" t="n">
-        <v>27.34</v>
+        <v>26.85</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2543</v>
+        <v>2.2477</v>
       </c>
       <c r="F10" t="n">
-        <v>2345.441349</v>
+        <v>2338.574511</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>345.4227600000002</v>
+        <v>338.5559220000002</v>
       </c>
       <c r="J10" t="n">
-        <v>17.27</v>
+        <v>16.93</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7059</v>
+        <v>1.6997</v>
       </c>
       <c r="F11" t="n">
-        <v>7057.700656999999</v>
+        <v>7032.049830999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1078.575860999999</v>
+        <v>1052.925034999999</v>
       </c>
       <c r="J11" t="n">
-        <v>18.04</v>
+        <v>17.61</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7059</v>
+        <v>1.6997</v>
       </c>
       <c r="F12" t="n">
-        <v>10259.402013</v>
+        <v>10222.114779</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1159.512696</v>
+        <v>1122.225462</v>
       </c>
       <c r="J12" t="n">
-        <v>12.74</v>
+        <v>12.33</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4605</v>
+        <v>2.4506</v>
       </c>
       <c r="F15" t="n">
-        <v>22882.65</v>
+        <v>22790.58</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3436.350000000002</v>
+        <v>3344.280000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>17.67</v>
+        <v>17.2</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.35</v>
+        <v>28.5</v>
       </c>
       <c r="F16" t="n">
-        <v>14175</v>
+        <v>14250</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>360</v>
+        <v>435</v>
       </c>
       <c r="J16" t="n">
-        <v>2.61</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>8.890000000000001</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
-        <v>17780</v>
+        <v>18000</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="J17" t="n">
-        <v>0.11</v>
+        <v>1.35</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0375</v>
+        <v>1.0385</v>
       </c>
       <c r="F18" t="n">
-        <v>4075.497125</v>
+        <v>4079.425315</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-230.9775719999993</v>
+        <v>-227.0493819999997</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.36</v>
+        <v>-5.27</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.532</v>
+        <v>1.5293</v>
       </c>
       <c r="F19" t="n">
-        <v>13328.4</v>
+        <v>13304.91</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-130.5</v>
+        <v>-153.989999999998</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.97</v>
+        <v>-1.14</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1483</v>
+        <v>1.146</v>
       </c>
       <c r="F20" t="n">
-        <v>9101.265038</v>
+        <v>9083.035559999998</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-898.7925240000004</v>
+        <v>-917.0220020000015</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.99</v>
+        <v>-9.17</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1807</v>
+        <v>1.1797</v>
       </c>
       <c r="F21" t="n">
-        <v>13341.91</v>
+        <v>13330.61</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>708.510000000002</v>
+        <v>697.2099999999991</v>
       </c>
       <c r="J21" t="n">
-        <v>5.61</v>
+        <v>5.52</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7997</v>
+        <v>1.7861</v>
       </c>
       <c r="F22" t="n">
-        <v>960.8418330000001</v>
+        <v>953.580929</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>231.7082600000001</v>
+        <v>224.447356</v>
       </c>
       <c r="J22" t="n">
-        <v>31.78</v>
+        <v>30.78</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7997</v>
+        <v>1.7861</v>
       </c>
       <c r="F23" t="n">
-        <v>23255.255478</v>
+        <v>23079.519814</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>4054.842011999997</v>
+        <v>3879.106347999998</v>
       </c>
       <c r="J23" t="n">
-        <v>21.12</v>
+        <v>20.2</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6166</v>
+        <v>1.6049</v>
       </c>
       <c r="F24" t="n">
-        <v>1057.773712</v>
+        <v>1050.118168</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>257.8020800000002</v>
+        <v>250.146536</v>
       </c>
       <c r="J24" t="n">
-        <v>32.23</v>
+        <v>31.27</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.4652</v>
+        <v>6.4142</v>
       </c>
       <c r="F26" t="n">
-        <v>2685.256168</v>
+        <v>2664.073828</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>585.2555939999997</v>
+        <v>564.0732539999999</v>
       </c>
       <c r="J26" t="n">
-        <v>27.87</v>
+        <v>26.86</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0909</v>
+        <v>2.0748</v>
       </c>
       <c r="F28" t="n">
-        <v>8068.36492</v>
+        <v>8006.238240000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1768.48804</v>
+        <v>1706.361360000002</v>
       </c>
       <c r="J28" t="n">
-        <v>28.07</v>
+        <v>27.09</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0909</v>
+        <v>2.0748</v>
       </c>
       <c r="F29" t="n">
-        <v>18210.254461</v>
+        <v>18070.034892</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>3210.244294</v>
+        <v>3070.024725000003</v>
       </c>
       <c r="J29" t="n">
-        <v>21.4</v>
+        <v>20.47</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1779</v>
+        <v>2.1614</v>
       </c>
       <c r="F30" t="n">
-        <v>11451.594211</v>
+        <v>11364.835726</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2571.206010000002</v>
+        <v>2484.447525000001</v>
       </c>
       <c r="J30" t="n">
-        <v>28.95</v>
+        <v>27.98</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1779</v>
+        <v>2.1614</v>
       </c>
       <c r="F31" t="n">
-        <v>1468.492633</v>
+        <v>1457.367178</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>268.494314</v>
+        <v>257.3688589999999</v>
       </c>
       <c r="J31" t="n">
-        <v>22.37</v>
+        <v>21.45</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.5464</v>
+        <v>2.53</v>
       </c>
       <c r="F33" t="n">
-        <v>15533.04</v>
+        <v>15433</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3259.84</v>
+        <v>3159.799999999997</v>
       </c>
       <c r="J33" t="n">
-        <v>26.56</v>
+        <v>25.75</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0498</v>
+        <v>2.0335</v>
       </c>
       <c r="F34" t="n">
-        <v>39151.18</v>
+        <v>38839.85</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>7979.98</v>
+        <v>7668.649999999998</v>
       </c>
       <c r="J34" t="n">
-        <v>25.6</v>
+        <v>24.6</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.9792</v>
+        <v>6.9863</v>
       </c>
       <c r="F35" t="n">
-        <v>42478.063296</v>
+        <v>42521.276594</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>9278.077671999999</v>
+        <v>9321.290970000002</v>
       </c>
       <c r="J35" t="n">
-        <v>27.95</v>
+        <v>28.08</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.9792</v>
+        <v>6.9863</v>
       </c>
       <c r="F36" t="n">
-        <v>14425.029312</v>
+        <v>14439.704018</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>3125.09232</v>
+        <v>3139.767026</v>
       </c>
       <c r="J36" t="n">
-        <v>27.66</v>
+        <v>27.79</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.9792</v>
+        <v>6.9863</v>
       </c>
       <c r="F37" t="n">
-        <v>104688</v>
+        <v>104794.5</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>21393</v>
+        <v>21499.5</v>
       </c>
       <c r="J37" t="n">
-        <v>25.68</v>
+        <v>25.81</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.9986</v>
+        <v>2.9753</v>
       </c>
       <c r="F38" t="n">
-        <v>21810.047226</v>
+        <v>21640.576773</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>6010.018683000002</v>
+        <v>5840.548229999997</v>
       </c>
       <c r="J38" t="n">
-        <v>38.04</v>
+        <v>36.97</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9986</v>
+        <v>2.9753</v>
       </c>
       <c r="F39" t="n">
-        <v>31269.130926</v>
+        <v>31026.160623</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>8269.332630000001</v>
+        <v>8026.362326999995</v>
       </c>
       <c r="J39" t="n">
-        <v>35.95</v>
+        <v>34.9</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.3844</v>
+        <v>2.369</v>
       </c>
       <c r="F40" t="n">
-        <v>15975.48</v>
+        <v>15872.3</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>5523.48</v>
+        <v>5420.300000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>52.85</v>
+        <v>51.86</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.119999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="F41" t="n">
-        <v>8119.999999999999</v>
+        <v>8160</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1010.999999999999</v>
+        <v>1051</v>
       </c>
       <c r="J41" t="n">
-        <v>14.22</v>
+        <v>14.78</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>40.67</v>
+        <v>40.49</v>
       </c>
       <c r="F43" t="n">
-        <v>61005</v>
+        <v>60735</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-3450</v>
+        <v>-3720</v>
       </c>
       <c r="J43" t="n">
-        <v>-5.35</v>
+        <v>-5.77</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.814</v>
+        <v>2.8436</v>
       </c>
       <c r="F2" t="n">
-        <v>2081.48766</v>
+        <v>2103.382484</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>211.2554640000003</v>
+        <v>233.1502880000003</v>
       </c>
       <c r="J2" t="n">
-        <v>11.3</v>
+        <v>12.47</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8036</v>
+        <v>2.8074</v>
       </c>
       <c r="F3" t="n">
-        <v>909.2635519999999</v>
+        <v>910.4959679999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-90.67987200000016</v>
+        <v>-89.4474560000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-9.07</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1961</v>
+        <v>1.1986</v>
       </c>
       <c r="F4" t="n">
-        <v>6817.77</v>
+        <v>6832.02</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1397.07</v>
+        <v>1411.320000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>25.77</v>
+        <v>26.04</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.921</v>
+        <v>1.9206</v>
       </c>
       <c r="F5" t="n">
-        <v>2278.17153</v>
+        <v>2277.697158</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-121.7950109999997</v>
+        <v>-122.2693829999994</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.07</v>
+        <v>-5.09</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2999</v>
+        <v>1.2953</v>
       </c>
       <c r="F6" t="n">
-        <v>2206.307271</v>
+        <v>2198.499737</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-293.6311699999997</v>
+        <v>-301.4387040000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.75</v>
+        <v>-12.06</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2999</v>
+        <v>1.2953</v>
       </c>
       <c r="F7" t="n">
-        <v>4671.97059</v>
+        <v>4655.43773</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-648.0162300000002</v>
+        <v>-664.5490900000004</v>
       </c>
       <c r="J7" t="n">
-        <v>-12.18</v>
+        <v>-12.49</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1922</v>
+        <v>2.2463</v>
       </c>
       <c r="F8" t="n">
-        <v>28279.38</v>
+        <v>28977.27</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8980.98</v>
+        <v>9678.870000000003</v>
       </c>
       <c r="J8" t="n">
-        <v>46.54</v>
+        <v>50.15</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1374</v>
+        <v>3.1328</v>
       </c>
       <c r="F9" t="n">
-        <v>950.036094</v>
+        <v>948.6431680000001</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>201.096121</v>
+        <v>199.7031950000001</v>
       </c>
       <c r="J9" t="n">
-        <v>26.85</v>
+        <v>26.66</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2477</v>
+        <v>2.2444</v>
       </c>
       <c r="F10" t="n">
-        <v>2338.574511</v>
+        <v>2335.141092</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>338.5559220000002</v>
+        <v>335.1225030000003</v>
       </c>
       <c r="J10" t="n">
-        <v>16.93</v>
+        <v>16.76</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6997</v>
+        <v>1.6974</v>
       </c>
       <c r="F11" t="n">
-        <v>7032.049830999999</v>
+        <v>7022.534201999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1052.925034999999</v>
+        <v>1043.409405999999</v>
       </c>
       <c r="J11" t="n">
-        <v>17.61</v>
+        <v>17.45</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6997</v>
+        <v>1.6974</v>
       </c>
       <c r="F12" t="n">
-        <v>10222.114779</v>
+        <v>10208.282418</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1122.225462</v>
+        <v>1108.393101</v>
       </c>
       <c r="J12" t="n">
-        <v>12.33</v>
+        <v>12.18</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4506</v>
+        <v>2.4469</v>
       </c>
       <c r="F15" t="n">
-        <v>22790.58</v>
+        <v>22756.17</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3344.280000000002</v>
+        <v>3309.869999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>17.2</v>
+        <v>17.02</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.5</v>
+        <v>28.39</v>
       </c>
       <c r="F16" t="n">
-        <v>14250</v>
+        <v>14195</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>435</v>
+        <v>380</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>18000</v>
+        <v>18080</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>240</v>
+        <v>320</v>
       </c>
       <c r="J17" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0385</v>
+        <v>1.0491</v>
       </c>
       <c r="F18" t="n">
-        <v>4079.425315</v>
+        <v>4121.064128999999</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-227.0493819999997</v>
+        <v>-185.4105680000002</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.27</v>
+        <v>-4.31</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5293</v>
+        <v>1.5478</v>
       </c>
       <c r="F19" t="n">
-        <v>13304.91</v>
+        <v>13465.86</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-153.989999999998</v>
+        <v>6.960000000000946</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.14</v>
+        <v>0.05</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.146</v>
+        <v>1.1534</v>
       </c>
       <c r="F20" t="n">
-        <v>9083.035559999998</v>
+        <v>9141.686924</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-917.0220020000015</v>
+        <v>-858.3706380000003</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.17</v>
+        <v>-8.58</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1797</v>
+        <v>1.1973</v>
       </c>
       <c r="F21" t="n">
-        <v>13330.61</v>
+        <v>13529.49</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>697.2099999999991</v>
+        <v>896.0900000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>5.52</v>
+        <v>7.09</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7861</v>
+        <v>1.7899</v>
       </c>
       <c r="F22" t="n">
-        <v>953.580929</v>
+        <v>955.6097109999999</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>224.447356</v>
+        <v>226.476138</v>
       </c>
       <c r="J22" t="n">
-        <v>30.78</v>
+        <v>31.06</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7861</v>
+        <v>1.7899</v>
       </c>
       <c r="F23" t="n">
-        <v>23079.519814</v>
+        <v>23128.622426</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3879.106347999998</v>
+        <v>3928.20896</v>
       </c>
       <c r="J23" t="n">
-        <v>20.2</v>
+        <v>20.46</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6049</v>
+        <v>1.6075</v>
       </c>
       <c r="F24" t="n">
-        <v>1050.118168</v>
+        <v>1051.8194</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>250.146536</v>
+        <v>251.8477680000001</v>
       </c>
       <c r="J24" t="n">
-        <v>31.27</v>
+        <v>31.48</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.4142</v>
+        <v>6.4259</v>
       </c>
       <c r="F26" t="n">
-        <v>2664.073828</v>
+        <v>2668.933306</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>564.0732539999999</v>
+        <v>568.9327319999998</v>
       </c>
       <c r="J26" t="n">
-        <v>26.86</v>
+        <v>27.09</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0748</v>
+        <v>2.0792</v>
       </c>
       <c r="F28" t="n">
-        <v>8006.238240000001</v>
+        <v>8023.216960000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1706.361360000002</v>
+        <v>1723.340080000001</v>
       </c>
       <c r="J28" t="n">
-        <v>27.09</v>
+        <v>27.36</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0748</v>
+        <v>2.0792</v>
       </c>
       <c r="F29" t="n">
-        <v>18070.034892</v>
+        <v>18108.355768</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>3070.024725000003</v>
+        <v>3108.345601000005</v>
       </c>
       <c r="J29" t="n">
-        <v>20.47</v>
+        <v>20.72</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1614</v>
+        <v>2.1659</v>
       </c>
       <c r="F30" t="n">
-        <v>11364.835726</v>
+        <v>11388.497131</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2484.447525000001</v>
+        <v>2508.108930000002</v>
       </c>
       <c r="J30" t="n">
-        <v>27.98</v>
+        <v>28.24</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1614</v>
+        <v>2.1659</v>
       </c>
       <c r="F31" t="n">
-        <v>1457.367178</v>
+        <v>1460.401393</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>257.3688589999999</v>
+        <v>260.4030740000001</v>
       </c>
       <c r="J31" t="n">
-        <v>21.45</v>
+        <v>21.7</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.53</v>
+        <v>2.5314</v>
       </c>
       <c r="F33" t="n">
-        <v>15433</v>
+        <v>15441.54</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3159.799999999997</v>
+        <v>3168.34</v>
       </c>
       <c r="J33" t="n">
-        <v>25.75</v>
+        <v>25.82</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0335</v>
+        <v>2.0379</v>
       </c>
       <c r="F34" t="n">
-        <v>38839.85</v>
+        <v>38923.89</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>7668.649999999998</v>
+        <v>7752.689999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>24.6</v>
+        <v>24.87</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.9863</v>
+        <v>6.9694</v>
       </c>
       <c r="F35" t="n">
-        <v>42521.276594</v>
+        <v>42418.416772</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>9321.290970000002</v>
+        <v>9218.431148000003</v>
       </c>
       <c r="J35" t="n">
-        <v>28.08</v>
+        <v>27.77</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.9863</v>
+        <v>6.9694</v>
       </c>
       <c r="F36" t="n">
-        <v>14439.704018</v>
+        <v>14404.774084</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>3139.767026</v>
+        <v>3104.837092</v>
       </c>
       <c r="J36" t="n">
-        <v>27.79</v>
+        <v>27.48</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.9863</v>
+        <v>6.9694</v>
       </c>
       <c r="F37" t="n">
-        <v>104794.5</v>
+        <v>104541</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>21499.5</v>
+        <v>21246</v>
       </c>
       <c r="J37" t="n">
-        <v>25.81</v>
+        <v>25.51</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.9753</v>
+        <v>2.9758</v>
       </c>
       <c r="F38" t="n">
-        <v>21640.576773</v>
+        <v>21644.213478</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>5840.548229999997</v>
+        <v>5844.184934999997</v>
       </c>
       <c r="J38" t="n">
-        <v>36.97</v>
+        <v>36.99</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9753</v>
+        <v>2.9758</v>
       </c>
       <c r="F39" t="n">
-        <v>31026.160623</v>
+        <v>31031.374578</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>8026.362326999995</v>
+        <v>8031.576281999998</v>
       </c>
       <c r="J39" t="n">
-        <v>34.9</v>
+        <v>34.92</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.369</v>
+        <v>2.3721</v>
       </c>
       <c r="F40" t="n">
-        <v>15872.3</v>
+        <v>15893.07</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>5420.300000000001</v>
+        <v>5441.070000000002</v>
       </c>
       <c r="J40" t="n">
-        <v>51.86</v>
+        <v>52.06</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.16</v>
+        <v>8.17</v>
       </c>
       <c r="F41" t="n">
-        <v>8160</v>
+        <v>8170</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1051</v>
+        <v>1061</v>
       </c>
       <c r="J41" t="n">
-        <v>14.78</v>
+        <v>14.92</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>6.88</v>
+        <v>6.93</v>
       </c>
       <c r="F42" t="n">
-        <v>7568</v>
+        <v>7623</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>983.3999999999996</v>
+        <v>1038.4</v>
       </c>
       <c r="J42" t="n">
-        <v>14.93</v>
+        <v>15.77</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>40.49</v>
+        <v>40.59</v>
       </c>
       <c r="F43" t="n">
-        <v>60735</v>
+        <v>60885.00000000001</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-3720</v>
+        <v>-3569.999999999993</v>
       </c>
       <c r="J43" t="n">
-        <v>-5.77</v>
+        <v>-5.54</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8436</v>
+        <v>2.7966</v>
       </c>
       <c r="F2" t="n">
-        <v>2103.382484</v>
+        <v>2068.617054</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>233.1502880000003</v>
+        <v>198.3848580000003</v>
       </c>
       <c r="J2" t="n">
-        <v>12.47</v>
+        <v>10.61</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8074</v>
+        <v>2.828</v>
       </c>
       <c r="F3" t="n">
-        <v>910.4959679999999</v>
+        <v>917.1769599999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-89.4474560000001</v>
+        <v>-82.76646400000016</v>
       </c>
       <c r="J3" t="n">
-        <v>-8.949999999999999</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1986</v>
+        <v>1.1799</v>
       </c>
       <c r="F4" t="n">
-        <v>6832.02</v>
+        <v>6725.429999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1411.320000000001</v>
+        <v>1304.73</v>
       </c>
       <c r="J4" t="n">
-        <v>26.04</v>
+        <v>24.07</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9206</v>
+        <v>1.8999</v>
       </c>
       <c r="F5" t="n">
-        <v>2277.697158</v>
+        <v>2253.148407</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-122.2693829999994</v>
+        <v>-146.8181339999996</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.09</v>
+        <v>-6.12</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2953</v>
+        <v>1.2959</v>
       </c>
       <c r="F6" t="n">
-        <v>2198.499737</v>
+        <v>2199.518111</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-301.4387040000001</v>
+        <v>-300.4203299999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.06</v>
+        <v>-12.02</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2953</v>
+        <v>1.2959</v>
       </c>
       <c r="F7" t="n">
-        <v>4655.43773</v>
+        <v>4657.59419</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-664.5490900000004</v>
+        <v>-662.3926300000003</v>
       </c>
       <c r="J7" t="n">
-        <v>-12.49</v>
+        <v>-12.45</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2463</v>
+        <v>2.301</v>
       </c>
       <c r="F8" t="n">
-        <v>28977.27</v>
+        <v>29682.9</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>9678.870000000003</v>
+        <v>10384.5</v>
       </c>
       <c r="J8" t="n">
-        <v>50.15</v>
+        <v>53.81</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1328</v>
+        <v>3.1229</v>
       </c>
       <c r="F9" t="n">
-        <v>948.6431680000001</v>
+        <v>945.645349</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>199.7031950000001</v>
+        <v>196.705376</v>
       </c>
       <c r="J9" t="n">
-        <v>26.66</v>
+        <v>26.26</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2444</v>
+        <v>2.2406</v>
       </c>
       <c r="F10" t="n">
-        <v>2335.141092</v>
+        <v>2331.187458</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>335.1225030000003</v>
+        <v>331.1688690000003</v>
       </c>
       <c r="J10" t="n">
-        <v>16.76</v>
+        <v>16.56</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6974</v>
+        <v>1.6923</v>
       </c>
       <c r="F11" t="n">
-        <v>7022.534201999999</v>
+        <v>7001.434328999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1043.409405999999</v>
+        <v>1022.309532999999</v>
       </c>
       <c r="J11" t="n">
-        <v>17.45</v>
+        <v>17.1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6974</v>
+        <v>1.6923</v>
       </c>
       <c r="F12" t="n">
-        <v>10208.282418</v>
+        <v>10177.610661</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1108.393101</v>
+        <v>1077.721344</v>
       </c>
       <c r="J12" t="n">
-        <v>12.18</v>
+        <v>11.84</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4469</v>
+        <v>2.4389</v>
       </c>
       <c r="F15" t="n">
-        <v>22756.17</v>
+        <v>22681.77</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3309.869999999999</v>
+        <v>3235.469999999998</v>
       </c>
       <c r="J15" t="n">
-        <v>17.02</v>
+        <v>16.64</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.39</v>
+        <v>28.5</v>
       </c>
       <c r="F16" t="n">
-        <v>14195</v>
+        <v>14250</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>380</v>
+        <v>435</v>
       </c>
       <c r="J16" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.039999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="F17" t="n">
-        <v>18080</v>
+        <v>18160</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0491</v>
+        <v>1.0603</v>
       </c>
       <c r="F18" t="n">
-        <v>4121.064128999999</v>
+        <v>4165.059857</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-185.4105680000002</v>
+        <v>-141.4148399999995</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.31</v>
+        <v>-3.28</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5478</v>
+        <v>1.5653</v>
       </c>
       <c r="F19" t="n">
-        <v>13465.86</v>
+        <v>13618.11</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>6.960000000000946</v>
+        <v>159.2099999999991</v>
       </c>
       <c r="J19" t="n">
-        <v>0.05</v>
+        <v>1.18</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1534</v>
+        <v>1.1498</v>
       </c>
       <c r="F20" t="n">
-        <v>9141.686924</v>
+        <v>9113.153827999999</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-858.3706380000003</v>
+        <v>-886.9037340000014</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.58</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1973</v>
+        <v>1.2109</v>
       </c>
       <c r="F21" t="n">
-        <v>13529.49</v>
+        <v>13683.17</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>896.0900000000001</v>
+        <v>1049.770000000002</v>
       </c>
       <c r="J21" t="n">
-        <v>7.09</v>
+        <v>8.31</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7899</v>
+        <v>1.7922</v>
       </c>
       <c r="F22" t="n">
-        <v>955.6097109999999</v>
+        <v>956.837658</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>226.476138</v>
+        <v>227.7040850000001</v>
       </c>
       <c r="J22" t="n">
-        <v>31.06</v>
+        <v>31.23</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7899</v>
+        <v>1.7922</v>
       </c>
       <c r="F23" t="n">
-        <v>23128.622426</v>
+        <v>23158.342428</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3928.20896</v>
+        <v>3957.928961999998</v>
       </c>
       <c r="J23" t="n">
-        <v>20.46</v>
+        <v>20.61</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6075</v>
+        <v>1.6095</v>
       </c>
       <c r="F24" t="n">
-        <v>1051.8194</v>
+        <v>1053.12804</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>251.8477680000001</v>
+        <v>253.1564080000001</v>
       </c>
       <c r="J24" t="n">
-        <v>31.48</v>
+        <v>31.65</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.4259</v>
+        <v>6.4356</v>
       </c>
       <c r="F26" t="n">
-        <v>2668.933306</v>
+        <v>2672.962104</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>568.9327319999998</v>
+        <v>572.9615299999996</v>
       </c>
       <c r="J26" t="n">
-        <v>27.09</v>
+        <v>27.28</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0792</v>
+        <v>2.082</v>
       </c>
       <c r="F28" t="n">
-        <v>8023.216960000001</v>
+        <v>8034.0216</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1723.340080000001</v>
+        <v>1734.14472</v>
       </c>
       <c r="J28" t="n">
-        <v>27.36</v>
+        <v>27.53</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0792</v>
+        <v>2.082</v>
       </c>
       <c r="F29" t="n">
-        <v>18108.355768</v>
+        <v>18132.74178</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>3108.345601000005</v>
+        <v>3132.731613</v>
       </c>
       <c r="J29" t="n">
-        <v>20.72</v>
+        <v>20.88</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1659</v>
+        <v>2.1695</v>
       </c>
       <c r="F30" t="n">
-        <v>11388.497131</v>
+        <v>11407.426255</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2508.108930000002</v>
+        <v>2527.038054000002</v>
       </c>
       <c r="J30" t="n">
-        <v>28.24</v>
+        <v>28.46</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1659</v>
+        <v>2.1695</v>
       </c>
       <c r="F31" t="n">
-        <v>1460.401393</v>
+        <v>1462.828765</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>260.4030740000001</v>
+        <v>262.8304460000002</v>
       </c>
       <c r="J31" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.5314</v>
+        <v>2.5375</v>
       </c>
       <c r="F33" t="n">
-        <v>15441.54</v>
+        <v>15478.75</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3168.34</v>
+        <v>3205.549999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>25.82</v>
+        <v>26.12</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0379</v>
+        <v>2.0409</v>
       </c>
       <c r="F34" t="n">
-        <v>38923.89</v>
+        <v>38981.19</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>7752.689999999999</v>
+        <v>7809.990000000002</v>
       </c>
       <c r="J34" t="n">
-        <v>24.87</v>
+        <v>25.06</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.9694</v>
+        <v>7.0028</v>
       </c>
       <c r="F35" t="n">
-        <v>42418.416772</v>
+        <v>42621.701864</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>9218.431148000003</v>
+        <v>9421.716240000002</v>
       </c>
       <c r="J35" t="n">
-        <v>27.77</v>
+        <v>28.38</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.9694</v>
+        <v>7.0028</v>
       </c>
       <c r="F36" t="n">
-        <v>14404.774084</v>
+        <v>14473.807208</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>3104.837092</v>
+        <v>3173.870215999999</v>
       </c>
       <c r="J36" t="n">
-        <v>27.48</v>
+        <v>28.09</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.9694</v>
+        <v>7.0028</v>
       </c>
       <c r="F37" t="n">
-        <v>104541</v>
+        <v>105042</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>21246</v>
+        <v>21747</v>
       </c>
       <c r="J37" t="n">
-        <v>25.51</v>
+        <v>26.11</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.9758</v>
+        <v>2.9853</v>
       </c>
       <c r="F38" t="n">
-        <v>21644.213478</v>
+        <v>21713.310873</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>5844.184934999997</v>
+        <v>5913.282329999998</v>
       </c>
       <c r="J38" t="n">
-        <v>36.99</v>
+        <v>37.43</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9758</v>
+        <v>2.9853</v>
       </c>
       <c r="F39" t="n">
-        <v>31031.374578</v>
+        <v>31130.439723</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>8031.576281999998</v>
+        <v>8130.641426999999</v>
       </c>
       <c r="J39" t="n">
-        <v>34.92</v>
+        <v>35.35</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.3721</v>
+        <v>2.3804</v>
       </c>
       <c r="F40" t="n">
-        <v>15893.07</v>
+        <v>15948.68</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>5441.070000000002</v>
+        <v>5496.679999999998</v>
       </c>
       <c r="J40" t="n">
-        <v>52.06</v>
+        <v>52.59</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.17</v>
+        <v>8.26</v>
       </c>
       <c r="F41" t="n">
-        <v>8170</v>
+        <v>8260</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1061</v>
+        <v>1151</v>
       </c>
       <c r="J41" t="n">
-        <v>14.92</v>
+        <v>16.19</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>6.93</v>
+        <v>6.96</v>
       </c>
       <c r="F42" t="n">
-        <v>7623</v>
+        <v>7656</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1038.4</v>
+        <v>1071.4</v>
       </c>
       <c r="J42" t="n">
-        <v>15.77</v>
+        <v>16.27</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>40.59</v>
+        <v>41.26</v>
       </c>
       <c r="F43" t="n">
-        <v>60885.00000000001</v>
+        <v>61890</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-3569.999999999993</v>
+        <v>-2565</v>
       </c>
       <c r="J43" t="n">
-        <v>-5.54</v>
+        <v>-3.98</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7966</v>
+        <v>2.8335</v>
       </c>
       <c r="F2" t="n">
-        <v>2068.617054</v>
+        <v>2095.911615</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>198.3848580000003</v>
+        <v>225.6794190000001</v>
       </c>
       <c r="J2" t="n">
-        <v>10.61</v>
+        <v>12.07</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.828</v>
+        <v>2.7191</v>
       </c>
       <c r="F3" t="n">
-        <v>917.1769599999999</v>
+        <v>881.858512</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-82.76646400000016</v>
+        <v>-118.084912</v>
       </c>
       <c r="J3" t="n">
-        <v>-8.279999999999999</v>
+        <v>-11.81</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1799</v>
+        <v>1.1821</v>
       </c>
       <c r="F4" t="n">
-        <v>6725.429999999999</v>
+        <v>6737.969999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1304.73</v>
+        <v>1317.27</v>
       </c>
       <c r="J4" t="n">
-        <v>24.07</v>
+        <v>24.3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8999</v>
+        <v>1.8535</v>
       </c>
       <c r="F5" t="n">
-        <v>2253.148407</v>
+        <v>2198.121255</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-146.8181339999996</v>
+        <v>-201.8452859999998</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.12</v>
+        <v>-8.41</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2959</v>
+        <v>1.2657</v>
       </c>
       <c r="F6" t="n">
-        <v>2199.518111</v>
+        <v>2148.259953</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-300.4203299999999</v>
+        <v>-351.6784879999996</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.02</v>
+        <v>-14.07</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2959</v>
+        <v>1.2657</v>
       </c>
       <c r="F7" t="n">
-        <v>4657.59419</v>
+        <v>4549.05237</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-662.3926300000003</v>
+        <v>-770.9344499999997</v>
       </c>
       <c r="J7" t="n">
-        <v>-12.45</v>
+        <v>-14.49</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.301</v>
+        <v>2.2966</v>
       </c>
       <c r="F8" t="n">
-        <v>29682.9</v>
+        <v>29626.14</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>10384.5</v>
+        <v>10327.74</v>
       </c>
       <c r="J8" t="n">
-        <v>53.81</v>
+        <v>53.52</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1229</v>
+        <v>3.1679</v>
       </c>
       <c r="F9" t="n">
-        <v>945.645349</v>
+        <v>959.271799</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>196.705376</v>
+        <v>210.331826</v>
       </c>
       <c r="J9" t="n">
-        <v>26.26</v>
+        <v>28.08</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2406</v>
+        <v>2.2691</v>
       </c>
       <c r="F10" t="n">
-        <v>2331.187458</v>
+        <v>2360.839713</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>331.1688690000003</v>
+        <v>360.8211239999998</v>
       </c>
       <c r="J10" t="n">
-        <v>16.56</v>
+        <v>18.04</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6923</v>
+        <v>1.7165</v>
       </c>
       <c r="F11" t="n">
-        <v>7001.434328999999</v>
+        <v>7101.555294999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1022.309532999999</v>
+        <v>1122.430498999999</v>
       </c>
       <c r="J11" t="n">
-        <v>17.1</v>
+        <v>18.77</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6923</v>
+        <v>1.7165</v>
       </c>
       <c r="F12" t="n">
-        <v>10177.610661</v>
+        <v>10323.151155</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1077.721344</v>
+        <v>1223.261838</v>
       </c>
       <c r="J12" t="n">
-        <v>11.84</v>
+        <v>13.44</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4389</v>
+        <v>2.4762</v>
       </c>
       <c r="F15" t="n">
-        <v>22681.77</v>
+        <v>23028.66</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3235.469999999998</v>
+        <v>3582.360000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>16.64</v>
+        <v>18.42</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.5</v>
+        <v>28.98</v>
       </c>
       <c r="F16" t="n">
-        <v>14250</v>
+        <v>14490</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>435</v>
+        <v>675</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>4.89</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.08</v>
+        <v>9.16</v>
       </c>
       <c r="F17" t="n">
-        <v>18160</v>
+        <v>18320</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>400</v>
+        <v>560</v>
       </c>
       <c r="J17" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0603</v>
+        <v>1.0595</v>
       </c>
       <c r="F18" t="n">
-        <v>4165.059857</v>
+        <v>4161.917305000001</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-141.4148399999995</v>
+        <v>-144.5573919999988</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.28</v>
+        <v>-3.36</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5653</v>
+        <v>1.578</v>
       </c>
       <c r="F19" t="n">
-        <v>13618.11</v>
+        <v>13728.6</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>159.2099999999991</v>
+        <v>269.7000000000007</v>
       </c>
       <c r="J19" t="n">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1498</v>
+        <v>1.1619</v>
       </c>
       <c r="F20" t="n">
-        <v>9113.153827999999</v>
+        <v>9209.056734</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-886.9037340000014</v>
+        <v>-791.0008280000002</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.869999999999999</v>
+        <v>-7.91</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2109</v>
+        <v>1.2075</v>
       </c>
       <c r="F21" t="n">
-        <v>13683.17</v>
+        <v>13644.75</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1049.770000000002</v>
+        <v>1011.35</v>
       </c>
       <c r="J21" t="n">
-        <v>8.31</v>
+        <v>8.01</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7922</v>
+        <v>1.8102</v>
       </c>
       <c r="F22" t="n">
-        <v>956.837658</v>
+        <v>966.447678</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>227.7040850000001</v>
+        <v>237.314105</v>
       </c>
       <c r="J22" t="n">
-        <v>31.23</v>
+        <v>32.55</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7922</v>
+        <v>1.8102</v>
       </c>
       <c r="F23" t="n">
-        <v>23158.342428</v>
+        <v>23390.933748</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3957.928961999998</v>
+        <v>4190.520281999998</v>
       </c>
       <c r="J23" t="n">
-        <v>20.61</v>
+        <v>21.83</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6095</v>
+        <v>1.6249</v>
       </c>
       <c r="F24" t="n">
-        <v>1053.12804</v>
+        <v>1063.204568</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>253.1564080000001</v>
+        <v>263.2329360000001</v>
       </c>
       <c r="J24" t="n">
-        <v>31.65</v>
+        <v>32.91</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.4356</v>
+        <v>6.5009</v>
       </c>
       <c r="F26" t="n">
-        <v>2672.962104</v>
+        <v>2700.083806</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>572.9615299999996</v>
+        <v>600.0832319999995</v>
       </c>
       <c r="J26" t="n">
-        <v>27.28</v>
+        <v>28.58</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.082</v>
+        <v>2.103</v>
       </c>
       <c r="F28" t="n">
-        <v>8034.0216</v>
+        <v>8115.056400000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1734.14472</v>
+        <v>1815.179520000002</v>
       </c>
       <c r="J28" t="n">
-        <v>27.53</v>
+        <v>28.81</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.082</v>
+        <v>2.103</v>
       </c>
       <c r="F29" t="n">
-        <v>18132.74178</v>
+        <v>18315.63687</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>3132.731613</v>
+        <v>3315.626703000002</v>
       </c>
       <c r="J29" t="n">
-        <v>20.88</v>
+        <v>22.1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1695</v>
+        <v>2.1913</v>
       </c>
       <c r="F30" t="n">
-        <v>11407.426255</v>
+        <v>11522.052617</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2527.038054000002</v>
+        <v>2641.664416000001</v>
       </c>
       <c r="J30" t="n">
-        <v>28.46</v>
+        <v>29.75</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1695</v>
+        <v>2.1913</v>
       </c>
       <c r="F31" t="n">
-        <v>1462.828765</v>
+        <v>1477.527851</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>262.8304460000002</v>
+        <v>277.529532</v>
       </c>
       <c r="J31" t="n">
-        <v>21.9</v>
+        <v>23.13</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.5375</v>
+        <v>2.5631</v>
       </c>
       <c r="F33" t="n">
-        <v>15478.75</v>
+        <v>15634.91</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3205.549999999999</v>
+        <v>3361.709999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>26.12</v>
+        <v>27.39</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0409</v>
+        <v>2.0622</v>
       </c>
       <c r="F34" t="n">
-        <v>38981.19</v>
+        <v>39388.02</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>7809.990000000002</v>
+        <v>8216.819999999996</v>
       </c>
       <c r="J34" t="n">
-        <v>25.06</v>
+        <v>26.36</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>7.0028</v>
+        <v>7.0838</v>
       </c>
       <c r="F35" t="n">
-        <v>42621.701864</v>
+        <v>43114.698644</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>9421.716240000002</v>
+        <v>9914.713020000003</v>
       </c>
       <c r="J35" t="n">
-        <v>28.38</v>
+        <v>29.86</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>7.0028</v>
+        <v>7.0838</v>
       </c>
       <c r="F36" t="n">
-        <v>14473.807208</v>
+        <v>14641.222868</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>3173.870215999999</v>
+        <v>3341.285876</v>
       </c>
       <c r="J36" t="n">
-        <v>28.09</v>
+        <v>29.57</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>7.0028</v>
+        <v>7.0838</v>
       </c>
       <c r="F37" t="n">
-        <v>105042</v>
+        <v>106257</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>21747</v>
+        <v>22962</v>
       </c>
       <c r="J37" t="n">
-        <v>26.11</v>
+        <v>27.57</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.9853</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>21713.310873</v>
+        <v>21820.23</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>5913.282329999998</v>
+        <v>6020.201456999999</v>
       </c>
       <c r="J38" t="n">
-        <v>37.43</v>
+        <v>38.1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9853</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>31130.439723</v>
+        <v>31283.73</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>8130.641426999999</v>
+        <v>8283.931703999999</v>
       </c>
       <c r="J39" t="n">
-        <v>35.35</v>
+        <v>36.02</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.3804</v>
+        <v>2.393</v>
       </c>
       <c r="F40" t="n">
-        <v>15948.68</v>
+        <v>16033.1</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>5496.679999999998</v>
+        <v>5581.099999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>52.59</v>
+        <v>53.4</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.26</v>
+        <v>8.33</v>
       </c>
       <c r="F41" t="n">
-        <v>8260</v>
+        <v>8330</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1151</v>
+        <v>1221</v>
       </c>
       <c r="J41" t="n">
-        <v>16.19</v>
+        <v>17.18</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>6.96</v>
+        <v>7.04</v>
       </c>
       <c r="F42" t="n">
-        <v>7656</v>
+        <v>7744</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1071.4</v>
+        <v>1159.4</v>
       </c>
       <c r="J42" t="n">
-        <v>16.27</v>
+        <v>17.61</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>41.26</v>
+        <v>41.72</v>
       </c>
       <c r="F43" t="n">
-        <v>61890</v>
+        <v>62580</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-2565</v>
+        <v>-1875</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.98</v>
+        <v>-2.91</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8335</v>
+        <v>2.8307</v>
       </c>
       <c r="F2" t="n">
-        <v>2095.911615</v>
+        <v>2093.840483</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>225.6794190000001</v>
+        <v>223.6082870000005</v>
       </c>
       <c r="J2" t="n">
-        <v>12.07</v>
+        <v>11.96</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7191</v>
+        <v>2.7226</v>
       </c>
       <c r="F3" t="n">
-        <v>881.858512</v>
+        <v>882.9936319999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-118.084912</v>
+        <v>-116.9497920000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-11.81</v>
+        <v>-11.7</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1821</v>
+        <v>1.1682</v>
       </c>
       <c r="F4" t="n">
-        <v>6737.969999999999</v>
+        <v>6658.74</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1317.27</v>
+        <v>1238.04</v>
       </c>
       <c r="J4" t="n">
-        <v>24.3</v>
+        <v>22.84</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8535</v>
+        <v>1.871</v>
       </c>
       <c r="F5" t="n">
-        <v>2198.121255</v>
+        <v>2218.87503</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-201.8452859999998</v>
+        <v>-181.0915109999996</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.41</v>
+        <v>-7.55</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2657</v>
+        <v>1.2764</v>
       </c>
       <c r="F6" t="n">
-        <v>2148.259953</v>
+        <v>2166.420956</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-351.6784879999996</v>
+        <v>-333.5174849999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.07</v>
+        <v>-13.34</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2657</v>
+        <v>1.2764</v>
       </c>
       <c r="F7" t="n">
-        <v>4549.05237</v>
+        <v>4587.509239999999</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-770.9344499999997</v>
+        <v>-732.4775800000007</v>
       </c>
       <c r="J7" t="n">
-        <v>-14.49</v>
+        <v>-13.77</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2966</v>
+        <v>2.2932</v>
       </c>
       <c r="F8" t="n">
-        <v>29626.14</v>
+        <v>29582.28</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>10327.74</v>
+        <v>10283.88</v>
       </c>
       <c r="J8" t="n">
-        <v>53.52</v>
+        <v>53.29</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1679</v>
+        <v>3.1843</v>
       </c>
       <c r="F9" t="n">
-        <v>959.271799</v>
+        <v>964.237883</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>210.331826</v>
+        <v>215.29791</v>
       </c>
       <c r="J9" t="n">
-        <v>28.08</v>
+        <v>28.75</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2691</v>
+        <v>2.2799</v>
       </c>
       <c r="F10" t="n">
-        <v>2360.839713</v>
+        <v>2372.076357</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>360.8211239999998</v>
+        <v>372.0577680000004</v>
       </c>
       <c r="J10" t="n">
-        <v>18.04</v>
+        <v>18.6</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7165</v>
+        <v>1.7251</v>
       </c>
       <c r="F11" t="n">
-        <v>7101.555294999999</v>
+        <v>7137.135472999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1122.430498999999</v>
+        <v>1158.010676999999</v>
       </c>
       <c r="J11" t="n">
-        <v>18.77</v>
+        <v>19.37</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7165</v>
+        <v>1.7251</v>
       </c>
       <c r="F12" t="n">
-        <v>10323.151155</v>
+        <v>10374.872157</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1223.261838</v>
+        <v>1274.982840000001</v>
       </c>
       <c r="J12" t="n">
-        <v>13.44</v>
+        <v>14.01</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4762</v>
+        <v>2.4897</v>
       </c>
       <c r="F15" t="n">
-        <v>23028.66</v>
+        <v>23154.21</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3582.360000000001</v>
+        <v>3707.91</v>
       </c>
       <c r="J15" t="n">
-        <v>18.42</v>
+        <v>19.07</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>28.98</v>
+        <v>29</v>
       </c>
       <c r="F16" t="n">
-        <v>14490</v>
+        <v>14500</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="J16" t="n">
-        <v>4.89</v>
+        <v>4.96</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.16</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>18320</v>
+        <v>18220</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>560</v>
+        <v>460</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>2.59</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0595</v>
+        <v>1.0735</v>
       </c>
       <c r="F18" t="n">
-        <v>4161.917305000001</v>
+        <v>4216.911964999999</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-144.5573919999988</v>
+        <v>-89.56273200000032</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.36</v>
+        <v>-2.08</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.578</v>
+        <v>1.5829</v>
       </c>
       <c r="F19" t="n">
-        <v>13728.6</v>
+        <v>13771.23</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>269.7000000000007</v>
+        <v>312.3299999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1619</v>
+        <v>1.1644</v>
       </c>
       <c r="F20" t="n">
-        <v>9209.056734</v>
+        <v>9228.871384</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-791.0008280000002</v>
+        <v>-771.1861779999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.91</v>
+        <v>-7.71</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2075</v>
+        <v>1.2302</v>
       </c>
       <c r="F21" t="n">
-        <v>13644.75</v>
+        <v>13901.26</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1011.35</v>
+        <v>1267.860000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>8.01</v>
+        <v>10.04</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8102</v>
+        <v>1.8179</v>
       </c>
       <c r="F22" t="n">
-        <v>966.447678</v>
+        <v>970.558631</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>237.314105</v>
+        <v>241.425058</v>
       </c>
       <c r="J22" t="n">
-        <v>32.55</v>
+        <v>33.11</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8102</v>
+        <v>1.8179</v>
       </c>
       <c r="F23" t="n">
-        <v>23390.933748</v>
+        <v>23490.431146</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>4190.520281999998</v>
+        <v>4290.017679999997</v>
       </c>
       <c r="J23" t="n">
-        <v>21.83</v>
+        <v>22.34</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6249</v>
+        <v>1.6313</v>
       </c>
       <c r="F24" t="n">
-        <v>1063.204568</v>
+        <v>1067.392216</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>263.2329360000001</v>
+        <v>267.420584</v>
       </c>
       <c r="J24" t="n">
-        <v>32.91</v>
+        <v>33.43</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.5009</v>
+        <v>6.5274</v>
       </c>
       <c r="F26" t="n">
-        <v>2700.083806</v>
+        <v>2711.090316</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>600.0832319999995</v>
+        <v>611.0897419999997</v>
       </c>
       <c r="J26" t="n">
-        <v>28.58</v>
+        <v>29.1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.103</v>
+        <v>2.1116</v>
       </c>
       <c r="F28" t="n">
-        <v>8115.056400000001</v>
+        <v>8148.242080000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1815.179520000002</v>
+        <v>1848.365200000001</v>
       </c>
       <c r="J28" t="n">
-        <v>28.81</v>
+        <v>29.34</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.103</v>
+        <v>2.1116</v>
       </c>
       <c r="F29" t="n">
-        <v>18315.63687</v>
+        <v>18390.536764</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>3315.626703000002</v>
+        <v>3390.526597000004</v>
       </c>
       <c r="J29" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1913</v>
+        <v>2.1998</v>
       </c>
       <c r="F30" t="n">
-        <v>11522.052617</v>
+        <v>11566.746382</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2641.664416000001</v>
+        <v>2686.358181000001</v>
       </c>
       <c r="J30" t="n">
-        <v>29.75</v>
+        <v>30.25</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1913</v>
+        <v>2.1998</v>
       </c>
       <c r="F31" t="n">
-        <v>1477.527851</v>
+        <v>1483.259146</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>277.529532</v>
+        <v>283.2608270000001</v>
       </c>
       <c r="J31" t="n">
-        <v>23.13</v>
+        <v>23.61</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.5631</v>
+        <v>2.5725</v>
       </c>
       <c r="F33" t="n">
-        <v>15634.91</v>
+        <v>15692.25</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3361.709999999999</v>
+        <v>3419.049999999997</v>
       </c>
       <c r="J33" t="n">
-        <v>27.39</v>
+        <v>27.86</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0622</v>
+        <v>2.0715</v>
       </c>
       <c r="F34" t="n">
-        <v>39388.02</v>
+        <v>39565.65</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>8216.819999999996</v>
+        <v>8394.450000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>26.36</v>
+        <v>26.93</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>7.0838</v>
+        <v>7.1048</v>
       </c>
       <c r="F35" t="n">
-        <v>43114.698644</v>
+        <v>43242.512624</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>9914.713020000003</v>
+        <v>10042.527</v>
       </c>
       <c r="J35" t="n">
-        <v>29.86</v>
+        <v>30.25</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>7.0838</v>
+        <v>7.1048</v>
       </c>
       <c r="F36" t="n">
-        <v>14641.222868</v>
+        <v>14684.626928</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>3341.285876</v>
+        <v>3384.689936000001</v>
       </c>
       <c r="J36" t="n">
-        <v>29.57</v>
+        <v>29.95</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>7.0838</v>
+        <v>7.1048</v>
       </c>
       <c r="F37" t="n">
-        <v>106257</v>
+        <v>106572</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>22962</v>
+        <v>23277</v>
       </c>
       <c r="J37" t="n">
-        <v>27.57</v>
+        <v>27.95</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>2.9976</v>
       </c>
       <c r="F38" t="n">
-        <v>21820.23</v>
+        <v>21802.773816</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>6020.201456999999</v>
+        <v>6002.745272999997</v>
       </c>
       <c r="J38" t="n">
-        <v>38.1</v>
+        <v>37.99</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>2.9976</v>
       </c>
       <c r="F39" t="n">
-        <v>31283.73</v>
+        <v>31258.703016</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>8283.931703999999</v>
+        <v>8258.904719999999</v>
       </c>
       <c r="J39" t="n">
-        <v>36.02</v>
+        <v>35.91</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.393</v>
+        <v>2.3992</v>
       </c>
       <c r="F40" t="n">
-        <v>16033.1</v>
+        <v>16074.64</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>5581.099999999999</v>
+        <v>5622.639999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>53.4</v>
+        <v>53.79</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.33</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>8330</v>
+        <v>8220</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1221</v>
+        <v>1111</v>
       </c>
       <c r="J41" t="n">
-        <v>17.18</v>
+        <v>15.63</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7.04</v>
+        <v>6.98</v>
       </c>
       <c r="F42" t="n">
-        <v>7744</v>
+        <v>7678.000000000001</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1159.4</v>
+        <v>1093.400000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>17.61</v>
+        <v>16.61</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>41.72</v>
+        <v>41.56</v>
       </c>
       <c r="F43" t="n">
-        <v>62580</v>
+        <v>62340</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-1875</v>
+        <v>-2115</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.91</v>
+        <v>-3.28</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8307</v>
+        <v>2.8337</v>
       </c>
       <c r="F2" t="n">
-        <v>2093.840483</v>
+        <v>2096.059553</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>223.6082870000005</v>
+        <v>225.8273570000001</v>
       </c>
       <c r="J2" t="n">
-        <v>11.96</v>
+        <v>12.07</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7226</v>
+        <v>2.6948</v>
       </c>
       <c r="F3" t="n">
-        <v>882.9936319999999</v>
+        <v>873.977536</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-116.9497920000001</v>
+        <v>-125.9658880000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-11.7</v>
+        <v>-12.6</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1682</v>
+        <v>1.1656</v>
       </c>
       <c r="F4" t="n">
-        <v>6658.74</v>
+        <v>6643.92</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1238.04</v>
+        <v>1223.22</v>
       </c>
       <c r="J4" t="n">
-        <v>22.84</v>
+        <v>22.57</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.871</v>
+        <v>1.8822</v>
       </c>
       <c r="F5" t="n">
-        <v>2218.87503</v>
+        <v>2232.157446</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-181.0915109999996</v>
+        <v>-167.8090949999996</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.55</v>
+        <v>-6.99</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2764</v>
+        <v>1.286</v>
       </c>
       <c r="F6" t="n">
-        <v>2166.420956</v>
+        <v>2182.71494</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-333.5174849999999</v>
+        <v>-317.2235009999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.34</v>
+        <v>-12.69</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2764</v>
+        <v>1.286</v>
       </c>
       <c r="F7" t="n">
-        <v>4587.509239999999</v>
+        <v>4622.0126</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-732.4775800000007</v>
+        <v>-697.9742200000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-13.77</v>
+        <v>-13.12</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2932</v>
+        <v>2.2549</v>
       </c>
       <c r="F8" t="n">
-        <v>29582.28</v>
+        <v>29088.21</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>10283.88</v>
+        <v>9789.810000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>53.29</v>
+        <v>50.73</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1843</v>
+        <v>3.1817</v>
       </c>
       <c r="F9" t="n">
-        <v>964.237883</v>
+        <v>963.4505770000001</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>215.29791</v>
+        <v>214.5106040000001</v>
       </c>
       <c r="J9" t="n">
-        <v>28.75</v>
+        <v>28.64</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2799</v>
+        <v>2.2785</v>
       </c>
       <c r="F10" t="n">
-        <v>2372.076357</v>
+        <v>2370.619755</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>372.0577680000004</v>
+        <v>370.6011660000001</v>
       </c>
       <c r="J10" t="n">
-        <v>18.6</v>
+        <v>18.53</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7251</v>
+        <v>1.7237</v>
       </c>
       <c r="F11" t="n">
-        <v>7137.135472999999</v>
+        <v>7131.343351</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1158.010676999999</v>
+        <v>1152.218554999999</v>
       </c>
       <c r="J11" t="n">
-        <v>19.37</v>
+        <v>19.27</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7251</v>
+        <v>1.7237</v>
       </c>
       <c r="F12" t="n">
-        <v>10374.872157</v>
+        <v>10366.452459</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1274.982840000001</v>
+        <v>1266.563142000001</v>
       </c>
       <c r="J12" t="n">
-        <v>14.01</v>
+        <v>13.92</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4897</v>
+        <v>2.4875</v>
       </c>
       <c r="F15" t="n">
-        <v>23154.21</v>
+        <v>23133.75</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3707.91</v>
+        <v>3687.450000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>19.07</v>
+        <v>18.96</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>29</v>
+        <v>29.21</v>
       </c>
       <c r="F16" t="n">
-        <v>14500</v>
+        <v>14605</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>685</v>
+        <v>790</v>
       </c>
       <c r="J16" t="n">
-        <v>4.96</v>
+        <v>5.72</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.109999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="F17" t="n">
-        <v>18220</v>
+        <v>18360</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>460</v>
+        <v>600</v>
       </c>
       <c r="J17" t="n">
-        <v>2.59</v>
+        <v>3.38</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0735</v>
+        <v>1.0667</v>
       </c>
       <c r="F18" t="n">
-        <v>4216.911964999999</v>
+        <v>4190.200273</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-89.56273200000032</v>
+        <v>-116.2744239999993</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.08</v>
+        <v>-2.7</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5829</v>
+        <v>1.5876</v>
       </c>
       <c r="F19" t="n">
-        <v>13771.23</v>
+        <v>13812.12</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>312.3299999999999</v>
+        <v>353.2199999999993</v>
       </c>
       <c r="J19" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1644</v>
+        <v>1.1708</v>
       </c>
       <c r="F20" t="n">
-        <v>9228.871384</v>
+        <v>9279.596888</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-771.1861779999999</v>
+        <v>-720.4606739999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.71</v>
+        <v>-7.2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2302</v>
+        <v>1.2236</v>
       </c>
       <c r="F21" t="n">
-        <v>13901.26</v>
+        <v>13826.68</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1267.860000000001</v>
+        <v>1193.280000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>10.04</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8179</v>
+        <v>1.8053</v>
       </c>
       <c r="F22" t="n">
-        <v>970.558631</v>
+        <v>963.8316169999999</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>241.425058</v>
+        <v>234.698044</v>
       </c>
       <c r="J22" t="n">
-        <v>33.11</v>
+        <v>32.19</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8179</v>
+        <v>1.8053</v>
       </c>
       <c r="F23" t="n">
-        <v>23490.431146</v>
+        <v>23327.617222</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>4290.017679999997</v>
+        <v>4127.203755999995</v>
       </c>
       <c r="J23" t="n">
-        <v>22.34</v>
+        <v>21.5</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6313</v>
+        <v>1.6205</v>
       </c>
       <c r="F24" t="n">
-        <v>1067.392216</v>
+        <v>1060.32556</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>267.420584</v>
+        <v>260.3539280000002</v>
       </c>
       <c r="J24" t="n">
-        <v>33.43</v>
+        <v>32.55</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.5274</v>
+        <v>6.4799</v>
       </c>
       <c r="F26" t="n">
-        <v>2711.090316</v>
+        <v>2691.361666</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>611.0897419999997</v>
+        <v>591.3610919999996</v>
       </c>
       <c r="J26" t="n">
-        <v>29.1</v>
+        <v>28.16</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.1116</v>
+        <v>2.0968</v>
       </c>
       <c r="F28" t="n">
-        <v>8148.242080000001</v>
+        <v>8091.13184</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1848.365200000001</v>
+        <v>1791.25496</v>
       </c>
       <c r="J28" t="n">
-        <v>29.34</v>
+        <v>28.43</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.1116</v>
+        <v>2.0968</v>
       </c>
       <c r="F29" t="n">
-        <v>18390.536764</v>
+        <v>18261.639272</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>3390.526597000004</v>
+        <v>3261.629105</v>
       </c>
       <c r="J29" t="n">
-        <v>22.6</v>
+        <v>21.74</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1998</v>
+        <v>2.1856</v>
       </c>
       <c r="F30" t="n">
-        <v>11566.746382</v>
+        <v>11492.081504</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2686.358181000001</v>
+        <v>2611.693303</v>
       </c>
       <c r="J30" t="n">
-        <v>30.25</v>
+        <v>29.41</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1998</v>
+        <v>2.1856</v>
       </c>
       <c r="F31" t="n">
-        <v>1483.259146</v>
+        <v>1473.684512</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>283.2608270000001</v>
+        <v>273.686193</v>
       </c>
       <c r="J31" t="n">
-        <v>23.61</v>
+        <v>22.81</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.5725</v>
+        <v>2.554</v>
       </c>
       <c r="F33" t="n">
-        <v>15692.25</v>
+        <v>15579.4</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3419.049999999997</v>
+        <v>3306.199999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>27.86</v>
+        <v>26.94</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0715</v>
+        <v>2.0563</v>
       </c>
       <c r="F34" t="n">
-        <v>39565.65</v>
+        <v>39275.32999999999</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>8394.450000000001</v>
+        <v>8104.129999999994</v>
       </c>
       <c r="J34" t="n">
-        <v>26.93</v>
+        <v>26</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>7.1048</v>
+        <v>7.0424</v>
       </c>
       <c r="F35" t="n">
-        <v>43242.512624</v>
+        <v>42862.722512</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>10042.527</v>
+        <v>9662.736887999999</v>
       </c>
       <c r="J35" t="n">
-        <v>30.25</v>
+        <v>29.1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>7.1048</v>
+        <v>7.0424</v>
       </c>
       <c r="F36" t="n">
-        <v>14684.626928</v>
+        <v>14555.654864</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>3384.689936000001</v>
+        <v>3255.717871999999</v>
       </c>
       <c r="J36" t="n">
-        <v>29.95</v>
+        <v>28.81</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>7.1048</v>
+        <v>7.0424</v>
       </c>
       <c r="F37" t="n">
-        <v>106572</v>
+        <v>105636</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>23277</v>
+        <v>22341</v>
       </c>
       <c r="J37" t="n">
-        <v>27.95</v>
+        <v>26.82</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.9976</v>
+        <v>2.9755</v>
       </c>
       <c r="F38" t="n">
-        <v>21802.773816</v>
+        <v>21642.031455</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>6002.745272999997</v>
+        <v>5842.002911999996</v>
       </c>
       <c r="J38" t="n">
-        <v>37.99</v>
+        <v>36.97</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9976</v>
+        <v>2.9755</v>
       </c>
       <c r="F39" t="n">
-        <v>31258.703016</v>
+        <v>31028.246205</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>8258.904719999999</v>
+        <v>8028.447908999995</v>
       </c>
       <c r="J39" t="n">
-        <v>35.91</v>
+        <v>34.91</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.3992</v>
+        <v>2.3871</v>
       </c>
       <c r="F40" t="n">
-        <v>16074.64</v>
+        <v>15993.57</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>5622.639999999999</v>
+        <v>5541.570000000002</v>
       </c>
       <c r="J40" t="n">
-        <v>53.79</v>
+        <v>53.02</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.220000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>8220</v>
+        <v>8450</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1111</v>
+        <v>1341</v>
       </c>
       <c r="J41" t="n">
-        <v>15.63</v>
+        <v>18.86</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>6.98</v>
+        <v>7.19</v>
       </c>
       <c r="F42" t="n">
-        <v>7678.000000000001</v>
+        <v>7909</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1093.400000000001</v>
+        <v>1324.4</v>
       </c>
       <c r="J42" t="n">
-        <v>16.61</v>
+        <v>20.11</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>41.56</v>
+        <v>42.66</v>
       </c>
       <c r="F43" t="n">
-        <v>62340</v>
+        <v>63989.99999999999</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-2115</v>
+        <v>-465.0000000000073</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.28</v>
+        <v>-0.72</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8337</v>
+        <v>2.8046</v>
       </c>
       <c r="F2" t="n">
-        <v>2096.059553</v>
+        <v>2074.534574</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>225.8273570000001</v>
+        <v>204.3023780000003</v>
       </c>
       <c r="J2" t="n">
-        <v>12.07</v>
+        <v>10.92</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6948</v>
+        <v>2.6712</v>
       </c>
       <c r="F3" t="n">
-        <v>873.977536</v>
+        <v>866.3235839999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-125.9658880000001</v>
+        <v>-133.6198400000002</v>
       </c>
       <c r="J3" t="n">
-        <v>-12.6</v>
+        <v>-13.36</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1656</v>
+        <v>1.1476</v>
       </c>
       <c r="F4" t="n">
-        <v>6643.92</v>
+        <v>6541.32</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1223.22</v>
+        <v>1120.62</v>
       </c>
       <c r="J4" t="n">
-        <v>22.57</v>
+        <v>20.67</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8822</v>
+        <v>1.8733</v>
       </c>
       <c r="F5" t="n">
-        <v>2232.157446</v>
+        <v>2221.602669</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-167.8090949999996</v>
+        <v>-178.3638719999999</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.99</v>
+        <v>-7.43</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.286</v>
+        <v>1.2993</v>
       </c>
       <c r="F6" t="n">
-        <v>2182.71494</v>
+        <v>2205.288897</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-317.2235009999999</v>
+        <v>-294.6495439999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.69</v>
+        <v>-11.79</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.286</v>
+        <v>1.2993</v>
       </c>
       <c r="F7" t="n">
-        <v>4622.0126</v>
+        <v>4669.81413</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-697.9742200000001</v>
+        <v>-650.1726900000003</v>
       </c>
       <c r="J7" t="n">
-        <v>-13.12</v>
+        <v>-12.22</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2549</v>
+        <v>2.254</v>
       </c>
       <c r="F8" t="n">
-        <v>29088.21</v>
+        <v>29076.6</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>9789.810000000001</v>
+        <v>9778.199999999997</v>
       </c>
       <c r="J8" t="n">
-        <v>50.73</v>
+        <v>50.67</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1817</v>
+        <v>3.1803</v>
       </c>
       <c r="F9" t="n">
-        <v>963.4505770000001</v>
+        <v>963.0266429999999</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>214.5106040000001</v>
+        <v>214.0866699999999</v>
       </c>
       <c r="J9" t="n">
-        <v>28.64</v>
+        <v>28.59</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2785</v>
+        <v>2.2771</v>
       </c>
       <c r="F10" t="n">
-        <v>2370.619755</v>
+        <v>2369.163153</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>370.6011660000001</v>
+        <v>369.1445639999999</v>
       </c>
       <c r="J10" t="n">
-        <v>18.53</v>
+        <v>18.46</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7237</v>
+        <v>1.7233</v>
       </c>
       <c r="F11" t="n">
-        <v>7131.343351</v>
+        <v>7129.688458999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1152.218554999999</v>
+        <v>1150.563662999999</v>
       </c>
       <c r="J11" t="n">
-        <v>19.27</v>
+        <v>19.24</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7237</v>
+        <v>1.7233</v>
       </c>
       <c r="F12" t="n">
-        <v>10366.452459</v>
+        <v>10364.046831</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1266.563142000001</v>
+        <v>1264.157514</v>
       </c>
       <c r="J12" t="n">
-        <v>13.92</v>
+        <v>13.89</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4875</v>
+        <v>2.4866</v>
       </c>
       <c r="F15" t="n">
-        <v>23133.75</v>
+        <v>23125.38</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3687.450000000001</v>
+        <v>3679.080000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>18.96</v>
+        <v>18.92</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>29.21</v>
+        <v>29.1</v>
       </c>
       <c r="F16" t="n">
-        <v>14605</v>
+        <v>14550</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>790</v>
+        <v>735</v>
       </c>
       <c r="J16" t="n">
-        <v>5.72</v>
+        <v>5.32</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.18</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>18360</v>
+        <v>18260</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J17" t="n">
-        <v>3.38</v>
+        <v>2.82</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0667</v>
+        <v>1.0763</v>
       </c>
       <c r="F18" t="n">
-        <v>4190.200273</v>
+        <v>4227.910897</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-116.2744239999993</v>
+        <v>-78.5637999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.7</v>
+        <v>-1.82</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5876</v>
+        <v>1.599</v>
       </c>
       <c r="F19" t="n">
-        <v>13812.12</v>
+        <v>13911.3</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>353.2199999999993</v>
+        <v>452.3999999999996</v>
       </c>
       <c r="J19" t="n">
-        <v>2.62</v>
+        <v>3.36</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1708</v>
+        <v>1.1723</v>
       </c>
       <c r="F20" t="n">
-        <v>9279.596888</v>
+        <v>9291.485677999999</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-720.4606739999999</v>
+        <v>-708.5718840000009</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.2</v>
+        <v>-7.09</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2236</v>
+        <v>1.2305</v>
       </c>
       <c r="F21" t="n">
-        <v>13826.68</v>
+        <v>13904.65</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1193.280000000001</v>
+        <v>1271.25</v>
       </c>
       <c r="J21" t="n">
-        <v>9.449999999999999</v>
+        <v>10.06</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8053</v>
+        <v>1.7996</v>
       </c>
       <c r="F22" t="n">
-        <v>963.8316169999999</v>
+        <v>960.788444</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>234.698044</v>
+        <v>231.6548710000001</v>
       </c>
       <c r="J22" t="n">
-        <v>32.19</v>
+        <v>31.77</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8053</v>
+        <v>1.7996</v>
       </c>
       <c r="F23" t="n">
-        <v>23327.617222</v>
+        <v>23253.963304</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>4127.203755999995</v>
+        <v>4053.549837999999</v>
       </c>
       <c r="J23" t="n">
-        <v>21.5</v>
+        <v>21.11</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6205</v>
+        <v>1.6156</v>
       </c>
       <c r="F24" t="n">
-        <v>1060.32556</v>
+        <v>1057.119392</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>260.3539280000002</v>
+        <v>257.1477600000001</v>
       </c>
       <c r="J24" t="n">
-        <v>32.55</v>
+        <v>32.14</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.4799</v>
+        <v>6.458</v>
       </c>
       <c r="F26" t="n">
-        <v>2691.361666</v>
+        <v>2682.26572</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>591.3610919999996</v>
+        <v>582.2651459999997</v>
       </c>
       <c r="J26" t="n">
-        <v>28.16</v>
+        <v>27.73</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0968</v>
+        <v>2.09</v>
       </c>
       <c r="F28" t="n">
-        <v>8091.13184</v>
+        <v>8064.892</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1791.25496</v>
+        <v>1765.01512</v>
       </c>
       <c r="J28" t="n">
-        <v>28.43</v>
+        <v>28.02</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0968</v>
+        <v>2.09</v>
       </c>
       <c r="F29" t="n">
-        <v>18261.639272</v>
+        <v>18202.4161</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>3261.629105</v>
+        <v>3202.405933000002</v>
       </c>
       <c r="J29" t="n">
-        <v>21.74</v>
+        <v>21.35</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1856</v>
+        <v>2.1816</v>
       </c>
       <c r="F30" t="n">
-        <v>11492.081504</v>
+        <v>11471.049144</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2611.693303</v>
+        <v>2590.660943000001</v>
       </c>
       <c r="J30" t="n">
-        <v>29.41</v>
+        <v>29.17</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1856</v>
+        <v>2.1816</v>
       </c>
       <c r="F31" t="n">
-        <v>1473.684512</v>
+        <v>1470.987432</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>273.686193</v>
+        <v>270.9891129999999</v>
       </c>
       <c r="J31" t="n">
-        <v>22.81</v>
+        <v>22.58</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.554</v>
+        <v>2.5466</v>
       </c>
       <c r="F33" t="n">
-        <v>15579.4</v>
+        <v>15534.26</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3306.199999999999</v>
+        <v>3261.060000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>26.94</v>
+        <v>26.57</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0563</v>
+        <v>2.0494</v>
       </c>
       <c r="F34" t="n">
-        <v>39275.32999999999</v>
+        <v>39143.54</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>8104.129999999994</v>
+        <v>7972.34</v>
       </c>
       <c r="J34" t="n">
-        <v>26</v>
+        <v>25.58</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>7.0424</v>
+        <v>7.0454</v>
       </c>
       <c r="F35" t="n">
-        <v>42862.722512</v>
+        <v>42880.981652</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>9662.736887999999</v>
+        <v>9680.996028000001</v>
       </c>
       <c r="J35" t="n">
-        <v>29.1</v>
+        <v>29.16</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>7.0424</v>
+        <v>7.0454</v>
       </c>
       <c r="F36" t="n">
-        <v>14555.654864</v>
+        <v>14561.855444</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>3255.717871999999</v>
+        <v>3261.918452</v>
       </c>
       <c r="J36" t="n">
-        <v>28.81</v>
+        <v>28.87</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>7.0424</v>
+        <v>7.0454</v>
       </c>
       <c r="F37" t="n">
-        <v>105636</v>
+        <v>105681</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>22341</v>
+        <v>22386</v>
       </c>
       <c r="J37" t="n">
-        <v>26.82</v>
+        <v>26.88</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.9755</v>
+        <v>2.9642</v>
       </c>
       <c r="F38" t="n">
-        <v>21642.031455</v>
+        <v>21559.841922</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>5842.002911999996</v>
+        <v>5759.813378999999</v>
       </c>
       <c r="J38" t="n">
-        <v>36.97</v>
+        <v>36.45</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9755</v>
+        <v>2.9642</v>
       </c>
       <c r="F39" t="n">
-        <v>31028.246205</v>
+        <v>30910.410822</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>8028.447908999995</v>
+        <v>7910.612525999997</v>
       </c>
       <c r="J39" t="n">
-        <v>34.91</v>
+        <v>34.39</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.3871</v>
+        <v>2.3895</v>
       </c>
       <c r="F40" t="n">
-        <v>15993.57</v>
+        <v>16009.65</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>5541.570000000002</v>
+        <v>5557.65</v>
       </c>
       <c r="J40" t="n">
-        <v>53.02</v>
+        <v>53.17</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.449999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="F41" t="n">
-        <v>8450</v>
+        <v>8480</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1341</v>
+        <v>1371</v>
       </c>
       <c r="J41" t="n">
-        <v>18.86</v>
+        <v>19.29</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7.19</v>
+        <v>7.25</v>
       </c>
       <c r="F42" t="n">
-        <v>7909</v>
+        <v>7975</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1324.4</v>
+        <v>1390.4</v>
       </c>
       <c r="J42" t="n">
-        <v>20.11</v>
+        <v>21.12</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>42.66</v>
+        <v>42.61</v>
       </c>
       <c r="F43" t="n">
-        <v>63989.99999999999</v>
+        <v>63915</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-465.0000000000073</v>
+        <v>-540</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.72</v>
+        <v>-0.84</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8046</v>
+        <v>2.798</v>
       </c>
       <c r="F2" t="n">
-        <v>2074.534574</v>
+        <v>2069.65262</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>204.3023780000003</v>
+        <v>199.4204240000004</v>
       </c>
       <c r="J2" t="n">
-        <v>10.92</v>
+        <v>10.66</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6712</v>
+        <v>2.6224</v>
       </c>
       <c r="F3" t="n">
-        <v>866.3235839999999</v>
+        <v>850.496768</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-133.6198400000002</v>
+        <v>-149.4466560000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-13.36</v>
+        <v>-14.95</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1476</v>
+        <v>1.128</v>
       </c>
       <c r="F4" t="n">
-        <v>6541.32</v>
+        <v>6429.599999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1120.62</v>
+        <v>1008.9</v>
       </c>
       <c r="J4" t="n">
-        <v>20.67</v>
+        <v>18.61</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8733</v>
+        <v>1.8814</v>
       </c>
       <c r="F5" t="n">
-        <v>2221.602669</v>
+        <v>2231.208702</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-178.3638719999999</v>
+        <v>-168.7578389999999</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.43</v>
+        <v>-7.03</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2993</v>
+        <v>1.2925</v>
       </c>
       <c r="F6" t="n">
-        <v>2205.288897</v>
+        <v>2193.747325</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-294.6495439999999</v>
+        <v>-306.191116</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.79</v>
+        <v>-12.25</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2993</v>
+        <v>1.2925</v>
       </c>
       <c r="F7" t="n">
-        <v>4669.81413</v>
+        <v>4645.37425</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-650.1726900000003</v>
+        <v>-674.6125700000002</v>
       </c>
       <c r="J7" t="n">
-        <v>-12.22</v>
+        <v>-12.68</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.254</v>
+        <v>2.1534</v>
       </c>
       <c r="F8" t="n">
-        <v>29076.6</v>
+        <v>27778.86</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>9778.199999999997</v>
+        <v>8480.459999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>50.67</v>
+        <v>43.94</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1803</v>
+        <v>3.1448</v>
       </c>
       <c r="F9" t="n">
-        <v>963.0266429999999</v>
+        <v>952.276888</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>214.0866699999999</v>
+        <v>203.336915</v>
       </c>
       <c r="J9" t="n">
-        <v>28.59</v>
+        <v>27.15</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2771</v>
+        <v>2.2543</v>
       </c>
       <c r="F10" t="n">
-        <v>2369.163153</v>
+        <v>2345.441349</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>369.1445639999999</v>
+        <v>345.4227600000002</v>
       </c>
       <c r="J10" t="n">
-        <v>18.46</v>
+        <v>17.27</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7233</v>
+        <v>1.7037</v>
       </c>
       <c r="F11" t="n">
-        <v>7129.688458999999</v>
+        <v>7048.598751</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1150.563662999999</v>
+        <v>1069.473954999999</v>
       </c>
       <c r="J11" t="n">
-        <v>19.24</v>
+        <v>17.89</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7233</v>
+        <v>1.7037</v>
       </c>
       <c r="F12" t="n">
-        <v>10364.046831</v>
+        <v>10246.171059</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1264.157514</v>
+        <v>1146.281742000001</v>
       </c>
       <c r="J12" t="n">
-        <v>13.89</v>
+        <v>12.6</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4866</v>
+        <v>2.4567</v>
       </c>
       <c r="F15" t="n">
-        <v>23125.38</v>
+        <v>22847.31</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3679.080000000002</v>
+        <v>3401.010000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>18.92</v>
+        <v>17.49</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>29.1</v>
+        <v>29.48</v>
       </c>
       <c r="F16" t="n">
-        <v>14550</v>
+        <v>14740</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>735</v>
+        <v>925</v>
       </c>
       <c r="J16" t="n">
-        <v>5.32</v>
+        <v>6.7</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.130000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="F17" t="n">
-        <v>18260</v>
+        <v>18840</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>500</v>
+        <v>1080</v>
       </c>
       <c r="J17" t="n">
-        <v>2.82</v>
+        <v>6.08</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0763</v>
+        <v>1.0731</v>
       </c>
       <c r="F18" t="n">
-        <v>4227.910897</v>
+        <v>4215.340689</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-78.5637999999999</v>
+        <v>-91.13400799999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.82</v>
+        <v>-2.12</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.599</v>
+        <v>1.5604</v>
       </c>
       <c r="F19" t="n">
-        <v>13911.3</v>
+        <v>13575.48</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>452.3999999999996</v>
+        <v>116.5799999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>3.36</v>
+        <v>0.87</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1723</v>
+        <v>1.1584</v>
       </c>
       <c r="F20" t="n">
-        <v>9291.485677999999</v>
+        <v>9181.316224</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-708.5718840000009</v>
+        <v>-818.7413379999998</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.09</v>
+        <v>-8.19</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2305</v>
+        <v>1.215</v>
       </c>
       <c r="F21" t="n">
-        <v>13904.65</v>
+        <v>13729.5</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1271.25</v>
+        <v>1096.1</v>
       </c>
       <c r="J21" t="n">
-        <v>10.06</v>
+        <v>8.68</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7996</v>
+        <v>1.7641</v>
       </c>
       <c r="F22" t="n">
-        <v>960.788444</v>
+        <v>941.835349</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>231.6548710000001</v>
+        <v>212.701776</v>
       </c>
       <c r="J22" t="n">
-        <v>31.77</v>
+        <v>29.17</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7996</v>
+        <v>1.7641</v>
       </c>
       <c r="F23" t="n">
-        <v>23253.963304</v>
+        <v>22795.241534</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>4053.549837999999</v>
+        <v>3594.828067999999</v>
       </c>
       <c r="J23" t="n">
-        <v>21.11</v>
+        <v>18.72</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6156</v>
+        <v>1.5849</v>
       </c>
       <c r="F24" t="n">
-        <v>1057.119392</v>
+        <v>1037.031768</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>257.1477600000001</v>
+        <v>237.0601360000001</v>
       </c>
       <c r="J24" t="n">
-        <v>32.14</v>
+        <v>29.63</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.458</v>
+        <v>6.3249</v>
       </c>
       <c r="F26" t="n">
-        <v>2682.26572</v>
+        <v>2626.983966</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>582.2651459999997</v>
+        <v>526.9833920000001</v>
       </c>
       <c r="J26" t="n">
-        <v>27.73</v>
+        <v>25.09</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.09</v>
+        <v>2.0484</v>
       </c>
       <c r="F28" t="n">
-        <v>8064.892</v>
+        <v>7904.36592</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1765.01512</v>
+        <v>1604.48904</v>
       </c>
       <c r="J28" t="n">
-        <v>28.02</v>
+        <v>25.47</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.09</v>
+        <v>2.0484</v>
       </c>
       <c r="F29" t="n">
-        <v>18202.4161</v>
+        <v>17840.109636</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>3202.405933000002</v>
+        <v>2840.099469000001</v>
       </c>
       <c r="J29" t="n">
-        <v>21.35</v>
+        <v>18.93</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1816</v>
+        <v>2.1383</v>
       </c>
       <c r="F30" t="n">
-        <v>11471.049144</v>
+        <v>11243.373847</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2590.660943000001</v>
+        <v>2362.985646000001</v>
       </c>
       <c r="J30" t="n">
-        <v>29.17</v>
+        <v>26.61</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1816</v>
+        <v>2.1383</v>
       </c>
       <c r="F31" t="n">
-        <v>1470.987432</v>
+        <v>1441.791541</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>270.9891129999999</v>
+        <v>241.793222</v>
       </c>
       <c r="J31" t="n">
-        <v>22.58</v>
+        <v>20.15</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.5466</v>
+        <v>2.4945</v>
       </c>
       <c r="F33" t="n">
-        <v>15534.26</v>
+        <v>15216.45</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3261.060000000001</v>
+        <v>2943.249999999998</v>
       </c>
       <c r="J33" t="n">
-        <v>26.57</v>
+        <v>23.98</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0494</v>
+        <v>2.0067</v>
       </c>
       <c r="F34" t="n">
-        <v>39143.54</v>
+        <v>38327.97</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>7972.34</v>
+        <v>7156.77</v>
       </c>
       <c r="J34" t="n">
-        <v>25.58</v>
+        <v>22.96</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>7.0454</v>
+        <v>6.8671</v>
       </c>
       <c r="F35" t="n">
-        <v>42880.981652</v>
+        <v>41795.780098</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>9680.996028000001</v>
+        <v>8595.794474000002</v>
       </c>
       <c r="J35" t="n">
-        <v>29.16</v>
+        <v>25.89</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>7.0454</v>
+        <v>6.8671</v>
       </c>
       <c r="F36" t="n">
-        <v>14561.855444</v>
+        <v>14193.334306</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>3261.918452</v>
+        <v>2893.397314</v>
       </c>
       <c r="J36" t="n">
-        <v>28.87</v>
+        <v>25.61</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>7.0454</v>
+        <v>6.8671</v>
       </c>
       <c r="F37" t="n">
-        <v>105681</v>
+        <v>103006.5</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>22386</v>
+        <v>19711.5</v>
       </c>
       <c r="J37" t="n">
-        <v>26.88</v>
+        <v>23.66</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.9642</v>
+        <v>2.8793</v>
       </c>
       <c r="F38" t="n">
-        <v>21559.841922</v>
+        <v>20942.329413</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>5759.813378999999</v>
+        <v>5142.300869999999</v>
       </c>
       <c r="J38" t="n">
-        <v>36.45</v>
+        <v>32.55</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9642</v>
+        <v>2.8793</v>
       </c>
       <c r="F39" t="n">
-        <v>30910.410822</v>
+        <v>30025.081263</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>7910.612525999997</v>
+        <v>7025.282966999999</v>
       </c>
       <c r="J39" t="n">
-        <v>34.39</v>
+        <v>30.54</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.3895</v>
+        <v>2.3264</v>
       </c>
       <c r="F40" t="n">
-        <v>16009.65</v>
+        <v>15586.88</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>5557.65</v>
+        <v>5134.880000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>53.17</v>
+        <v>49.13</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.48</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>8480</v>
+        <v>8470</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1371</v>
+        <v>1361</v>
       </c>
       <c r="J41" t="n">
-        <v>19.29</v>
+        <v>19.14</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7.25</v>
+        <v>7.21</v>
       </c>
       <c r="F42" t="n">
-        <v>7975</v>
+        <v>7931</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1390.4</v>
+        <v>1346.4</v>
       </c>
       <c r="J42" t="n">
-        <v>21.12</v>
+        <v>20.45</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>42.61</v>
+        <v>42.74</v>
       </c>
       <c r="F43" t="n">
-        <v>63915</v>
+        <v>64110</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-540</v>
+        <v>-345</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.84</v>
+        <v>-0.54</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.798</v>
+        <v>2.8243</v>
       </c>
       <c r="F2" t="n">
-        <v>2069.65262</v>
+        <v>2089.106467</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>199.4204240000004</v>
+        <v>218.8742710000001</v>
       </c>
       <c r="J2" t="n">
-        <v>10.66</v>
+        <v>11.7</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6224</v>
+        <v>2.5842</v>
       </c>
       <c r="F3" t="n">
-        <v>850.496768</v>
+        <v>838.107744</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-149.4466560000001</v>
+        <v>-161.83568</v>
       </c>
       <c r="J3" t="n">
-        <v>-14.95</v>
+        <v>-16.18</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.128</v>
+        <v>1.1297</v>
       </c>
       <c r="F4" t="n">
-        <v>6429.599999999999</v>
+        <v>6439.29</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1008.9</v>
+        <v>1018.59</v>
       </c>
       <c r="J4" t="n">
-        <v>18.61</v>
+        <v>18.79</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8814</v>
+        <v>1.8846</v>
       </c>
       <c r="F5" t="n">
-        <v>2231.208702</v>
+        <v>2235.003678</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-168.7578389999999</v>
+        <v>-164.9628629999997</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.03</v>
+        <v>-6.87</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2925</v>
+        <v>1.2992</v>
       </c>
       <c r="F6" t="n">
-        <v>2193.747325</v>
+        <v>2205.119168</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-306.191116</v>
+        <v>-294.8192730000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.25</v>
+        <v>-11.79</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2925</v>
+        <v>1.2992</v>
       </c>
       <c r="F7" t="n">
-        <v>4645.37425</v>
+        <v>4669.45472</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-674.6125700000002</v>
+        <v>-650.5321000000004</v>
       </c>
       <c r="J7" t="n">
-        <v>-12.68</v>
+        <v>-12.23</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1534</v>
+        <v>2.1784</v>
       </c>
       <c r="F8" t="n">
-        <v>27778.86</v>
+        <v>28101.36</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8480.459999999999</v>
+        <v>8802.959999999995</v>
       </c>
       <c r="J8" t="n">
-        <v>43.94</v>
+        <v>45.61</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1448</v>
+        <v>3.1548</v>
       </c>
       <c r="F9" t="n">
-        <v>952.276888</v>
+        <v>955.304988</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>203.336915</v>
+        <v>206.365015</v>
       </c>
       <c r="J9" t="n">
-        <v>27.15</v>
+        <v>27.55</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2543</v>
+        <v>2.2587</v>
       </c>
       <c r="F10" t="n">
-        <v>2345.441349</v>
+        <v>2350.019241</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>345.4227600000002</v>
+        <v>350.0006520000004</v>
       </c>
       <c r="J10" t="n">
-        <v>17.27</v>
+        <v>17.5</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7037</v>
+        <v>1.7088</v>
       </c>
       <c r="F11" t="n">
-        <v>7048.598751</v>
+        <v>7069.698624</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1069.473954999999</v>
+        <v>1090.573828</v>
       </c>
       <c r="J11" t="n">
-        <v>17.89</v>
+        <v>18.24</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7037</v>
+        <v>1.7088</v>
       </c>
       <c r="F12" t="n">
-        <v>10246.171059</v>
+        <v>10276.842816</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1146.281742000001</v>
+        <v>1176.953499000001</v>
       </c>
       <c r="J12" t="n">
-        <v>12.6</v>
+        <v>12.93</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4567</v>
+        <v>2.4648</v>
       </c>
       <c r="F15" t="n">
-        <v>22847.31</v>
+        <v>22922.64</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3401.010000000002</v>
+        <v>3476.34</v>
       </c>
       <c r="J15" t="n">
-        <v>17.49</v>
+        <v>17.88</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>29.48</v>
+        <v>29.38</v>
       </c>
       <c r="F16" t="n">
-        <v>14740</v>
+        <v>14690</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>925</v>
+        <v>875</v>
       </c>
       <c r="J16" t="n">
-        <v>6.7</v>
+        <v>6.33</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.42</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>18840</v>
+        <v>18780</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>1080</v>
+        <v>1020</v>
       </c>
       <c r="J17" t="n">
-        <v>6.08</v>
+        <v>5.74</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0731</v>
+        <v>1.0749</v>
       </c>
       <c r="F18" t="n">
-        <v>4215.340689</v>
+        <v>4222.411431</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-91.13400799999999</v>
+        <v>-84.06326600000011</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.12</v>
+        <v>-1.95</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5604</v>
+        <v>1.5738</v>
       </c>
       <c r="F19" t="n">
-        <v>13575.48</v>
+        <v>13692.06</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>116.5799999999999</v>
+        <v>233.1600000000017</v>
       </c>
       <c r="J19" t="n">
-        <v>0.87</v>
+        <v>1.73</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1584</v>
+        <v>1.1577</v>
       </c>
       <c r="F20" t="n">
-        <v>9181.316224</v>
+        <v>9175.768121999999</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-818.7413379999998</v>
+        <v>-824.2894400000005</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.19</v>
+        <v>-8.24</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.215</v>
+        <v>1.2196</v>
       </c>
       <c r="F21" t="n">
-        <v>13729.5</v>
+        <v>13781.48</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1096.1</v>
+        <v>1148.08</v>
       </c>
       <c r="J21" t="n">
-        <v>8.68</v>
+        <v>9.09</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7641</v>
+        <v>1.7634</v>
       </c>
       <c r="F22" t="n">
-        <v>941.835349</v>
+        <v>941.461626</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>212.701776</v>
+        <v>212.3280530000001</v>
       </c>
       <c r="J22" t="n">
-        <v>29.17</v>
+        <v>29.12</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7641</v>
+        <v>1.7634</v>
       </c>
       <c r="F23" t="n">
-        <v>22795.241534</v>
+        <v>22786.196316</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3594.828067999999</v>
+        <v>3585.78285</v>
       </c>
       <c r="J23" t="n">
-        <v>18.72</v>
+        <v>18.68</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5849</v>
+        <v>1.5842</v>
       </c>
       <c r="F24" t="n">
-        <v>1037.031768</v>
+        <v>1036.573744</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>237.0601360000001</v>
+        <v>236.602112</v>
       </c>
       <c r="J24" t="n">
-        <v>29.63</v>
+        <v>29.58</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.3249</v>
+        <v>6.3187</v>
       </c>
       <c r="F26" t="n">
-        <v>2626.983966</v>
+        <v>2624.408858</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>526.9833920000001</v>
+        <v>524.4082839999996</v>
       </c>
       <c r="J26" t="n">
-        <v>25.09</v>
+        <v>24.97</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0484</v>
+        <v>2.0474</v>
       </c>
       <c r="F28" t="n">
-        <v>7904.36592</v>
+        <v>7900.507120000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1604.48904</v>
+        <v>1600.630240000001</v>
       </c>
       <c r="J28" t="n">
-        <v>25.47</v>
+        <v>25.41</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0484</v>
+        <v>2.0474</v>
       </c>
       <c r="F29" t="n">
-        <v>17840.109636</v>
+        <v>17831.400346</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2840.099469000001</v>
+        <v>2831.390179000002</v>
       </c>
       <c r="J29" t="n">
-        <v>18.93</v>
+        <v>18.88</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1383</v>
+        <v>2.1372</v>
       </c>
       <c r="F30" t="n">
-        <v>11243.373847</v>
+        <v>11237.589948</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2362.985646000001</v>
+        <v>2357.201747000001</v>
       </c>
       <c r="J30" t="n">
-        <v>26.61</v>
+        <v>26.54</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1383</v>
+        <v>2.1372</v>
       </c>
       <c r="F31" t="n">
-        <v>1441.791541</v>
+        <v>1441.049844</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>241.793222</v>
+        <v>241.0515249999999</v>
       </c>
       <c r="J31" t="n">
-        <v>20.15</v>
+        <v>20.09</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4945</v>
+        <v>2.4927</v>
       </c>
       <c r="F33" t="n">
-        <v>15216.45</v>
+        <v>15205.47</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2943.249999999998</v>
+        <v>2932.27</v>
       </c>
       <c r="J33" t="n">
-        <v>23.98</v>
+        <v>23.89</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0067</v>
+        <v>2.0057</v>
       </c>
       <c r="F34" t="n">
-        <v>38327.97</v>
+        <v>38308.87</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>7156.77</v>
+        <v>7137.670000000002</v>
       </c>
       <c r="J34" t="n">
-        <v>22.96</v>
+        <v>22.9</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.8671</v>
+        <v>6.833</v>
       </c>
       <c r="F35" t="n">
-        <v>41795.780098</v>
+        <v>41588.23454</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>8595.794474000002</v>
+        <v>8388.248916000004</v>
       </c>
       <c r="J35" t="n">
-        <v>25.89</v>
+        <v>25.27</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.8671</v>
+        <v>6.833</v>
       </c>
       <c r="F36" t="n">
-        <v>14193.334306</v>
+        <v>14122.85438</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2893.397314</v>
+        <v>2822.917388</v>
       </c>
       <c r="J36" t="n">
-        <v>25.61</v>
+        <v>24.98</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.8671</v>
+        <v>6.833</v>
       </c>
       <c r="F37" t="n">
-        <v>103006.5</v>
+        <v>102495</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>19711.5</v>
+        <v>19200</v>
       </c>
       <c r="J37" t="n">
-        <v>23.66</v>
+        <v>23.05</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.8793</v>
+        <v>2.8666</v>
       </c>
       <c r="F38" t="n">
-        <v>20942.329413</v>
+        <v>20849.957106</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>5142.300869999999</v>
+        <v>5049.928563000001</v>
       </c>
       <c r="J38" t="n">
-        <v>32.55</v>
+        <v>31.96</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.8793</v>
+        <v>2.8666</v>
       </c>
       <c r="F39" t="n">
-        <v>30025.081263</v>
+        <v>29892.646806</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>7025.282966999999</v>
+        <v>6892.84851</v>
       </c>
       <c r="J39" t="n">
-        <v>30.54</v>
+        <v>29.97</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.3264</v>
+        <v>2.3218</v>
       </c>
       <c r="F40" t="n">
-        <v>15586.88</v>
+        <v>15556.06</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>5134.880000000001</v>
+        <v>5104.060000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>49.13</v>
+        <v>48.83</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7.21</v>
+        <v>7.2</v>
       </c>
       <c r="F42" t="n">
-        <v>7931</v>
+        <v>7920</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1346.4</v>
+        <v>1335.4</v>
       </c>
       <c r="J42" t="n">
-        <v>20.45</v>
+        <v>20.28</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>42.74</v>
+        <v>42.6</v>
       </c>
       <c r="F43" t="n">
-        <v>64110</v>
+        <v>63900</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-345</v>
+        <v>-555</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.54</v>
+        <v>-0.86</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8243</v>
+        <v>2.8227</v>
       </c>
       <c r="F2" t="n">
-        <v>2089.106467</v>
+        <v>2087.922963</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>218.8742710000001</v>
+        <v>217.6907670000005</v>
       </c>
       <c r="J2" t="n">
-        <v>11.7</v>
+        <v>11.64</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5842</v>
+        <v>2.597</v>
       </c>
       <c r="F3" t="n">
-        <v>838.107744</v>
+        <v>842.25904</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-161.83568</v>
+        <v>-157.684384</v>
       </c>
       <c r="J3" t="n">
-        <v>-16.18</v>
+        <v>-15.77</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1297</v>
+        <v>1.1323</v>
       </c>
       <c r="F4" t="n">
-        <v>6439.29</v>
+        <v>6454.110000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1018.59</v>
+        <v>1033.410000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>18.79</v>
+        <v>19.06</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8846</v>
+        <v>1.9044</v>
       </c>
       <c r="F5" t="n">
-        <v>2235.003678</v>
+        <v>2258.485092</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-164.9628629999997</v>
+        <v>-141.4814489999994</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.87</v>
+        <v>-5.9</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2992</v>
+        <v>1.3026</v>
       </c>
       <c r="F6" t="n">
-        <v>2205.119168</v>
+        <v>2210.889954</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-294.8192730000001</v>
+        <v>-289.048487</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.79</v>
+        <v>-11.56</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2992</v>
+        <v>1.3026</v>
       </c>
       <c r="F7" t="n">
-        <v>4669.45472</v>
+        <v>4681.67466</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-650.5321000000004</v>
+        <v>-638.3121600000004</v>
       </c>
       <c r="J7" t="n">
-        <v>-12.23</v>
+        <v>-12</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1784</v>
+        <v>2.1579</v>
       </c>
       <c r="F8" t="n">
-        <v>28101.36</v>
+        <v>27836.91</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8802.959999999995</v>
+        <v>8538.510000000002</v>
       </c>
       <c r="J8" t="n">
-        <v>45.61</v>
+        <v>44.24</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1548</v>
+        <v>3.1206</v>
       </c>
       <c r="F9" t="n">
-        <v>955.304988</v>
+        <v>944.948886</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>206.365015</v>
+        <v>196.008913</v>
       </c>
       <c r="J9" t="n">
-        <v>27.55</v>
+        <v>26.17</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2587</v>
+        <v>2.2375</v>
       </c>
       <c r="F10" t="n">
-        <v>2350.019241</v>
+        <v>2327.962125</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>350.0006520000004</v>
+        <v>327.943536</v>
       </c>
       <c r="J10" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7088</v>
+        <v>1.6897</v>
       </c>
       <c r="F11" t="n">
-        <v>7069.698624</v>
+        <v>6990.677530999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1090.573828</v>
+        <v>1011.552734999999</v>
       </c>
       <c r="J11" t="n">
-        <v>18.24</v>
+        <v>16.92</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7088</v>
+        <v>1.6897</v>
       </c>
       <c r="F12" t="n">
-        <v>10276.842816</v>
+        <v>10161.974079</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1176.953499000001</v>
+        <v>1062.084762</v>
       </c>
       <c r="J12" t="n">
-        <v>12.93</v>
+        <v>11.67</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4648</v>
+        <v>2.4359</v>
       </c>
       <c r="F15" t="n">
-        <v>22922.64</v>
+        <v>22653.87</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3476.34</v>
+        <v>3207.570000000003</v>
       </c>
       <c r="J15" t="n">
-        <v>17.88</v>
+        <v>16.49</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>29.38</v>
+        <v>29.26</v>
       </c>
       <c r="F16" t="n">
-        <v>14690</v>
+        <v>14630</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>875</v>
+        <v>815</v>
       </c>
       <c r="J16" t="n">
-        <v>6.33</v>
+        <v>5.9</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.390000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="F17" t="n">
-        <v>18780</v>
+        <v>18820</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>1020</v>
+        <v>1060</v>
       </c>
       <c r="J17" t="n">
-        <v>5.74</v>
+        <v>5.97</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0749</v>
+        <v>1.0839</v>
       </c>
       <c r="F18" t="n">
-        <v>4222.411431</v>
+        <v>4257.765141000001</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-84.06326600000011</v>
+        <v>-48.70955599999888</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.95</v>
+        <v>-1.13</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5738</v>
+        <v>1.5859</v>
       </c>
       <c r="F19" t="n">
-        <v>13692.06</v>
+        <v>13797.33</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>233.1600000000017</v>
+        <v>338.4300000000003</v>
       </c>
       <c r="J19" t="n">
-        <v>1.73</v>
+        <v>2.51</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1577</v>
+        <v>1.1575</v>
       </c>
       <c r="F20" t="n">
-        <v>9175.768121999999</v>
+        <v>9174.182949999999</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-824.2894400000005</v>
+        <v>-825.8746120000014</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.24</v>
+        <v>-8.26</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2196</v>
+        <v>1.2363</v>
       </c>
       <c r="F21" t="n">
-        <v>13781.48</v>
+        <v>13970.19</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1148.08</v>
+        <v>1336.789999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>9.09</v>
+        <v>10.58</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7634</v>
+        <v>1.7211</v>
       </c>
       <c r="F22" t="n">
-        <v>941.461626</v>
+        <v>918.8780790000001</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>212.3280530000001</v>
+        <v>189.7445060000001</v>
       </c>
       <c r="J22" t="n">
-        <v>29.12</v>
+        <v>26.02</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7634</v>
+        <v>1.7211</v>
       </c>
       <c r="F23" t="n">
-        <v>22786.196316</v>
+        <v>22239.606714</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3585.78285</v>
+        <v>3039.193248</v>
       </c>
       <c r="J23" t="n">
-        <v>18.68</v>
+        <v>15.83</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5842</v>
+        <v>1.5476</v>
       </c>
       <c r="F24" t="n">
-        <v>1036.573744</v>
+        <v>1012.625632</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>236.602112</v>
+        <v>212.6540000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>29.58</v>
+        <v>26.58</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.3187</v>
+        <v>6.1593</v>
       </c>
       <c r="F26" t="n">
-        <v>2624.408858</v>
+        <v>2558.203662</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>524.4082839999996</v>
+        <v>458.2030879999998</v>
       </c>
       <c r="J26" t="n">
-        <v>24.97</v>
+        <v>21.82</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0474</v>
+        <v>1.9979</v>
       </c>
       <c r="F28" t="n">
-        <v>7900.507120000001</v>
+        <v>7709.496520000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1600.630240000001</v>
+        <v>1409.619640000001</v>
       </c>
       <c r="J28" t="n">
-        <v>25.41</v>
+        <v>22.38</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0474</v>
+        <v>1.9979</v>
       </c>
       <c r="F29" t="n">
-        <v>17831.400346</v>
+        <v>17400.290491</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2831.390179000002</v>
+        <v>2400.280324000003</v>
       </c>
       <c r="J29" t="n">
-        <v>18.88</v>
+        <v>16</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1372</v>
+        <v>2.0853</v>
       </c>
       <c r="F30" t="n">
-        <v>11237.589948</v>
+        <v>10964.695077</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2357.201747000001</v>
+        <v>2084.306876000001</v>
       </c>
       <c r="J30" t="n">
-        <v>26.54</v>
+        <v>23.47</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1372</v>
+        <v>2.0853</v>
       </c>
       <c r="F31" t="n">
-        <v>1441.049844</v>
+        <v>1406.055231</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>241.0515249999999</v>
+        <v>206.056912</v>
       </c>
       <c r="J31" t="n">
-        <v>20.09</v>
+        <v>17.17</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4927</v>
+        <v>2.4286</v>
       </c>
       <c r="F33" t="n">
-        <v>15205.47</v>
+        <v>14814.46</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2932.27</v>
+        <v>2541.259999999998</v>
       </c>
       <c r="J33" t="n">
-        <v>23.89</v>
+        <v>20.71</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0057</v>
+        <v>1.9548</v>
       </c>
       <c r="F34" t="n">
-        <v>38308.87</v>
+        <v>37336.68</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>7137.670000000002</v>
+        <v>6165.48</v>
       </c>
       <c r="J34" t="n">
-        <v>22.9</v>
+        <v>19.78</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.833</v>
+        <v>6.6654</v>
       </c>
       <c r="F35" t="n">
-        <v>41588.23454</v>
+        <v>40568.157252</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>8388.248916000004</v>
+        <v>7368.171627999996</v>
       </c>
       <c r="J35" t="n">
-        <v>25.27</v>
+        <v>22.19</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.833</v>
+        <v>6.6654</v>
       </c>
       <c r="F36" t="n">
-        <v>14122.85438</v>
+        <v>13776.448644</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2822.917388</v>
+        <v>2476.511651999999</v>
       </c>
       <c r="J36" t="n">
-        <v>24.98</v>
+        <v>21.92</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.833</v>
+        <v>6.6654</v>
       </c>
       <c r="F37" t="n">
-        <v>102495</v>
+        <v>99981</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>19200</v>
+        <v>16686</v>
       </c>
       <c r="J37" t="n">
-        <v>23.05</v>
+        <v>20.03</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.8666</v>
+        <v>2.7894</v>
       </c>
       <c r="F38" t="n">
-        <v>20849.957106</v>
+        <v>20288.449854</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>5049.928563000001</v>
+        <v>4488.421310999998</v>
       </c>
       <c r="J38" t="n">
-        <v>31.96</v>
+        <v>28.41</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.8666</v>
+        <v>2.7894</v>
       </c>
       <c r="F39" t="n">
-        <v>29892.646806</v>
+        <v>29087.612154</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>6892.84851</v>
+        <v>6087.813858000001</v>
       </c>
       <c r="J39" t="n">
-        <v>29.97</v>
+        <v>26.47</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.3218</v>
+        <v>2.2539</v>
       </c>
       <c r="F40" t="n">
-        <v>15556.06</v>
+        <v>15101.13</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>5104.060000000001</v>
+        <v>4649.129999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>48.83</v>
+        <v>44.48</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7.2</v>
+        <v>7.22</v>
       </c>
       <c r="F42" t="n">
-        <v>7920</v>
+        <v>7942</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1335.4</v>
+        <v>1357.4</v>
       </c>
       <c r="J42" t="n">
-        <v>20.28</v>
+        <v>20.61</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>42.6</v>
+        <v>42.3</v>
       </c>
       <c r="F43" t="n">
-        <v>63900</v>
+        <v>63449.99999999999</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-555</v>
+        <v>-1005.000000000007</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.86</v>
+        <v>-1.56</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8227</v>
+        <v>2.7885</v>
       </c>
       <c r="F2" t="n">
-        <v>2087.922963</v>
+        <v>2062.625565</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>217.6907670000005</v>
+        <v>192.3933690000003</v>
       </c>
       <c r="J2" t="n">
-        <v>11.64</v>
+        <v>10.29</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.597</v>
+        <v>2.5974</v>
       </c>
       <c r="F3" t="n">
-        <v>842.25904</v>
+        <v>842.3887679999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-157.684384</v>
+        <v>-157.5546560000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-15.77</v>
+        <v>-15.76</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1323</v>
+        <v>1.1287</v>
       </c>
       <c r="F4" t="n">
-        <v>6454.110000000001</v>
+        <v>6433.59</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1033.410000000001</v>
+        <v>1012.89</v>
       </c>
       <c r="J4" t="n">
-        <v>19.06</v>
+        <v>18.69</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9044</v>
+        <v>1.8832</v>
       </c>
       <c r="F5" t="n">
-        <v>2258.485092</v>
+        <v>2233.343376</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-141.4814489999994</v>
+        <v>-166.6231649999995</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.9</v>
+        <v>-6.94</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3026</v>
+        <v>1.2941</v>
       </c>
       <c r="F6" t="n">
-        <v>2210.889954</v>
+        <v>2196.462989</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-289.048487</v>
+        <v>-303.4754519999997</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.56</v>
+        <v>-12.14</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3026</v>
+        <v>1.2941</v>
       </c>
       <c r="F7" t="n">
-        <v>4681.67466</v>
+        <v>4651.12481</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-638.3121600000004</v>
+        <v>-668.8620099999998</v>
       </c>
       <c r="J7" t="n">
-        <v>-12</v>
+        <v>-12.57</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1579</v>
+        <v>2.1299</v>
       </c>
       <c r="F8" t="n">
-        <v>27836.91</v>
+        <v>27475.71</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8538.510000000002</v>
+        <v>8177.310000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>44.24</v>
+        <v>42.37</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1206</v>
+        <v>3.1319</v>
       </c>
       <c r="F9" t="n">
-        <v>944.948886</v>
+        <v>948.370639</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>196.008913</v>
+        <v>199.430666</v>
       </c>
       <c r="J9" t="n">
-        <v>26.17</v>
+        <v>26.63</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2375</v>
+        <v>2.2449</v>
       </c>
       <c r="F10" t="n">
-        <v>2327.962125</v>
+        <v>2335.661307</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>327.943536</v>
+        <v>335.6427179999998</v>
       </c>
       <c r="J10" t="n">
-        <v>16.4</v>
+        <v>16.78</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6897</v>
+        <v>1.6963</v>
       </c>
       <c r="F11" t="n">
-        <v>6990.677530999999</v>
+        <v>7017.983248999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1011.552734999999</v>
+        <v>1038.858452999999</v>
       </c>
       <c r="J11" t="n">
-        <v>16.92</v>
+        <v>17.37</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6897</v>
+        <v>1.6963</v>
       </c>
       <c r="F12" t="n">
-        <v>10161.974079</v>
+        <v>10201.666941</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1062.084762</v>
+        <v>1101.777624</v>
       </c>
       <c r="J12" t="n">
-        <v>11.67</v>
+        <v>12.11</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4359</v>
+        <v>2.4454</v>
       </c>
       <c r="F15" t="n">
-        <v>22653.87</v>
+        <v>22742.22</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3207.570000000003</v>
+        <v>3295.919999999998</v>
       </c>
       <c r="J15" t="n">
-        <v>16.49</v>
+        <v>16.95</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>29.26</v>
+        <v>29.54</v>
       </c>
       <c r="F16" t="n">
-        <v>14630</v>
+        <v>14770</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>815</v>
+        <v>955</v>
       </c>
       <c r="J16" t="n">
-        <v>5.9</v>
+        <v>6.91</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.41</v>
+        <v>9.57</v>
       </c>
       <c r="F17" t="n">
-        <v>18820</v>
+        <v>19140</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>1060</v>
+        <v>1380</v>
       </c>
       <c r="J17" t="n">
-        <v>5.97</v>
+        <v>7.77</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0839</v>
+        <v>1.0764</v>
       </c>
       <c r="F18" t="n">
-        <v>4257.765141000001</v>
+        <v>4228.303716</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-48.70955599999888</v>
+        <v>-78.1709809999993</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.13</v>
+        <v>-1.82</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5859</v>
+        <v>1.5673</v>
       </c>
       <c r="F19" t="n">
-        <v>13797.33</v>
+        <v>13635.51</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>338.4300000000003</v>
+        <v>176.6099999999988</v>
       </c>
       <c r="J19" t="n">
-        <v>2.51</v>
+        <v>1.31</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1575</v>
+        <v>1.1461</v>
       </c>
       <c r="F20" t="n">
-        <v>9174.182949999999</v>
+        <v>9083.828145999998</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-825.8746120000014</v>
+        <v>-916.2294160000019</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.26</v>
+        <v>-9.16</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2363</v>
+        <v>1.2237</v>
       </c>
       <c r="F21" t="n">
-        <v>13970.19</v>
+        <v>13827.81</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1336.789999999999</v>
+        <v>1194.41</v>
       </c>
       <c r="J21" t="n">
-        <v>10.58</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7211</v>
+        <v>1.7396</v>
       </c>
       <c r="F22" t="n">
-        <v>918.8780790000001</v>
+        <v>928.755044</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>189.7445060000001</v>
+        <v>199.621471</v>
       </c>
       <c r="J22" t="n">
-        <v>26.02</v>
+        <v>27.38</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7211</v>
+        <v>1.7396</v>
       </c>
       <c r="F23" t="n">
-        <v>22239.606714</v>
+        <v>22478.658904</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3039.193248</v>
+        <v>3278.245437999998</v>
       </c>
       <c r="J23" t="n">
-        <v>15.83</v>
+        <v>17.07</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5476</v>
+        <v>1.5636</v>
       </c>
       <c r="F24" t="n">
-        <v>1012.625632</v>
+        <v>1023.094752</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>212.6540000000001</v>
+        <v>223.1231200000002</v>
       </c>
       <c r="J24" t="n">
-        <v>26.58</v>
+        <v>27.89</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.1593</v>
+        <v>6.2286</v>
       </c>
       <c r="F26" t="n">
-        <v>2558.203662</v>
+        <v>2586.986724</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>458.2030879999998</v>
+        <v>486.9861499999997</v>
       </c>
       <c r="J26" t="n">
-        <v>21.82</v>
+        <v>23.19</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9979</v>
+        <v>2.0197</v>
       </c>
       <c r="F28" t="n">
-        <v>7709.496520000001</v>
+        <v>7793.618359999999</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1409.619640000001</v>
+        <v>1493.74148</v>
       </c>
       <c r="J28" t="n">
-        <v>22.38</v>
+        <v>23.71</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9979</v>
+        <v>2.0197</v>
       </c>
       <c r="F29" t="n">
-        <v>17400.290491</v>
+        <v>17590.153013</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2400.280324000003</v>
+        <v>2590.142845999999</v>
       </c>
       <c r="J29" t="n">
-        <v>16</v>
+        <v>17.27</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0853</v>
+        <v>2.108</v>
       </c>
       <c r="F30" t="n">
-        <v>10964.695077</v>
+        <v>11084.05372</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2084.306876000001</v>
+        <v>2203.665519000002</v>
       </c>
       <c r="J30" t="n">
-        <v>23.47</v>
+        <v>24.81</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.0853</v>
+        <v>2.108</v>
       </c>
       <c r="F31" t="n">
-        <v>1406.055231</v>
+        <v>1421.36116</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>206.056912</v>
+        <v>221.3628409999999</v>
       </c>
       <c r="J31" t="n">
-        <v>17.17</v>
+        <v>18.45</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4286</v>
+        <v>2.455</v>
       </c>
       <c r="F33" t="n">
-        <v>14814.46</v>
+        <v>14975.5</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2541.259999999998</v>
+        <v>2702.299999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>20.71</v>
+        <v>22.02</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9548</v>
+        <v>1.977</v>
       </c>
       <c r="F34" t="n">
-        <v>37336.68</v>
+        <v>37760.7</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6165.48</v>
+        <v>6589.500000000004</v>
       </c>
       <c r="J34" t="n">
-        <v>19.78</v>
+        <v>21.14</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.6654</v>
+        <v>6.7387</v>
       </c>
       <c r="F35" t="n">
-        <v>40568.157252</v>
+        <v>41014.288906</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>7368.171627999996</v>
+        <v>7814.303282000001</v>
       </c>
       <c r="J35" t="n">
-        <v>22.19</v>
+        <v>23.54</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.6654</v>
+        <v>6.7387</v>
       </c>
       <c r="F36" t="n">
-        <v>13776.448644</v>
+        <v>13927.949482</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2476.511651999999</v>
+        <v>2628.012489999999</v>
       </c>
       <c r="J36" t="n">
-        <v>21.92</v>
+        <v>23.26</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.6654</v>
+        <v>6.7387</v>
       </c>
       <c r="F37" t="n">
-        <v>99981</v>
+        <v>101080.5</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>16686</v>
+        <v>17785.5</v>
       </c>
       <c r="J37" t="n">
-        <v>20.03</v>
+        <v>21.35</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.7894</v>
+        <v>2.8166</v>
       </c>
       <c r="F38" t="n">
-        <v>20288.449854</v>
+        <v>20486.286606</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>4488.421310999998</v>
+        <v>4686.258063000001</v>
       </c>
       <c r="J38" t="n">
-        <v>28.41</v>
+        <v>29.66</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.7894</v>
+        <v>2.8166</v>
       </c>
       <c r="F39" t="n">
-        <v>29087.612154</v>
+        <v>29371.251306</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>6087.813858000001</v>
+        <v>6371.453010000001</v>
       </c>
       <c r="J39" t="n">
-        <v>26.47</v>
+        <v>27.7</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.2539</v>
+        <v>2.2779</v>
       </c>
       <c r="F40" t="n">
-        <v>15101.13</v>
+        <v>15261.93</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4649.129999999999</v>
+        <v>4809.929999999998</v>
       </c>
       <c r="J40" t="n">
-        <v>44.48</v>
+        <v>46.02</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.470000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="F41" t="n">
-        <v>8470</v>
+        <v>8600</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1361</v>
+        <v>1491</v>
       </c>
       <c r="J41" t="n">
-        <v>19.14</v>
+        <v>20.97</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7.22</v>
+        <v>7.47</v>
       </c>
       <c r="F42" t="n">
-        <v>7942</v>
+        <v>8217</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1357.4</v>
+        <v>1632.4</v>
       </c>
       <c r="J42" t="n">
-        <v>20.61</v>
+        <v>24.79</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>42.3</v>
+        <v>42.95</v>
       </c>
       <c r="F43" t="n">
-        <v>63449.99999999999</v>
+        <v>64425.00000000001</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-1005.000000000007</v>
+        <v>-29.99999999999272</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.56</v>
+        <v>-0.05</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7885</v>
+        <v>2.781</v>
       </c>
       <c r="F2" t="n">
-        <v>2062.625565</v>
+        <v>2057.07789</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>192.3933690000003</v>
+        <v>186.8456940000005</v>
       </c>
       <c r="J2" t="n">
-        <v>10.29</v>
+        <v>9.99</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5974</v>
+        <v>2.5683</v>
       </c>
       <c r="F3" t="n">
-        <v>842.3887679999999</v>
+        <v>832.9510559999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-157.5546560000001</v>
+        <v>-166.9923680000002</v>
       </c>
       <c r="J3" t="n">
-        <v>-15.76</v>
+        <v>-16.7</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1287</v>
+        <v>1.1205</v>
       </c>
       <c r="F4" t="n">
-        <v>6433.59</v>
+        <v>6386.85</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1012.89</v>
+        <v>966.1500000000005</v>
       </c>
       <c r="J4" t="n">
-        <v>18.69</v>
+        <v>17.82</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8832</v>
+        <v>1.8803</v>
       </c>
       <c r="F5" t="n">
-        <v>2233.343376</v>
+        <v>2229.904179</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-166.6231649999995</v>
+        <v>-170.0623619999997</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.94</v>
+        <v>-7.09</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2941</v>
+        <v>1.2939</v>
       </c>
       <c r="F6" t="n">
-        <v>2196.462989</v>
+        <v>2196.123531</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-303.4754519999997</v>
+        <v>-303.8149099999996</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.14</v>
+        <v>-12.15</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2941</v>
+        <v>1.2939</v>
       </c>
       <c r="F7" t="n">
-        <v>4651.12481</v>
+        <v>4650.40599</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-668.8620099999998</v>
+        <v>-669.5808299999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-12.57</v>
+        <v>-12.59</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1299</v>
+        <v>2.1459</v>
       </c>
       <c r="F8" t="n">
-        <v>27475.71</v>
+        <v>27682.11</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8177.310000000001</v>
+        <v>8383.709999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>42.37</v>
+        <v>43.44</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1319</v>
+        <v>3.14</v>
       </c>
       <c r="F9" t="n">
-        <v>948.370639</v>
+        <v>950.8234</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>199.430666</v>
+        <v>201.883427</v>
       </c>
       <c r="J9" t="n">
-        <v>26.63</v>
+        <v>26.96</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2449</v>
+        <v>2.25</v>
       </c>
       <c r="F10" t="n">
-        <v>2335.661307</v>
+        <v>2340.9675</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>335.6427179999998</v>
+        <v>340.9489110000002</v>
       </c>
       <c r="J10" t="n">
-        <v>16.78</v>
+        <v>17.05</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6963</v>
+        <v>1.7003</v>
       </c>
       <c r="F11" t="n">
-        <v>7017.983248999999</v>
+        <v>7034.532168999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1038.858452999999</v>
+        <v>1055.407372999999</v>
       </c>
       <c r="J11" t="n">
-        <v>17.37</v>
+        <v>17.65</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6963</v>
+        <v>1.7003</v>
       </c>
       <c r="F12" t="n">
-        <v>10201.666941</v>
+        <v>10225.723221</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1101.777624</v>
+        <v>1125.833903999999</v>
       </c>
       <c r="J12" t="n">
-        <v>12.11</v>
+        <v>12.37</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4454</v>
+        <v>2.4519</v>
       </c>
       <c r="F15" t="n">
-        <v>22742.22</v>
+        <v>22802.67</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3295.919999999998</v>
+        <v>3356.370000000003</v>
       </c>
       <c r="J15" t="n">
-        <v>16.95</v>
+        <v>17.26</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>29.54</v>
+        <v>29.7</v>
       </c>
       <c r="F16" t="n">
-        <v>14770</v>
+        <v>14850</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>955</v>
+        <v>1035</v>
       </c>
       <c r="J16" t="n">
-        <v>6.91</v>
+        <v>7.49</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.57</v>
+        <v>9.5</v>
       </c>
       <c r="F17" t="n">
-        <v>19140</v>
+        <v>19000</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>1380</v>
+        <v>1240</v>
       </c>
       <c r="J17" t="n">
-        <v>7.77</v>
+        <v>6.98</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0764</v>
+        <v>1.0624</v>
       </c>
       <c r="F18" t="n">
-        <v>4228.303716</v>
+        <v>4173.309056</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-78.1709809999993</v>
+        <v>-133.1656409999996</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.82</v>
+        <v>-3.09</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5673</v>
+        <v>1.5517</v>
       </c>
       <c r="F19" t="n">
-        <v>13635.51</v>
+        <v>13499.79</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>176.6099999999988</v>
+        <v>40.89000000000124</v>
       </c>
       <c r="J19" t="n">
-        <v>1.31</v>
+        <v>0.3</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1461</v>
+        <v>1.1353</v>
       </c>
       <c r="F20" t="n">
-        <v>9083.828145999998</v>
+        <v>8998.228857999999</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-916.2294160000019</v>
+        <v>-1001.828704000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.16</v>
+        <v>-10.02</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2237</v>
+        <v>1.2111</v>
       </c>
       <c r="F21" t="n">
-        <v>13827.81</v>
+        <v>13685.43</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1194.41</v>
+        <v>1052.030000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>9.449999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7396</v>
+        <v>1.7372</v>
       </c>
       <c r="F22" t="n">
-        <v>928.755044</v>
+        <v>927.473708</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>199.621471</v>
+        <v>198.340135</v>
       </c>
       <c r="J22" t="n">
-        <v>27.38</v>
+        <v>27.2</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7396</v>
+        <v>1.7372</v>
       </c>
       <c r="F23" t="n">
-        <v>22478.658904</v>
+        <v>22447.646728</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3278.245437999998</v>
+        <v>3247.233261999998</v>
       </c>
       <c r="J23" t="n">
-        <v>17.07</v>
+        <v>16.91</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5636</v>
+        <v>1.5616</v>
       </c>
       <c r="F24" t="n">
-        <v>1023.094752</v>
+        <v>1021.786112</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>223.1231200000002</v>
+        <v>221.8144800000001</v>
       </c>
       <c r="J24" t="n">
-        <v>27.89</v>
+        <v>27.73</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.2286</v>
+        <v>6.2192</v>
       </c>
       <c r="F26" t="n">
-        <v>2586.986724</v>
+        <v>2583.082528</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>486.9861499999997</v>
+        <v>483.0819539999998</v>
       </c>
       <c r="J26" t="n">
-        <v>23.19</v>
+        <v>23</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0197</v>
+        <v>2.0168</v>
       </c>
       <c r="F28" t="n">
-        <v>7793.618359999999</v>
+        <v>7782.42784</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1493.74148</v>
+        <v>1482.55096</v>
       </c>
       <c r="J28" t="n">
-        <v>23.71</v>
+        <v>23.53</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0197</v>
+        <v>2.0168</v>
       </c>
       <c r="F29" t="n">
-        <v>17590.153013</v>
+        <v>17564.896072</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2590.142845999999</v>
+        <v>2564.885904999999</v>
       </c>
       <c r="J29" t="n">
-        <v>17.27</v>
+        <v>17.1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.108</v>
+        <v>2.105</v>
       </c>
       <c r="F30" t="n">
-        <v>11084.05372</v>
+        <v>11068.27945</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2203.665519000002</v>
+        <v>2187.891249</v>
       </c>
       <c r="J30" t="n">
-        <v>24.81</v>
+        <v>24.64</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.108</v>
+        <v>2.105</v>
       </c>
       <c r="F31" t="n">
-        <v>1421.36116</v>
+        <v>1419.33835</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>221.3628409999999</v>
+        <v>219.340031</v>
       </c>
       <c r="J31" t="n">
-        <v>18.45</v>
+        <v>18.28</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.455</v>
+        <v>2.4507</v>
       </c>
       <c r="F33" t="n">
-        <v>14975.5</v>
+        <v>14949.27</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2702.299999999999</v>
+        <v>2676.069999999998</v>
       </c>
       <c r="J33" t="n">
-        <v>22.02</v>
+        <v>21.8</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.977</v>
+        <v>1.9741</v>
       </c>
       <c r="F34" t="n">
-        <v>37760.7</v>
+        <v>37705.31</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6589.500000000004</v>
+        <v>6534.109999999997</v>
       </c>
       <c r="J34" t="n">
-        <v>21.14</v>
+        <v>20.96</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.7387</v>
+        <v>6.7164</v>
       </c>
       <c r="F35" t="n">
-        <v>41014.288906</v>
+        <v>40878.562632</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>7814.303282000001</v>
+        <v>7678.577008</v>
       </c>
       <c r="J35" t="n">
-        <v>23.54</v>
+        <v>23.13</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.7387</v>
+        <v>6.7164</v>
       </c>
       <c r="F36" t="n">
-        <v>13927.949482</v>
+        <v>13881.858504</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2628.012489999999</v>
+        <v>2581.921512000001</v>
       </c>
       <c r="J36" t="n">
-        <v>23.26</v>
+        <v>22.85</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.7387</v>
+        <v>6.7164</v>
       </c>
       <c r="F37" t="n">
-        <v>101080.5</v>
+        <v>100746</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>17785.5</v>
+        <v>17451</v>
       </c>
       <c r="J37" t="n">
-        <v>21.35</v>
+        <v>20.95</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.8166</v>
+        <v>2.7915</v>
       </c>
       <c r="F38" t="n">
-        <v>20486.286606</v>
+        <v>20303.724015</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>4686.258063000001</v>
+        <v>4503.695471999999</v>
       </c>
       <c r="J38" t="n">
-        <v>29.66</v>
+        <v>28.5</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.8166</v>
+        <v>2.7915</v>
       </c>
       <c r="F39" t="n">
-        <v>29371.251306</v>
+        <v>29109.510765</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>6371.453010000001</v>
+        <v>6109.712468999998</v>
       </c>
       <c r="J39" t="n">
-        <v>27.7</v>
+        <v>26.56</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.2779</v>
+        <v>2.2645</v>
       </c>
       <c r="F40" t="n">
-        <v>15261.93</v>
+        <v>15172.15</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4809.929999999998</v>
+        <v>4720.15</v>
       </c>
       <c r="J40" t="n">
-        <v>46.02</v>
+        <v>45.16</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.6</v>
+        <v>8.43</v>
       </c>
       <c r="F41" t="n">
-        <v>8600</v>
+        <v>8430</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1491</v>
+        <v>1321</v>
       </c>
       <c r="J41" t="n">
-        <v>20.97</v>
+        <v>18.58</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7.47</v>
+        <v>7.28</v>
       </c>
       <c r="F42" t="n">
-        <v>8217</v>
+        <v>8008</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1632.4</v>
+        <v>1423.4</v>
       </c>
       <c r="J42" t="n">
-        <v>24.79</v>
+        <v>21.62</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>42.95</v>
+        <v>42.6</v>
       </c>
       <c r="F43" t="n">
-        <v>64425.00000000001</v>
+        <v>63900</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-29.99999999999272</v>
+        <v>-555</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.05</v>
+        <v>-0.86</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.781</v>
+        <v>2.7592</v>
       </c>
       <c r="F2" t="n">
-        <v>2057.07789</v>
+        <v>2040.952648</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>186.8456940000005</v>
+        <v>170.720452</v>
       </c>
       <c r="J2" t="n">
-        <v>9.99</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5683</v>
+        <v>2.5467</v>
       </c>
       <c r="F3" t="n">
-        <v>832.9510559999999</v>
+        <v>825.945744</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-166.9923680000002</v>
+        <v>-173.9976800000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-16.7</v>
+        <v>-17.4</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1205</v>
+        <v>1.0975</v>
       </c>
       <c r="F4" t="n">
-        <v>6386.85</v>
+        <v>6255.749999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>966.1500000000005</v>
+        <v>835.0499999999993</v>
       </c>
       <c r="J4" t="n">
-        <v>17.82</v>
+        <v>15.4</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8803</v>
+        <v>1.9049</v>
       </c>
       <c r="F5" t="n">
-        <v>2229.904179</v>
+        <v>2259.078057</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-170.0623619999997</v>
+        <v>-140.8884839999996</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.09</v>
+        <v>-5.87</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2939</v>
+        <v>1.2876</v>
       </c>
       <c r="F6" t="n">
-        <v>2196.123531</v>
+        <v>2185.430604</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-303.8149099999996</v>
+        <v>-314.5078369999997</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.15</v>
+        <v>-12.58</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2939</v>
+        <v>1.2876</v>
       </c>
       <c r="F7" t="n">
-        <v>4650.40599</v>
+        <v>4627.76316</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-669.5808299999999</v>
+        <v>-692.2236599999997</v>
       </c>
       <c r="J7" t="n">
-        <v>-12.59</v>
+        <v>-13.01</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1459</v>
+        <v>2.1036</v>
       </c>
       <c r="F8" t="n">
-        <v>27682.11</v>
+        <v>27136.44</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8383.709999999999</v>
+        <v>7838.040000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>43.44</v>
+        <v>40.61</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.14</v>
+        <v>3.1568</v>
       </c>
       <c r="F9" t="n">
-        <v>950.8234</v>
+        <v>955.910608</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>201.883427</v>
+        <v>206.970635</v>
       </c>
       <c r="J9" t="n">
-        <v>26.96</v>
+        <v>27.64</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.25</v>
+        <v>2.2605</v>
       </c>
       <c r="F10" t="n">
-        <v>2340.9675</v>
+        <v>2351.892015</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>340.9489110000002</v>
+        <v>351.8734259999999</v>
       </c>
       <c r="J10" t="n">
-        <v>17.05</v>
+        <v>17.59</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7003</v>
+        <v>1.7094</v>
       </c>
       <c r="F11" t="n">
-        <v>7034.532168999999</v>
+        <v>7072.180961999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1055.407372999999</v>
+        <v>1093.056165999999</v>
       </c>
       <c r="J11" t="n">
-        <v>17.65</v>
+        <v>18.28</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7003</v>
+        <v>1.7094</v>
       </c>
       <c r="F12" t="n">
-        <v>10225.723221</v>
+        <v>10280.451258</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1125.833903999999</v>
+        <v>1180.561941</v>
       </c>
       <c r="J12" t="n">
-        <v>12.37</v>
+        <v>12.97</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4519</v>
+        <v>2.4659</v>
       </c>
       <c r="F15" t="n">
-        <v>22802.67</v>
+        <v>22932.87</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3356.370000000003</v>
+        <v>3486.57</v>
       </c>
       <c r="J15" t="n">
-        <v>17.26</v>
+        <v>17.93</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>29.7</v>
+        <v>29.57</v>
       </c>
       <c r="F16" t="n">
-        <v>14850</v>
+        <v>14785</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>1035</v>
+        <v>970</v>
       </c>
       <c r="J16" t="n">
-        <v>7.49</v>
+        <v>7.02</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.5</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>19000</v>
+        <v>18920</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>1240</v>
+        <v>1160</v>
       </c>
       <c r="J17" t="n">
-        <v>6.98</v>
+        <v>6.53</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0624</v>
+        <v>1.0602</v>
       </c>
       <c r="F18" t="n">
-        <v>4173.309056</v>
+        <v>4164.667038000001</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-133.1656409999996</v>
+        <v>-141.8076589999991</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.09</v>
+        <v>-3.29</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5517</v>
+        <v>1.5261</v>
       </c>
       <c r="F19" t="n">
-        <v>13499.79</v>
+        <v>13277.07</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>40.89000000000124</v>
+        <v>-181.8299999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3</v>
+        <v>-1.35</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1353</v>
+        <v>1.1094</v>
       </c>
       <c r="F20" t="n">
-        <v>8998.228857999999</v>
+        <v>8792.949084</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-1001.828704000001</v>
+        <v>-1207.108478</v>
       </c>
       <c r="J20" t="n">
-        <v>-10.02</v>
+        <v>-12.07</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2111</v>
+        <v>1.2017</v>
       </c>
       <c r="F21" t="n">
-        <v>13685.43</v>
+        <v>13579.21</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1052.030000000001</v>
+        <v>945.8099999999995</v>
       </c>
       <c r="J21" t="n">
-        <v>8.33</v>
+        <v>7.49</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7372</v>
+        <v>1.7554</v>
       </c>
       <c r="F22" t="n">
-        <v>927.473708</v>
+        <v>937.190506</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>198.340135</v>
+        <v>208.0569330000001</v>
       </c>
       <c r="J22" t="n">
-        <v>27.2</v>
+        <v>28.53</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7372</v>
+        <v>1.7554</v>
       </c>
       <c r="F23" t="n">
-        <v>22447.646728</v>
+        <v>22682.822396</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3247.233261999998</v>
+        <v>3482.408929999998</v>
       </c>
       <c r="J23" t="n">
-        <v>16.91</v>
+        <v>18.14</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5616</v>
+        <v>1.5774</v>
       </c>
       <c r="F24" t="n">
-        <v>1021.786112</v>
+        <v>1032.124368</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>221.8144800000001</v>
+        <v>232.152736</v>
       </c>
       <c r="J24" t="n">
-        <v>27.73</v>
+        <v>29.02</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.2192</v>
+        <v>6.288</v>
       </c>
       <c r="F26" t="n">
-        <v>2583.082528</v>
+        <v>2611.65792</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>483.0819539999998</v>
+        <v>511.657346</v>
       </c>
       <c r="J26" t="n">
-        <v>23</v>
+        <v>24.36</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0168</v>
+        <v>2.0382</v>
       </c>
       <c r="F28" t="n">
-        <v>7782.42784</v>
+        <v>7865.00616</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1482.55096</v>
+        <v>1565.12928</v>
       </c>
       <c r="J28" t="n">
-        <v>23.53</v>
+        <v>24.84</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0168</v>
+        <v>2.0382</v>
       </c>
       <c r="F29" t="n">
-        <v>17564.896072</v>
+        <v>17751.274878</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2564.885904999999</v>
+        <v>2751.264711</v>
       </c>
       <c r="J29" t="n">
-        <v>17.1</v>
+        <v>18.34</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.105</v>
+        <v>2.1272</v>
       </c>
       <c r="F30" t="n">
-        <v>11068.27945</v>
+        <v>11185.009048</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2187.891249</v>
+        <v>2304.620847000002</v>
       </c>
       <c r="J30" t="n">
-        <v>24.64</v>
+        <v>25.95</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.105</v>
+        <v>2.1272</v>
       </c>
       <c r="F31" t="n">
-        <v>1419.33835</v>
+        <v>1434.307144</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>219.340031</v>
+        <v>234.3088250000001</v>
       </c>
       <c r="J31" t="n">
-        <v>18.28</v>
+        <v>19.53</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4507</v>
+        <v>2.478</v>
       </c>
       <c r="F33" t="n">
-        <v>14949.27</v>
+        <v>15115.8</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2676.069999999998</v>
+        <v>2842.6</v>
       </c>
       <c r="J33" t="n">
-        <v>21.8</v>
+        <v>23.16</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9741</v>
+        <v>1.996</v>
       </c>
       <c r="F34" t="n">
-        <v>37705.31</v>
+        <v>38123.6</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6534.109999999997</v>
+        <v>6952.399999999998</v>
       </c>
       <c r="J34" t="n">
-        <v>20.96</v>
+        <v>22.3</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.7164</v>
+        <v>6.8172</v>
       </c>
       <c r="F35" t="n">
-        <v>40878.562632</v>
+        <v>41492.069736</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>7678.577008</v>
+        <v>8292.084111999997</v>
       </c>
       <c r="J35" t="n">
-        <v>23.13</v>
+        <v>24.98</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.7164</v>
+        <v>6.8172</v>
       </c>
       <c r="F36" t="n">
-        <v>13881.858504</v>
+        <v>14090.197992</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2581.921512000001</v>
+        <v>2790.260999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>22.85</v>
+        <v>24.69</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.7164</v>
+        <v>6.8172</v>
       </c>
       <c r="F37" t="n">
-        <v>100746</v>
+        <v>102258</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>17451</v>
+        <v>18963</v>
       </c>
       <c r="J37" t="n">
-        <v>20.95</v>
+        <v>22.77</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.7915</v>
+        <v>2.8118</v>
       </c>
       <c r="F38" t="n">
-        <v>20303.724015</v>
+        <v>20451.374238</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>4503.695471999999</v>
+        <v>4651.345695</v>
       </c>
       <c r="J38" t="n">
-        <v>28.5</v>
+        <v>29.44</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.7915</v>
+        <v>2.8118</v>
       </c>
       <c r="F39" t="n">
-        <v>29109.510765</v>
+        <v>29321.197338</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>6109.712468999998</v>
+        <v>6321.399041999997</v>
       </c>
       <c r="J39" t="n">
-        <v>26.56</v>
+        <v>27.48</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.2645</v>
+        <v>2.288</v>
       </c>
       <c r="F40" t="n">
-        <v>15172.15</v>
+        <v>15329.6</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4720.15</v>
+        <v>4877.599999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>45.16</v>
+        <v>46.67</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.43</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>8430</v>
+        <v>8460</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1321</v>
+        <v>1351</v>
       </c>
       <c r="J41" t="n">
-        <v>18.58</v>
+        <v>19</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7.28</v>
+        <v>7.3</v>
       </c>
       <c r="F42" t="n">
-        <v>8008</v>
+        <v>8030</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1423.4</v>
+        <v>1445.4</v>
       </c>
       <c r="J42" t="n">
-        <v>21.62</v>
+        <v>21.95</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>42.6</v>
+        <v>41.87</v>
       </c>
       <c r="F43" t="n">
-        <v>63900</v>
+        <v>62804.99999999999</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-555</v>
+        <v>-1650.000000000007</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.86</v>
+        <v>-2.56</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7592</v>
+        <v>2.7082</v>
       </c>
       <c r="F2" t="n">
-        <v>2040.952648</v>
+        <v>2003.228458</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>170.720452</v>
+        <v>132.9962620000003</v>
       </c>
       <c r="J2" t="n">
-        <v>9.130000000000001</v>
+        <v>7.11</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5467</v>
+        <v>2.468</v>
       </c>
       <c r="F3" t="n">
-        <v>825.945744</v>
+        <v>800.4217599999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-173.9976800000001</v>
+        <v>-199.5216640000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-17.4</v>
+        <v>-19.95</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0975</v>
+        <v>1.1201</v>
       </c>
       <c r="F4" t="n">
-        <v>6255.749999999999</v>
+        <v>6384.570000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>835.0499999999993</v>
+        <v>963.8700000000008</v>
       </c>
       <c r="J4" t="n">
-        <v>15.4</v>
+        <v>17.78</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9049</v>
+        <v>1.8868</v>
       </c>
       <c r="F5" t="n">
-        <v>2259.078057</v>
+        <v>2237.612724</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-140.8884839999996</v>
+        <v>-162.3538169999997</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.87</v>
+        <v>-6.76</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2876</v>
+        <v>1.2776</v>
       </c>
       <c r="F6" t="n">
-        <v>2185.430604</v>
+        <v>2168.457704</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-314.5078369999997</v>
+        <v>-331.4807369999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.58</v>
+        <v>-13.26</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2876</v>
+        <v>1.2776</v>
       </c>
       <c r="F7" t="n">
-        <v>4627.76316</v>
+        <v>4591.82216</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-692.2236599999997</v>
+        <v>-728.1646600000004</v>
       </c>
       <c r="J7" t="n">
-        <v>-13.01</v>
+        <v>-13.69</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1036</v>
+        <v>2.0965</v>
       </c>
       <c r="F8" t="n">
-        <v>27136.44</v>
+        <v>27044.85</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>7838.040000000001</v>
+        <v>7746.449999999997</v>
       </c>
       <c r="J8" t="n">
-        <v>40.61</v>
+        <v>40.14</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1568</v>
+        <v>3.1208</v>
       </c>
       <c r="F9" t="n">
-        <v>955.910608</v>
+        <v>945.009448</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>206.970635</v>
+        <v>196.069475</v>
       </c>
       <c r="J9" t="n">
-        <v>27.64</v>
+        <v>26.18</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2605</v>
+        <v>2.2361</v>
       </c>
       <c r="F10" t="n">
-        <v>2351.892015</v>
+        <v>2326.505523</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>351.8734259999999</v>
+        <v>326.4869340000002</v>
       </c>
       <c r="J10" t="n">
-        <v>17.59</v>
+        <v>16.32</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7094</v>
+        <v>1.6894</v>
       </c>
       <c r="F11" t="n">
-        <v>7072.180961999999</v>
+        <v>6989.436361999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1093.056165999999</v>
+        <v>1010.311565999999</v>
       </c>
       <c r="J11" t="n">
-        <v>18.28</v>
+        <v>16.9</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7094</v>
+        <v>1.6894</v>
       </c>
       <c r="F12" t="n">
-        <v>10280.451258</v>
+        <v>10160.169858</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1180.561941</v>
+        <v>1060.280541</v>
       </c>
       <c r="J12" t="n">
-        <v>12.97</v>
+        <v>11.65</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4659</v>
+        <v>2.4355</v>
       </c>
       <c r="F15" t="n">
-        <v>22932.87</v>
+        <v>22650.15</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3486.57</v>
+        <v>3203.850000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>17.93</v>
+        <v>16.48</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>29.57</v>
+        <v>29.7</v>
       </c>
       <c r="F16" t="n">
-        <v>14785</v>
+        <v>14850</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>970</v>
+        <v>1035</v>
       </c>
       <c r="J16" t="n">
-        <v>7.02</v>
+        <v>7.49</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.460000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="F17" t="n">
-        <v>18920</v>
+        <v>18840</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>1160</v>
+        <v>1080</v>
       </c>
       <c r="J17" t="n">
-        <v>6.53</v>
+        <v>6.08</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0602</v>
+        <v>1.0568</v>
       </c>
       <c r="F18" t="n">
-        <v>4164.667038000001</v>
+        <v>4151.311192</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-141.8076589999991</v>
+        <v>-155.1635049999995</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.29</v>
+        <v>-3.6</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5261</v>
+        <v>1.5256</v>
       </c>
       <c r="F19" t="n">
-        <v>13277.07</v>
+        <v>13272.72</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-181.8299999999999</v>
+        <v>-186.1799999999985</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.35</v>
+        <v>-1.38</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1094</v>
+        <v>1.109</v>
       </c>
       <c r="F20" t="n">
-        <v>8792.949084</v>
+        <v>8789.77874</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-1207.108478</v>
+        <v>-1210.278822</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.07</v>
+        <v>-12.1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2017</v>
+        <v>1.1973</v>
       </c>
       <c r="F21" t="n">
-        <v>13579.21</v>
+        <v>13529.49</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>945.8099999999995</v>
+        <v>896.0900000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>7.49</v>
+        <v>7.09</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7554</v>
+        <v>1.7076</v>
       </c>
       <c r="F22" t="n">
-        <v>937.190506</v>
+        <v>911.670564</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>208.0569330000001</v>
+        <v>182.5369910000001</v>
       </c>
       <c r="J22" t="n">
-        <v>28.53</v>
+        <v>25.03</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7554</v>
+        <v>1.7076</v>
       </c>
       <c r="F23" t="n">
-        <v>22682.822396</v>
+        <v>22065.163224</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3482.408929999998</v>
+        <v>2864.749757999998</v>
       </c>
       <c r="J23" t="n">
-        <v>18.14</v>
+        <v>14.92</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5774</v>
+        <v>1.5358</v>
       </c>
       <c r="F24" t="n">
-        <v>1032.124368</v>
+        <v>1004.904656</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>232.152736</v>
+        <v>204.9330240000002</v>
       </c>
       <c r="J24" t="n">
-        <v>29.02</v>
+        <v>25.62</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.288</v>
+        <v>6.1077</v>
       </c>
       <c r="F26" t="n">
-        <v>2611.65792</v>
+        <v>2536.772118</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>511.657346</v>
+        <v>436.7715439999997</v>
       </c>
       <c r="J26" t="n">
-        <v>24.36</v>
+        <v>20.8</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0382</v>
+        <v>1.9821</v>
       </c>
       <c r="F28" t="n">
-        <v>7865.00616</v>
+        <v>7648.527480000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1565.12928</v>
+        <v>1348.650600000001</v>
       </c>
       <c r="J28" t="n">
-        <v>24.84</v>
+        <v>21.41</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0382</v>
+        <v>1.9821</v>
       </c>
       <c r="F29" t="n">
-        <v>17751.274878</v>
+        <v>17262.683709</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2751.264711</v>
+        <v>2262.673542</v>
       </c>
       <c r="J29" t="n">
-        <v>18.34</v>
+        <v>15.08</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1272</v>
+        <v>2.0686</v>
       </c>
       <c r="F30" t="n">
-        <v>11185.009048</v>
+        <v>10876.884974</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2304.620847000002</v>
+        <v>1996.496773000001</v>
       </c>
       <c r="J30" t="n">
-        <v>25.95</v>
+        <v>22.48</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1272</v>
+        <v>2.0686</v>
       </c>
       <c r="F31" t="n">
-        <v>1434.307144</v>
+        <v>1394.794922</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>234.3088250000001</v>
+        <v>194.796603</v>
       </c>
       <c r="J31" t="n">
-        <v>19.53</v>
+        <v>16.23</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.478</v>
+        <v>2.4045</v>
       </c>
       <c r="F33" t="n">
-        <v>15115.8</v>
+        <v>14667.45</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2842.6</v>
+        <v>2394.25</v>
       </c>
       <c r="J33" t="n">
-        <v>23.16</v>
+        <v>19.51</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.996</v>
+        <v>1.9384</v>
       </c>
       <c r="F34" t="n">
-        <v>38123.6</v>
+        <v>37023.44</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6952.399999999998</v>
+        <v>5852.239999999994</v>
       </c>
       <c r="J34" t="n">
-        <v>22.3</v>
+        <v>18.77</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.8172</v>
+        <v>6.6235</v>
       </c>
       <c r="F35" t="n">
-        <v>41492.069736</v>
+        <v>40313.13793</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>8292.084111999997</v>
+        <v>7113.152305999996</v>
       </c>
       <c r="J35" t="n">
-        <v>24.98</v>
+        <v>21.43</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.8172</v>
+        <v>6.6235</v>
       </c>
       <c r="F36" t="n">
-        <v>14090.197992</v>
+        <v>13689.84721</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2790.260999999999</v>
+        <v>2389.910217999999</v>
       </c>
       <c r="J36" t="n">
-        <v>24.69</v>
+        <v>21.15</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.8172</v>
+        <v>6.6235</v>
       </c>
       <c r="F37" t="n">
-        <v>102258</v>
+        <v>99352.5</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>18963</v>
+        <v>16057.5</v>
       </c>
       <c r="J37" t="n">
-        <v>22.77</v>
+        <v>19.28</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.8118</v>
+        <v>2.7198</v>
       </c>
       <c r="F38" t="n">
-        <v>20451.374238</v>
+        <v>19782.220518</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>4651.345695</v>
+        <v>3982.191975000002</v>
       </c>
       <c r="J38" t="n">
-        <v>29.44</v>
+        <v>25.2</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.8118</v>
+        <v>2.7198</v>
       </c>
       <c r="F39" t="n">
-        <v>29321.197338</v>
+        <v>28361.829618</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>6321.399041999997</v>
+        <v>5362.031322000003</v>
       </c>
       <c r="J39" t="n">
-        <v>27.48</v>
+        <v>23.31</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.288</v>
+        <v>2.2085</v>
       </c>
       <c r="F40" t="n">
-        <v>15329.6</v>
+        <v>14796.95</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4877.599999999999</v>
+        <v>4344.949999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>46.67</v>
+        <v>41.57</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.460000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="F41" t="n">
-        <v>8460</v>
+        <v>8600</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1351</v>
+        <v>1491</v>
       </c>
       <c r="J41" t="n">
-        <v>19</v>
+        <v>20.97</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7.3</v>
+        <v>7.33</v>
       </c>
       <c r="F42" t="n">
-        <v>8030</v>
+        <v>8063</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1445.4</v>
+        <v>1478.4</v>
       </c>
       <c r="J42" t="n">
-        <v>21.95</v>
+        <v>22.45</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>41.87</v>
+        <v>41.7</v>
       </c>
       <c r="F43" t="n">
-        <v>62804.99999999999</v>
+        <v>62550.00000000001</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-1650.000000000007</v>
+        <v>-1904.999999999993</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.56</v>
+        <v>-2.96</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7082</v>
+        <v>2.6992</v>
       </c>
       <c r="F2" t="n">
-        <v>2003.228458</v>
+        <v>1996.571248</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>132.9962620000003</v>
+        <v>126.339052</v>
       </c>
       <c r="J2" t="n">
-        <v>7.11</v>
+        <v>6.76</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.468</v>
+        <v>2.474</v>
       </c>
       <c r="F3" t="n">
-        <v>800.4217599999999</v>
+        <v>802.3676800000001</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-199.5216640000001</v>
+        <v>-197.575744</v>
       </c>
       <c r="J3" t="n">
-        <v>-19.95</v>
+        <v>-19.76</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1201</v>
+        <v>1.1149</v>
       </c>
       <c r="F4" t="n">
-        <v>6384.570000000001</v>
+        <v>6354.93</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>963.8700000000008</v>
+        <v>934.2300000000005</v>
       </c>
       <c r="J4" t="n">
-        <v>17.78</v>
+        <v>17.23</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8868</v>
+        <v>1.8711</v>
       </c>
       <c r="F5" t="n">
-        <v>2237.612724</v>
+        <v>2218.993623</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-162.3538169999997</v>
+        <v>-180.9729179999995</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.76</v>
+        <v>-7.54</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2776</v>
+        <v>1.2665</v>
       </c>
       <c r="F6" t="n">
-        <v>2168.457704</v>
+        <v>2149.617785</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-331.4807369999999</v>
+        <v>-350.3206559999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.26</v>
+        <v>-14.01</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2776</v>
+        <v>1.2665</v>
       </c>
       <c r="F7" t="n">
-        <v>4591.82216</v>
+        <v>4551.92765</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-728.1646600000004</v>
+        <v>-768.0591700000004</v>
       </c>
       <c r="J7" t="n">
-        <v>-13.69</v>
+        <v>-14.44</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0965</v>
+        <v>2.0772</v>
       </c>
       <c r="F8" t="n">
-        <v>27044.85</v>
+        <v>26795.88</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>7746.449999999997</v>
+        <v>7497.479999999996</v>
       </c>
       <c r="J8" t="n">
-        <v>40.14</v>
+        <v>38.85</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1208</v>
+        <v>3.1047</v>
       </c>
       <c r="F9" t="n">
-        <v>945.009448</v>
+        <v>940.1342069999999</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>196.069475</v>
+        <v>191.1942339999999</v>
       </c>
       <c r="J9" t="n">
-        <v>26.18</v>
+        <v>25.53</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2361</v>
+        <v>2.2258</v>
       </c>
       <c r="F10" t="n">
-        <v>2326.505523</v>
+        <v>2315.789094</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>326.4869340000002</v>
+        <v>315.7705050000002</v>
       </c>
       <c r="J10" t="n">
-        <v>16.32</v>
+        <v>15.79</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6894</v>
+        <v>1.6811</v>
       </c>
       <c r="F11" t="n">
-        <v>6989.436361999999</v>
+        <v>6955.097352999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1010.311565999999</v>
+        <v>975.9725569999991</v>
       </c>
       <c r="J11" t="n">
-        <v>16.9</v>
+        <v>16.32</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6894</v>
+        <v>1.6811</v>
       </c>
       <c r="F12" t="n">
-        <v>10160.169858</v>
+        <v>10110.253077</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1060.280541</v>
+        <v>1010.36376</v>
       </c>
       <c r="J12" t="n">
-        <v>11.65</v>
+        <v>11.1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4355</v>
+        <v>2.4223</v>
       </c>
       <c r="F15" t="n">
-        <v>22650.15</v>
+        <v>22527.39</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3203.850000000002</v>
+        <v>3081.09</v>
       </c>
       <c r="J15" t="n">
-        <v>16.48</v>
+        <v>15.84</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>29.7</v>
+        <v>29.45</v>
       </c>
       <c r="F16" t="n">
-        <v>14850</v>
+        <v>14725</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>1035</v>
+        <v>910</v>
       </c>
       <c r="J16" t="n">
-        <v>7.49</v>
+        <v>6.59</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.42</v>
+        <v>9.34</v>
       </c>
       <c r="F17" t="n">
-        <v>18840</v>
+        <v>18680</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>1080</v>
+        <v>920</v>
       </c>
       <c r="J17" t="n">
-        <v>6.08</v>
+        <v>5.18</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0568</v>
+        <v>1.0719</v>
       </c>
       <c r="F18" t="n">
-        <v>4151.311192</v>
+        <v>4210.626861000001</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-155.1635049999995</v>
+        <v>-95.84783599999901</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.6</v>
+        <v>-2.23</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5256</v>
+        <v>1.5445</v>
       </c>
       <c r="F19" t="n">
-        <v>13272.72</v>
+        <v>13437.15</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-186.1799999999985</v>
+        <v>-21.75</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.38</v>
+        <v>-0.16</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.109</v>
+        <v>1.1175</v>
       </c>
       <c r="F20" t="n">
-        <v>8789.77874</v>
+        <v>8857.14855</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-1210.278822</v>
+        <v>-1142.909012</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.1</v>
+        <v>-11.43</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1973</v>
+        <v>1.2142</v>
       </c>
       <c r="F21" t="n">
-        <v>13529.49</v>
+        <v>13720.46</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>896.0900000000001</v>
+        <v>1087.059999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>7.09</v>
+        <v>8.6</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7076</v>
+        <v>1.7073</v>
       </c>
       <c r="F22" t="n">
-        <v>911.670564</v>
+        <v>911.510397</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>182.5369910000001</v>
+        <v>182.3768240000001</v>
       </c>
       <c r="J22" t="n">
-        <v>25.03</v>
+        <v>25.01</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7076</v>
+        <v>1.7073</v>
       </c>
       <c r="F23" t="n">
-        <v>22065.163224</v>
+        <v>22061.286702</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>2864.749757999998</v>
+        <v>2860.873235999999</v>
       </c>
       <c r="J23" t="n">
-        <v>14.92</v>
+        <v>14.9</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5358</v>
+        <v>1.5354</v>
       </c>
       <c r="F24" t="n">
-        <v>1004.904656</v>
+        <v>1004.642928</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>204.9330240000002</v>
+        <v>204.6712960000001</v>
       </c>
       <c r="J24" t="n">
-        <v>25.62</v>
+        <v>25.58</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.1077</v>
+        <v>6.1048</v>
       </c>
       <c r="F26" t="n">
-        <v>2536.772118</v>
+        <v>2535.567632</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>436.7715439999997</v>
+        <v>435.5670579999996</v>
       </c>
       <c r="J26" t="n">
-        <v>20.8</v>
+        <v>20.74</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9821</v>
+        <v>1.9815</v>
       </c>
       <c r="F28" t="n">
-        <v>7648.527480000001</v>
+        <v>7646.212200000001</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1348.650600000001</v>
+        <v>1346.335320000001</v>
       </c>
       <c r="J28" t="n">
-        <v>21.41</v>
+        <v>21.37</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9821</v>
+        <v>1.9815</v>
       </c>
       <c r="F29" t="n">
-        <v>17262.683709</v>
+        <v>17257.458135</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2262.673542</v>
+        <v>2257.447968</v>
       </c>
       <c r="J29" t="n">
-        <v>15.08</v>
+        <v>15.05</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0686</v>
+        <v>2.068</v>
       </c>
       <c r="F30" t="n">
-        <v>10876.884974</v>
+        <v>10873.73012</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>1996.496773000001</v>
+        <v>1993.341919</v>
       </c>
       <c r="J30" t="n">
-        <v>22.48</v>
+        <v>22.45</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.0686</v>
+        <v>2.068</v>
       </c>
       <c r="F31" t="n">
-        <v>1394.794922</v>
+        <v>1394.39036</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>194.796603</v>
+        <v>194.3920410000001</v>
       </c>
       <c r="J31" t="n">
-        <v>16.23</v>
+        <v>16.2</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4045</v>
+        <v>2.4033</v>
       </c>
       <c r="F33" t="n">
-        <v>14667.45</v>
+        <v>14660.13</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2394.25</v>
+        <v>2386.93</v>
       </c>
       <c r="J33" t="n">
-        <v>19.51</v>
+        <v>19.45</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9384</v>
+        <v>1.9378</v>
       </c>
       <c r="F34" t="n">
-        <v>37023.44</v>
+        <v>37011.98</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>5852.239999999994</v>
+        <v>5840.779999999995</v>
       </c>
       <c r="J34" t="n">
-        <v>18.77</v>
+        <v>18.74</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.6235</v>
+        <v>6.6432</v>
       </c>
       <c r="F35" t="n">
-        <v>40313.13793</v>
+        <v>40433.039616</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>7113.152305999996</v>
+        <v>7233.053992000001</v>
       </c>
       <c r="J35" t="n">
-        <v>21.43</v>
+        <v>21.79</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.6235</v>
+        <v>6.6432</v>
       </c>
       <c r="F36" t="n">
-        <v>13689.84721</v>
+        <v>13730.564352</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2389.910217999999</v>
+        <v>2430.62736</v>
       </c>
       <c r="J36" t="n">
-        <v>21.15</v>
+        <v>21.51</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.6235</v>
+        <v>6.6432</v>
       </c>
       <c r="F37" t="n">
-        <v>99352.5</v>
+        <v>99648</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>16057.5</v>
+        <v>16353</v>
       </c>
       <c r="J37" t="n">
-        <v>19.28</v>
+        <v>19.63</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.7198</v>
+        <v>2.7234</v>
       </c>
       <c r="F38" t="n">
-        <v>19782.220518</v>
+        <v>19808.404794</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>3982.191975000002</v>
+        <v>4008.376250999998</v>
       </c>
       <c r="J38" t="n">
-        <v>25.2</v>
+        <v>25.37</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.7198</v>
+        <v>2.7234</v>
       </c>
       <c r="F39" t="n">
-        <v>28361.829618</v>
+        <v>28399.370094</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>5362.031322000003</v>
+        <v>5399.571797999997</v>
       </c>
       <c r="J39" t="n">
-        <v>23.31</v>
+        <v>23.48</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.2085</v>
+        <v>2.2117</v>
       </c>
       <c r="F40" t="n">
-        <v>14796.95</v>
+        <v>14818.39</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4344.949999999999</v>
+        <v>4366.389999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>41.57</v>
+        <v>41.78</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.6</v>
+        <v>8.33</v>
       </c>
       <c r="F41" t="n">
-        <v>8600</v>
+        <v>8330</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1491</v>
+        <v>1221</v>
       </c>
       <c r="J41" t="n">
-        <v>20.97</v>
+        <v>17.18</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7.33</v>
+        <v>7.17</v>
       </c>
       <c r="F42" t="n">
-        <v>8063</v>
+        <v>7887</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1478.4</v>
+        <v>1302.4</v>
       </c>
       <c r="J42" t="n">
-        <v>22.45</v>
+        <v>19.78</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>41.7</v>
+        <v>41.49</v>
       </c>
       <c r="F43" t="n">
-        <v>62550.00000000001</v>
+        <v>62235</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-1904.999999999993</v>
+        <v>-2220</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.96</v>
+        <v>-3.44</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6992</v>
+        <v>2.6964</v>
       </c>
       <c r="F2" t="n">
-        <v>1996.571248</v>
+        <v>1994.500116</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>126.339052</v>
+        <v>124.2679200000002</v>
       </c>
       <c r="J2" t="n">
-        <v>6.76</v>
+        <v>6.64</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.474</v>
+        <v>2.4711</v>
       </c>
       <c r="F3" t="n">
-        <v>802.3676800000001</v>
+        <v>801.427152</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-197.575744</v>
+        <v>-198.5162720000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-19.76</v>
+        <v>-19.85</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1149</v>
+        <v>1.0962</v>
       </c>
       <c r="F4" t="n">
-        <v>6354.93</v>
+        <v>6248.34</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>934.2300000000005</v>
+        <v>827.6400000000003</v>
       </c>
       <c r="J4" t="n">
-        <v>17.23</v>
+        <v>15.27</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8711</v>
+        <v>1.8849</v>
       </c>
       <c r="F5" t="n">
-        <v>2218.993623</v>
+        <v>2235.359457</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-180.9729179999995</v>
+        <v>-164.6070839999998</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.54</v>
+        <v>-6.86</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2665</v>
+        <v>1.2739</v>
       </c>
       <c r="F6" t="n">
-        <v>2149.617785</v>
+        <v>2162.177731</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-350.3206559999999</v>
+        <v>-337.7607099999996</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.01</v>
+        <v>-13.51</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2665</v>
+        <v>1.2739</v>
       </c>
       <c r="F7" t="n">
-        <v>4551.92765</v>
+        <v>4578.52399</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-768.0591700000004</v>
+        <v>-741.4628300000004</v>
       </c>
       <c r="J7" t="n">
-        <v>-14.44</v>
+        <v>-13.94</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0772</v>
+        <v>2.1043</v>
       </c>
       <c r="F8" t="n">
-        <v>26795.88</v>
+        <v>27145.47</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>7497.479999999996</v>
+        <v>7847.069999999996</v>
       </c>
       <c r="J8" t="n">
-        <v>38.85</v>
+        <v>40.66</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1047</v>
+        <v>3.1243</v>
       </c>
       <c r="F9" t="n">
-        <v>940.1342069999999</v>
+        <v>946.0692829999999</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>191.1942339999999</v>
+        <v>197.1293099999999</v>
       </c>
       <c r="J9" t="n">
-        <v>25.53</v>
+        <v>26.32</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2258</v>
+        <v>2.2384</v>
       </c>
       <c r="F10" t="n">
-        <v>2315.789094</v>
+        <v>2328.898512</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>315.7705050000002</v>
+        <v>328.8799230000002</v>
       </c>
       <c r="J10" t="n">
-        <v>15.79</v>
+        <v>16.44</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6811</v>
+        <v>1.6913</v>
       </c>
       <c r="F11" t="n">
-        <v>6955.097352999999</v>
+        <v>6997.297098999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>975.9725569999991</v>
+        <v>1018.172302999999</v>
       </c>
       <c r="J11" t="n">
-        <v>16.32</v>
+        <v>17.03</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6811</v>
+        <v>1.6913</v>
       </c>
       <c r="F12" t="n">
-        <v>10110.253077</v>
+        <v>10171.596591</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1010.36376</v>
+        <v>1071.707274</v>
       </c>
       <c r="J12" t="n">
-        <v>11.1</v>
+        <v>11.78</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4223</v>
+        <v>2.4379</v>
       </c>
       <c r="F15" t="n">
-        <v>22527.39</v>
+        <v>22672.47</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3081.09</v>
+        <v>3226.170000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>15.84</v>
+        <v>16.59</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>29.45</v>
+        <v>29.57</v>
       </c>
       <c r="F16" t="n">
-        <v>14725</v>
+        <v>14785</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>910</v>
+        <v>970</v>
       </c>
       <c r="J16" t="n">
-        <v>6.59</v>
+        <v>7.02</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.34</v>
+        <v>9.43</v>
       </c>
       <c r="F17" t="n">
-        <v>18680</v>
+        <v>18860</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>920</v>
+        <v>1100</v>
       </c>
       <c r="J17" t="n">
-        <v>5.18</v>
+        <v>6.19</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0719</v>
+        <v>1.0771</v>
       </c>
       <c r="F18" t="n">
-        <v>4210.626861000001</v>
+        <v>4231.053449</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-95.84783599999901</v>
+        <v>-75.42124799999965</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.23</v>
+        <v>-1.75</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5445</v>
+        <v>1.5542</v>
       </c>
       <c r="F19" t="n">
-        <v>13437.15</v>
+        <v>13521.54</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-21.75</v>
+        <v>62.64000000000124</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.16</v>
+        <v>0.47</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1175</v>
+        <v>1.1179</v>
       </c>
       <c r="F20" t="n">
-        <v>8857.14855</v>
+        <v>8860.318893999998</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-1142.909012</v>
+        <v>-1139.738668000002</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.43</v>
+        <v>-11.4</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2142</v>
+        <v>1.2227</v>
       </c>
       <c r="F21" t="n">
-        <v>13720.46</v>
+        <v>13816.51</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1087.059999999999</v>
+        <v>1183.109999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>8.6</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7073</v>
+        <v>1.7243</v>
       </c>
       <c r="F22" t="n">
-        <v>911.510397</v>
+        <v>920.5865269999999</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>182.3768240000001</v>
+        <v>191.452954</v>
       </c>
       <c r="J22" t="n">
-        <v>25.01</v>
+        <v>26.26</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7073</v>
+        <v>1.7243</v>
       </c>
       <c r="F23" t="n">
-        <v>22061.286702</v>
+        <v>22280.956282</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>2860.873235999999</v>
+        <v>3080.542815999997</v>
       </c>
       <c r="J23" t="n">
-        <v>14.9</v>
+        <v>16.04</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5354</v>
+        <v>1.5502</v>
       </c>
       <c r="F24" t="n">
-        <v>1004.642928</v>
+        <v>1014.326864</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>204.6712960000001</v>
+        <v>214.3552320000001</v>
       </c>
       <c r="J24" t="n">
-        <v>25.58</v>
+        <v>26.8</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.1048</v>
+        <v>6.1686</v>
       </c>
       <c r="F26" t="n">
-        <v>2535.567632</v>
+        <v>2562.066324</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>435.5670579999996</v>
+        <v>462.0657499999998</v>
       </c>
       <c r="J26" t="n">
-        <v>20.74</v>
+        <v>22</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9815</v>
+        <v>2.0015</v>
       </c>
       <c r="F28" t="n">
-        <v>7646.212200000001</v>
+        <v>7723.3882</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1346.335320000001</v>
+        <v>1423.511320000001</v>
       </c>
       <c r="J28" t="n">
-        <v>21.37</v>
+        <v>22.6</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9815</v>
+        <v>2.0015</v>
       </c>
       <c r="F29" t="n">
-        <v>17257.458135</v>
+        <v>17431.643935</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2257.447968</v>
+        <v>2431.633768000003</v>
       </c>
       <c r="J29" t="n">
-        <v>15.05</v>
+        <v>16.21</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.068</v>
+        <v>2.0888</v>
       </c>
       <c r="F30" t="n">
-        <v>10873.73012</v>
+        <v>10983.098392</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>1993.341919</v>
+        <v>2102.710191</v>
       </c>
       <c r="J30" t="n">
-        <v>22.45</v>
+        <v>23.68</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.068</v>
+        <v>2.0888</v>
       </c>
       <c r="F31" t="n">
-        <v>1394.39036</v>
+        <v>1408.415176</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>194.3920410000001</v>
+        <v>208.4168569999999</v>
       </c>
       <c r="J31" t="n">
-        <v>16.2</v>
+        <v>17.37</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4033</v>
+        <v>2.4285</v>
       </c>
       <c r="F33" t="n">
-        <v>14660.13</v>
+        <v>14813.85</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2386.93</v>
+        <v>2540.65</v>
       </c>
       <c r="J33" t="n">
-        <v>19.45</v>
+        <v>20.7</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9378</v>
+        <v>1.9582</v>
       </c>
       <c r="F34" t="n">
-        <v>37011.98</v>
+        <v>37401.62</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>5840.779999999995</v>
+        <v>6230.419999999995</v>
       </c>
       <c r="J34" t="n">
-        <v>18.74</v>
+        <v>19.99</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.6432</v>
+        <v>6.7345</v>
       </c>
       <c r="F35" t="n">
-        <v>40433.039616</v>
+        <v>40988.72611</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>7233.053992000001</v>
+        <v>7788.740485999995</v>
       </c>
       <c r="J35" t="n">
-        <v>21.79</v>
+        <v>23.46</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.6432</v>
+        <v>6.7345</v>
       </c>
       <c r="F36" t="n">
-        <v>13730.564352</v>
+        <v>13919.26867</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2430.62736</v>
+        <v>2619.331677999999</v>
       </c>
       <c r="J36" t="n">
-        <v>21.51</v>
+        <v>23.18</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.6432</v>
+        <v>6.7345</v>
       </c>
       <c r="F37" t="n">
-        <v>99648</v>
+        <v>101017.5</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>16353</v>
+        <v>17722.5</v>
       </c>
       <c r="J37" t="n">
-        <v>19.63</v>
+        <v>21.28</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.7234</v>
+        <v>2.7467</v>
       </c>
       <c r="F38" t="n">
-        <v>19808.404794</v>
+        <v>19977.875247</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>4008.376250999998</v>
+        <v>4177.846704</v>
       </c>
       <c r="J38" t="n">
-        <v>25.37</v>
+        <v>26.44</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.7234</v>
+        <v>2.7467</v>
       </c>
       <c r="F39" t="n">
-        <v>28399.370094</v>
+        <v>28642.340397</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>5399.571797999997</v>
+        <v>5642.542100999999</v>
       </c>
       <c r="J39" t="n">
-        <v>23.48</v>
+        <v>24.53</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.2117</v>
+        <v>2.2319</v>
       </c>
       <c r="F40" t="n">
-        <v>14818.39</v>
+        <v>14953.73</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4366.389999999999</v>
+        <v>4501.73</v>
       </c>
       <c r="J40" t="n">
-        <v>41.78</v>
+        <v>43.07</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="F41" t="n">
-        <v>8330</v>
+        <v>8500</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1221</v>
+        <v>1391</v>
       </c>
       <c r="J41" t="n">
-        <v>17.18</v>
+        <v>19.57</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7.17</v>
+        <v>7.25</v>
       </c>
       <c r="F42" t="n">
-        <v>7887</v>
+        <v>7975</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1302.4</v>
+        <v>1390.4</v>
       </c>
       <c r="J42" t="n">
-        <v>19.78</v>
+        <v>21.12</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>41.49</v>
+        <v>42.3</v>
       </c>
       <c r="F43" t="n">
-        <v>62235</v>
+        <v>63449.99999999999</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-2220</v>
+        <v>-1005.000000000007</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.44</v>
+        <v>-1.56</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6964</v>
+        <v>2.7226</v>
       </c>
       <c r="F2" t="n">
-        <v>1994.500116</v>
+        <v>2013.879994</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>124.2679200000002</v>
+        <v>143.6477980000002</v>
       </c>
       <c r="J2" t="n">
-        <v>6.64</v>
+        <v>7.68</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4711</v>
+        <v>2.4714</v>
       </c>
       <c r="F3" t="n">
-        <v>801.427152</v>
+        <v>801.524448</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-198.5162720000001</v>
+        <v>-198.418976</v>
       </c>
       <c r="J3" t="n">
-        <v>-19.85</v>
+        <v>-19.84</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0962</v>
+        <v>1.1085</v>
       </c>
       <c r="F4" t="n">
-        <v>6248.34</v>
+        <v>6318.45</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>827.6400000000003</v>
+        <v>897.75</v>
       </c>
       <c r="J4" t="n">
-        <v>15.27</v>
+        <v>16.56</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8849</v>
+        <v>1.8917</v>
       </c>
       <c r="F5" t="n">
-        <v>2235.359457</v>
+        <v>2243.423781</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-164.6070839999998</v>
+        <v>-156.5427599999998</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.86</v>
+        <v>-6.52</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2739</v>
+        <v>1.2864</v>
       </c>
       <c r="F6" t="n">
-        <v>2162.177731</v>
+        <v>2183.393856</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-337.7607099999996</v>
+        <v>-316.5445849999996</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.51</v>
+        <v>-12.66</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2739</v>
+        <v>1.2864</v>
       </c>
       <c r="F7" t="n">
-        <v>4578.52399</v>
+        <v>4623.45024</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-741.4628300000004</v>
+        <v>-696.53658</v>
       </c>
       <c r="J7" t="n">
-        <v>-13.94</v>
+        <v>-13.09</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1043</v>
+        <v>2.1256</v>
       </c>
       <c r="F8" t="n">
-        <v>27145.47</v>
+        <v>27420.24</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>7847.069999999996</v>
+        <v>8121.839999999997</v>
       </c>
       <c r="J8" t="n">
-        <v>40.66</v>
+        <v>42.09</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1243</v>
+        <v>3.1422</v>
       </c>
       <c r="F9" t="n">
-        <v>946.0692829999999</v>
+        <v>951.4895819999999</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>197.1293099999999</v>
+        <v>202.5496089999999</v>
       </c>
       <c r="J9" t="n">
-        <v>26.32</v>
+        <v>27.04</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2384</v>
+        <v>2.2507</v>
       </c>
       <c r="F10" t="n">
-        <v>2328.898512</v>
+        <v>2341.695801</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>328.8799230000002</v>
+        <v>341.6772120000003</v>
       </c>
       <c r="J10" t="n">
-        <v>16.44</v>
+        <v>17.08</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6913</v>
+        <v>1.7013</v>
       </c>
       <c r="F11" t="n">
-        <v>6997.297098999999</v>
+        <v>7038.669398999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1018.172302999999</v>
+        <v>1059.544602999999</v>
       </c>
       <c r="J11" t="n">
-        <v>17.03</v>
+        <v>17.72</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6913</v>
+        <v>1.7013</v>
       </c>
       <c r="F12" t="n">
-        <v>10171.596591</v>
+        <v>10231.737291</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1071.707274</v>
+        <v>1131.847974</v>
       </c>
       <c r="J12" t="n">
-        <v>11.78</v>
+        <v>12.44</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4379</v>
+        <v>2.4532</v>
       </c>
       <c r="F15" t="n">
-        <v>22672.47</v>
+        <v>22814.76</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3226.170000000002</v>
+        <v>3368.459999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>16.59</v>
+        <v>17.32</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>29.57</v>
+        <v>29.54</v>
       </c>
       <c r="F16" t="n">
-        <v>14785</v>
+        <v>14770</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>970</v>
+        <v>955</v>
       </c>
       <c r="J16" t="n">
-        <v>7.02</v>
+        <v>6.91</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.43</v>
+        <v>9.5</v>
       </c>
       <c r="F17" t="n">
-        <v>18860</v>
+        <v>19000</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>1100</v>
+        <v>1240</v>
       </c>
       <c r="J17" t="n">
-        <v>6.19</v>
+        <v>6.98</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0771</v>
+        <v>1.0716</v>
       </c>
       <c r="F18" t="n">
-        <v>4231.053449</v>
+        <v>4209.448404000001</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-75.42124799999965</v>
+        <v>-97.02629299999899</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.75</v>
+        <v>-2.25</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5542</v>
+        <v>1.5546</v>
       </c>
       <c r="F19" t="n">
-        <v>13521.54</v>
+        <v>13525.02</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>62.64000000000124</v>
+        <v>66.1200000000008</v>
       </c>
       <c r="J19" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1179</v>
+        <v>1.1144</v>
       </c>
       <c r="F20" t="n">
-        <v>8860.318893999998</v>
+        <v>8832.578384</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-1139.738668000002</v>
+        <v>-1167.479178</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.4</v>
+        <v>-11.67</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2227</v>
+        <v>1.2189</v>
       </c>
       <c r="F21" t="n">
-        <v>13816.51</v>
+        <v>13773.57</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1183.109999999999</v>
+        <v>1140.170000000002</v>
       </c>
       <c r="J21" t="n">
-        <v>9.359999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7243</v>
+        <v>1.7454</v>
       </c>
       <c r="F22" t="n">
-        <v>920.5865269999999</v>
+        <v>931.8516060000001</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>191.452954</v>
+        <v>202.7180330000001</v>
       </c>
       <c r="J22" t="n">
-        <v>26.26</v>
+        <v>27.8</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7243</v>
+        <v>1.7454</v>
       </c>
       <c r="F23" t="n">
-        <v>22280.956282</v>
+        <v>22553.604996</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3080.542815999997</v>
+        <v>3353.19153</v>
       </c>
       <c r="J23" t="n">
-        <v>16.04</v>
+        <v>17.46</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5502</v>
+        <v>1.5687</v>
       </c>
       <c r="F24" t="n">
-        <v>1014.326864</v>
+        <v>1026.431784</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>214.3552320000001</v>
+        <v>226.4601520000001</v>
       </c>
       <c r="J24" t="n">
-        <v>26.8</v>
+        <v>28.31</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.1686</v>
+        <v>6.2444</v>
       </c>
       <c r="F26" t="n">
-        <v>2562.066324</v>
+        <v>2593.549096</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>462.0657499999998</v>
+        <v>493.5485219999996</v>
       </c>
       <c r="J26" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0015</v>
+        <v>2.0263</v>
       </c>
       <c r="F28" t="n">
-        <v>7723.3882</v>
+        <v>7819.08644</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1423.511320000001</v>
+        <v>1519.20956</v>
       </c>
       <c r="J28" t="n">
-        <v>22.6</v>
+        <v>24.11</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0015</v>
+        <v>2.0263</v>
       </c>
       <c r="F29" t="n">
-        <v>17431.643935</v>
+        <v>17647.634327</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2431.633768000003</v>
+        <v>2647.624160000003</v>
       </c>
       <c r="J29" t="n">
-        <v>16.21</v>
+        <v>17.65</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0888</v>
+        <v>2.1147</v>
       </c>
       <c r="F30" t="n">
-        <v>10983.098392</v>
+        <v>11119.282923</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2102.710191</v>
+        <v>2238.894722000001</v>
       </c>
       <c r="J30" t="n">
-        <v>23.68</v>
+        <v>25.21</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.0888</v>
+        <v>2.1147</v>
       </c>
       <c r="F31" t="n">
-        <v>1408.415176</v>
+        <v>1425.878769</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>208.4168569999999</v>
+        <v>225.8804499999999</v>
       </c>
       <c r="J31" t="n">
-        <v>17.37</v>
+        <v>18.82</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4285</v>
+        <v>2.4598</v>
       </c>
       <c r="F33" t="n">
-        <v>14813.85</v>
+        <v>15004.78</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2540.65</v>
+        <v>2731.58</v>
       </c>
       <c r="J33" t="n">
-        <v>20.7</v>
+        <v>22.26</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9582</v>
+        <v>1.9836</v>
       </c>
       <c r="F34" t="n">
-        <v>37401.62</v>
+        <v>37886.76</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6230.419999999995</v>
+        <v>6715.560000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>19.99</v>
+        <v>21.54</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.7345</v>
+        <v>6.83</v>
       </c>
       <c r="F35" t="n">
-        <v>40988.72611</v>
+        <v>41569.9754</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>7788.740485999995</v>
+        <v>8369.989776000002</v>
       </c>
       <c r="J35" t="n">
-        <v>23.46</v>
+        <v>25.21</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.7345</v>
+        <v>6.83</v>
       </c>
       <c r="F36" t="n">
-        <v>13919.26867</v>
+        <v>14116.6538</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2619.331677999999</v>
+        <v>2816.716808000001</v>
       </c>
       <c r="J36" t="n">
-        <v>23.18</v>
+        <v>24.93</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.7345</v>
+        <v>6.83</v>
       </c>
       <c r="F37" t="n">
-        <v>101017.5</v>
+        <v>102450</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>17722.5</v>
+        <v>19155</v>
       </c>
       <c r="J37" t="n">
-        <v>21.28</v>
+        <v>23</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.7467</v>
+        <v>2.7815</v>
       </c>
       <c r="F38" t="n">
-        <v>19977.875247</v>
+        <v>20230.989915</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>4177.846704</v>
+        <v>4430.961371999998</v>
       </c>
       <c r="J38" t="n">
-        <v>26.44</v>
+        <v>28.04</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.7467</v>
+        <v>2.7815</v>
       </c>
       <c r="F39" t="n">
-        <v>28642.340397</v>
+        <v>29005.231665</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>5642.542100999999</v>
+        <v>6005.433368999998</v>
       </c>
       <c r="J39" t="n">
-        <v>24.53</v>
+        <v>26.11</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.2319</v>
+        <v>2.262</v>
       </c>
       <c r="F40" t="n">
-        <v>14953.73</v>
+        <v>15155.4</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4501.73</v>
+        <v>4703.4</v>
       </c>
       <c r="J40" t="n">
-        <v>43.07</v>
+        <v>45</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.5</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>8500</v>
+        <v>8620</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1391</v>
+        <v>1511</v>
       </c>
       <c r="J41" t="n">
-        <v>19.57</v>
+        <v>21.25</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7.25</v>
+        <v>7.43</v>
       </c>
       <c r="F42" t="n">
-        <v>7975</v>
+        <v>8173</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1390.4</v>
+        <v>1588.4</v>
       </c>
       <c r="J42" t="n">
-        <v>21.12</v>
+        <v>24.12</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>42.3</v>
+        <v>42.51</v>
       </c>
       <c r="F43" t="n">
-        <v>63449.99999999999</v>
+        <v>63765</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-1005.000000000007</v>
+        <v>-690</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.56</v>
+        <v>-1.07</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7226</v>
+        <v>2.7118</v>
       </c>
       <c r="F2" t="n">
-        <v>2013.879994</v>
+        <v>2005.891342</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>143.6477980000002</v>
+        <v>135.6591460000004</v>
       </c>
       <c r="J2" t="n">
-        <v>7.68</v>
+        <v>7.25</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4714</v>
+        <v>2.4823</v>
       </c>
       <c r="F3" t="n">
-        <v>801.524448</v>
+        <v>805.059536</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-198.418976</v>
+        <v>-194.8838880000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-19.84</v>
+        <v>-19.49</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1085</v>
+        <v>1.0919</v>
       </c>
       <c r="F4" t="n">
-        <v>6318.45</v>
+        <v>6223.830000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>897.75</v>
+        <v>803.130000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>16.56</v>
+        <v>14.82</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8917</v>
+        <v>1.8924</v>
       </c>
       <c r="F5" t="n">
-        <v>2243.423781</v>
+        <v>2244.253932</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-156.5427599999998</v>
+        <v>-155.7126089999997</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.52</v>
+        <v>-6.49</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2864</v>
+        <v>1.2845</v>
       </c>
       <c r="F6" t="n">
-        <v>2183.393856</v>
+        <v>2180.169005</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-316.5445849999996</v>
+        <v>-319.769436</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.66</v>
+        <v>-12.79</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2864</v>
+        <v>1.2845</v>
       </c>
       <c r="F7" t="n">
-        <v>4623.45024</v>
+        <v>4616.62145</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-696.53658</v>
+        <v>-703.3653700000004</v>
       </c>
       <c r="J7" t="n">
-        <v>-13.09</v>
+        <v>-13.22</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1256</v>
+        <v>2.1416</v>
       </c>
       <c r="F8" t="n">
-        <v>27420.24</v>
+        <v>27626.64</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8121.839999999997</v>
+        <v>8328.239999999998</v>
       </c>
       <c r="J8" t="n">
-        <v>42.09</v>
+        <v>43.16</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1422</v>
+        <v>3.1502</v>
       </c>
       <c r="F9" t="n">
-        <v>951.4895819999999</v>
+        <v>953.912062</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>202.5496089999999</v>
+        <v>204.972089</v>
       </c>
       <c r="J9" t="n">
-        <v>27.04</v>
+        <v>27.37</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2507</v>
+        <v>2.257</v>
       </c>
       <c r="F10" t="n">
-        <v>2341.695801</v>
+        <v>2348.25051</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>341.6772120000003</v>
+        <v>348.2319210000003</v>
       </c>
       <c r="J10" t="n">
-        <v>17.08</v>
+        <v>17.41</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7013</v>
+        <v>1.7055</v>
       </c>
       <c r="F11" t="n">
-        <v>7038.669398999999</v>
+        <v>7056.045764999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1059.544602999999</v>
+        <v>1076.920968999999</v>
       </c>
       <c r="J11" t="n">
-        <v>17.72</v>
+        <v>18.01</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7013</v>
+        <v>1.7055</v>
       </c>
       <c r="F12" t="n">
-        <v>10231.737291</v>
+        <v>10256.996385</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1131.847974</v>
+        <v>1157.107068000001</v>
       </c>
       <c r="J12" t="n">
-        <v>12.44</v>
+        <v>12.72</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4532</v>
+        <v>2.4597</v>
       </c>
       <c r="F15" t="n">
-        <v>22814.76</v>
+        <v>22875.21</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3368.459999999999</v>
+        <v>3428.910000000003</v>
       </c>
       <c r="J15" t="n">
-        <v>17.32</v>
+        <v>17.63</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>29.54</v>
+        <v>29.57</v>
       </c>
       <c r="F16" t="n">
-        <v>14770</v>
+        <v>14785</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="J16" t="n">
-        <v>6.91</v>
+        <v>7.02</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.5</v>
+        <v>9.66</v>
       </c>
       <c r="F17" t="n">
-        <v>19000</v>
+        <v>19320</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>1240</v>
+        <v>1560</v>
       </c>
       <c r="J17" t="n">
-        <v>6.98</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0716</v>
+        <v>1.0829</v>
       </c>
       <c r="F18" t="n">
-        <v>4209.448404000001</v>
+        <v>4253.836951</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-97.02629299999899</v>
+        <v>-52.63774599999942</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.25</v>
+        <v>-1.22</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5546</v>
+        <v>1.5679</v>
       </c>
       <c r="F19" t="n">
-        <v>13525.02</v>
+        <v>13640.73</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>66.1200000000008</v>
+        <v>181.8300000000017</v>
       </c>
       <c r="J19" t="n">
-        <v>0.49</v>
+        <v>1.35</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1144</v>
+        <v>1.1173</v>
       </c>
       <c r="F20" t="n">
-        <v>8832.578384</v>
+        <v>8855.563377999999</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-1167.479178</v>
+        <v>-1144.494184000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.67</v>
+        <v>-11.44</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2189</v>
+        <v>1.238</v>
       </c>
       <c r="F21" t="n">
-        <v>13773.57</v>
+        <v>13989.4</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1140.170000000002</v>
+        <v>1356</v>
       </c>
       <c r="J21" t="n">
-        <v>9.029999999999999</v>
+        <v>10.73</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7454</v>
+        <v>1.7542</v>
       </c>
       <c r="F22" t="n">
-        <v>931.8516060000001</v>
+        <v>936.549838</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>202.7180330000001</v>
+        <v>207.4162650000001</v>
       </c>
       <c r="J22" t="n">
-        <v>27.8</v>
+        <v>28.45</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7454</v>
+        <v>1.7542</v>
       </c>
       <c r="F23" t="n">
-        <v>22553.604996</v>
+        <v>22667.316308</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3353.19153</v>
+        <v>3466.902841999996</v>
       </c>
       <c r="J23" t="n">
-        <v>17.46</v>
+        <v>18.06</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5687</v>
+        <v>1.5763</v>
       </c>
       <c r="F24" t="n">
-        <v>1026.431784</v>
+        <v>1031.404616</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>226.4601520000001</v>
+        <v>231.432984</v>
       </c>
       <c r="J24" t="n">
-        <v>28.31</v>
+        <v>28.93</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.2444</v>
+        <v>6.2746</v>
       </c>
       <c r="F26" t="n">
-        <v>2593.549096</v>
+        <v>2606.092364</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>493.5485219999996</v>
+        <v>506.0917899999999</v>
       </c>
       <c r="J26" t="n">
-        <v>23.5</v>
+        <v>24.1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0263</v>
+        <v>2.0366</v>
       </c>
       <c r="F28" t="n">
-        <v>7819.08644</v>
+        <v>7858.83208</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1519.20956</v>
+        <v>1558.9552</v>
       </c>
       <c r="J28" t="n">
-        <v>24.11</v>
+        <v>24.75</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0263</v>
+        <v>2.0366</v>
       </c>
       <c r="F29" t="n">
-        <v>17647.634327</v>
+        <v>17737.340014</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2647.624160000003</v>
+        <v>2737.329847000001</v>
       </c>
       <c r="J29" t="n">
-        <v>17.65</v>
+        <v>18.25</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1147</v>
+        <v>2.1255</v>
       </c>
       <c r="F30" t="n">
-        <v>11119.282923</v>
+        <v>11176.070295</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2238.894722000001</v>
+        <v>2295.682094000002</v>
       </c>
       <c r="J30" t="n">
-        <v>25.21</v>
+        <v>25.85</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1147</v>
+        <v>2.1255</v>
       </c>
       <c r="F31" t="n">
-        <v>1425.878769</v>
+        <v>1433.160885</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>225.8804499999999</v>
+        <v>233.162566</v>
       </c>
       <c r="J31" t="n">
-        <v>18.82</v>
+        <v>19.43</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4598</v>
+        <v>2.4727</v>
       </c>
       <c r="F33" t="n">
-        <v>15004.78</v>
+        <v>15083.47</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2731.58</v>
+        <v>2810.27</v>
       </c>
       <c r="J33" t="n">
-        <v>22.26</v>
+        <v>22.9</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9836</v>
+        <v>1.9943</v>
       </c>
       <c r="F34" t="n">
-        <v>37886.76</v>
+        <v>38091.13</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6715.560000000001</v>
+        <v>6919.929999999997</v>
       </c>
       <c r="J34" t="n">
-        <v>21.54</v>
+        <v>22.2</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.83</v>
+        <v>6.8604</v>
       </c>
       <c r="F35" t="n">
-        <v>41569.9754</v>
+        <v>41755.001352</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>8369.989776000002</v>
+        <v>8555.015727999998</v>
       </c>
       <c r="J35" t="n">
-        <v>25.21</v>
+        <v>25.77</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.83</v>
+        <v>6.8604</v>
       </c>
       <c r="F36" t="n">
-        <v>14116.6538</v>
+        <v>14179.486344</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2816.716808000001</v>
+        <v>2879.549352</v>
       </c>
       <c r="J36" t="n">
-        <v>24.93</v>
+        <v>25.48</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.83</v>
+        <v>6.8604</v>
       </c>
       <c r="F37" t="n">
-        <v>102450</v>
+        <v>102906</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>19155</v>
+        <v>19611</v>
       </c>
       <c r="J37" t="n">
-        <v>23</v>
+        <v>23.54</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.7815</v>
+        <v>2.7998</v>
       </c>
       <c r="F38" t="n">
-        <v>20230.989915</v>
+        <v>20364.093318</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>4430.961371999998</v>
+        <v>4564.064774999999</v>
       </c>
       <c r="J38" t="n">
-        <v>28.04</v>
+        <v>28.89</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.7815</v>
+        <v>2.7998</v>
       </c>
       <c r="F39" t="n">
-        <v>29005.231665</v>
+        <v>29196.062418</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>6005.433368999998</v>
+        <v>6196.264121999997</v>
       </c>
       <c r="J39" t="n">
-        <v>26.11</v>
+        <v>26.94</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.262</v>
+        <v>2.2779</v>
       </c>
       <c r="F40" t="n">
-        <v>15155.4</v>
+        <v>15261.93</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4703.4</v>
+        <v>4809.929999999998</v>
       </c>
       <c r="J40" t="n">
-        <v>45</v>
+        <v>46.02</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.619999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="F41" t="n">
-        <v>8620</v>
+        <v>8650</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1511</v>
+        <v>1541</v>
       </c>
       <c r="J41" t="n">
-        <v>21.25</v>
+        <v>21.68</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7.43</v>
+        <v>7.48</v>
       </c>
       <c r="F42" t="n">
-        <v>8173</v>
+        <v>8228</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1588.4</v>
+        <v>1643.4</v>
       </c>
       <c r="J42" t="n">
-        <v>24.12</v>
+        <v>24.96</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>42.51</v>
+        <v>42.5</v>
       </c>
       <c r="F43" t="n">
-        <v>63765</v>
+        <v>63750</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-690</v>
+        <v>-705</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.07</v>
+        <v>-1.09</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>

--- a/Asset.xlsx
+++ b/Asset.xlsx
@@ -4157,10 +4157,10 @@
         <v>739.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7118</v>
+        <v>2.6795</v>
       </c>
       <c r="F2" t="n">
-        <v>2005.891342</v>
+        <v>1981.999355</v>
       </c>
       <c r="G2" t="n">
         <v>2.5284</v>
@@ -4169,10 +4169,10 @@
         <v>1870.232196</v>
       </c>
       <c r="I2" t="n">
-        <v>135.6591460000004</v>
+        <v>111.7671590000002</v>
       </c>
       <c r="J2" t="n">
-        <v>7.25</v>
+        <v>5.98</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>324.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4823</v>
+        <v>2.4718</v>
       </c>
       <c r="F3" t="n">
-        <v>805.059536</v>
+        <v>801.654176</v>
       </c>
       <c r="G3" t="n">
         <v>3.0832</v>
@@ -4210,10 +4210,10 @@
         <v>999.9434240000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-194.8838880000001</v>
+        <v>-198.289248</v>
       </c>
       <c r="J3" t="n">
-        <v>-19.49</v>
+        <v>-19.83</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>5700</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0919</v>
+        <v>1.0719</v>
       </c>
       <c r="F4" t="n">
-        <v>6223.830000000001</v>
+        <v>6109.830000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.951</v>
@@ -4251,10 +4251,10 @@
         <v>5420.7</v>
       </c>
       <c r="I4" t="n">
-        <v>803.130000000001</v>
+        <v>689.130000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>14.82</v>
+        <v>12.71</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>1185.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8924</v>
+        <v>1.9169</v>
       </c>
       <c r="F5" t="n">
-        <v>2244.253932</v>
+        <v>2273.309217</v>
       </c>
       <c r="G5" t="n">
         <v>2.0237</v>
@@ -4292,10 +4292,10 @@
         <v>2399.966541</v>
       </c>
       <c r="I5" t="n">
-        <v>-155.7126089999997</v>
+        <v>-126.6573239999998</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.49</v>
+        <v>-5.28</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         <v>1697.29</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2845</v>
+        <v>1.2944</v>
       </c>
       <c r="F6" t="n">
-        <v>2180.169005</v>
+        <v>2196.972176</v>
       </c>
       <c r="G6" t="n">
         <v>1.4729</v>
@@ -4333,10 +4333,10 @@
         <v>2499.938441</v>
       </c>
       <c r="I6" t="n">
-        <v>-319.769436</v>
+        <v>-302.966265</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.79</v>
+        <v>-12.12</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>3594.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2845</v>
+        <v>1.2944</v>
       </c>
       <c r="F7" t="n">
-        <v>4616.62145</v>
+        <v>4652.203039999999</v>
       </c>
       <c r="G7" t="n">
         <v>1.4802</v>
@@ -4374,10 +4374,10 @@
         <v>5319.98682</v>
       </c>
       <c r="I7" t="n">
-        <v>-703.3653700000004</v>
+        <v>-667.7837800000007</v>
       </c>
       <c r="J7" t="n">
-        <v>-13.22</v>
+        <v>-12.55</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>12900</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1416</v>
+        <v>2.0968</v>
       </c>
       <c r="F8" t="n">
-        <v>27626.64</v>
+        <v>27048.72</v>
       </c>
       <c r="G8" t="n">
         <v>1.496</v>
@@ -4415,10 +4415,10 @@
         <v>19298.4</v>
       </c>
       <c r="I8" t="n">
-        <v>8328.239999999998</v>
+        <v>7750.32</v>
       </c>
       <c r="J8" t="n">
-        <v>43.16</v>
+        <v>40.16</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>302.81</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1502</v>
+        <v>3.1403</v>
       </c>
       <c r="F9" t="n">
-        <v>953.912062</v>
+        <v>950.9142429999999</v>
       </c>
       <c r="G9" t="n">
         <v>2.4733</v>
@@ -4456,10 +4456,10 @@
         <v>748.939973</v>
       </c>
       <c r="I9" t="n">
-        <v>204.972089</v>
+        <v>201.9742699999999</v>
       </c>
       <c r="J9" t="n">
-        <v>27.37</v>
+        <v>26.97</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         <v>1040.43</v>
       </c>
       <c r="E10" t="n">
-        <v>2.257</v>
+        <v>2.249</v>
       </c>
       <c r="F10" t="n">
-        <v>2348.25051</v>
+        <v>2339.92707</v>
       </c>
       <c r="G10" t="n">
         <v>1.9223</v>
@@ -4497,10 +4497,10 @@
         <v>2000.018589</v>
       </c>
       <c r="I10" t="n">
-        <v>348.2319210000003</v>
+        <v>339.9084810000002</v>
       </c>
       <c r="J10" t="n">
-        <v>17.41</v>
+        <v>17</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         <v>4137.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7055</v>
+        <v>1.6997</v>
       </c>
       <c r="F11" t="n">
-        <v>7056.045764999999</v>
+        <v>7032.049830999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.4452</v>
@@ -4538,10 +4538,10 @@
         <v>5979.124796</v>
       </c>
       <c r="I11" t="n">
-        <v>1076.920968999999</v>
+        <v>1052.925034999999</v>
       </c>
       <c r="J11" t="n">
-        <v>18.01</v>
+        <v>17.61</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         <v>6014.07</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7055</v>
+        <v>1.6997</v>
       </c>
       <c r="F12" t="n">
-        <v>10256.996385</v>
+        <v>10222.114779</v>
       </c>
       <c r="G12" t="n">
         <v>1.5131</v>
@@ -4579,10 +4579,10 @@
         <v>9099.889316999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1157.107068000001</v>
+        <v>1122.225462</v>
       </c>
       <c r="J12" t="n">
-        <v>12.72</v>
+        <v>12.33</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         <v>9300</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4597</v>
+        <v>2.451</v>
       </c>
       <c r="F15" t="n">
-        <v>22875.21</v>
+        <v>22794.3</v>
       </c>
       <c r="G15" t="n">
         <v>2.091</v>
@@ -4702,10 +4702,10 @@
         <v>19446.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3428.910000000003</v>
+        <v>3348</v>
       </c>
       <c r="J15" t="n">
-        <v>17.63</v>
+        <v>17.22</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>29.57</v>
+        <v>29.76</v>
       </c>
       <c r="F16" t="n">
-        <v>14785</v>
+        <v>14880</v>
       </c>
       <c r="G16" t="n">
         <v>27.63</v>
@@ -4743,10 +4743,10 @@
         <v>13815</v>
       </c>
       <c r="I16" t="n">
-        <v>970</v>
+        <v>1065</v>
       </c>
       <c r="J16" t="n">
-        <v>7.02</v>
+        <v>7.71</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>9.66</v>
+        <v>9.94</v>
       </c>
       <c r="F17" t="n">
-        <v>19320</v>
+        <v>19880</v>
       </c>
       <c r="G17" t="n">
         <v>8.880000000000001</v>
@@ -4784,10 +4784,10 @@
         <v>17760</v>
       </c>
       <c r="I17" t="n">
-        <v>1560</v>
+        <v>2120</v>
       </c>
       <c r="J17" t="n">
-        <v>8.779999999999999</v>
+        <v>11.94</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         <v>3928.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0829</v>
+        <v>1.0926</v>
       </c>
       <c r="F18" t="n">
-        <v>4253.836951</v>
+        <v>4291.940394</v>
       </c>
       <c r="G18" t="n">
         <v>1.0963</v>
@@ -4825,10 +4825,10 @@
         <v>4306.474697</v>
       </c>
       <c r="I18" t="n">
-        <v>-52.63774599999942</v>
+        <v>-14.53430299999945</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.22</v>
+        <v>-0.34</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         <v>8700</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5679</v>
+        <v>1.5807</v>
       </c>
       <c r="F19" t="n">
-        <v>13640.73</v>
+        <v>13752.09</v>
       </c>
       <c r="G19" t="n">
         <v>1.547</v>
@@ -4866,10 +4866,10 @@
         <v>13458.9</v>
       </c>
       <c r="I19" t="n">
-        <v>181.8300000000017</v>
+        <v>293.1900000000005</v>
       </c>
       <c r="J19" t="n">
-        <v>1.35</v>
+        <v>2.18</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
         <v>7925.86</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1173</v>
+        <v>1.1397</v>
       </c>
       <c r="F20" t="n">
-        <v>8855.563377999999</v>
+        <v>9033.102642</v>
       </c>
       <c r="G20" t="n">
         <v>1.2617</v>
@@ -4907,10 +4907,10 @@
         <v>10000.057562</v>
       </c>
       <c r="I20" t="n">
-        <v>-1144.494184000001</v>
+        <v>-966.9549200000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.44</v>
+        <v>-9.67</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         <v>11300</v>
       </c>
       <c r="E21" t="n">
-        <v>1.238</v>
+        <v>1.2459</v>
       </c>
       <c r="F21" t="n">
-        <v>13989.4</v>
+        <v>14078.67</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -4948,10 +4948,10 @@
         <v>12633.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1356</v>
+        <v>1445.27</v>
       </c>
       <c r="J21" t="n">
-        <v>10.73</v>
+        <v>11.44</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>533.89</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7542</v>
+        <v>1.7311</v>
       </c>
       <c r="F22" t="n">
-        <v>936.549838</v>
+        <v>924.216979</v>
       </c>
       <c r="G22" t="n">
         <v>1.3657</v>
@@ -4989,10 +4989,10 @@
         <v>729.133573</v>
       </c>
       <c r="I22" t="n">
-        <v>207.4162650000001</v>
+        <v>195.0834060000001</v>
       </c>
       <c r="J22" t="n">
-        <v>28.45</v>
+        <v>26.76</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         <v>12921.74</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7542</v>
+        <v>1.7311</v>
       </c>
       <c r="F23" t="n">
-        <v>22667.316308</v>
+        <v>22368.824114</v>
       </c>
       <c r="G23" t="n">
         <v>1.4859</v>
@@ -5030,10 +5030,10 @@
         <v>19200.413466</v>
       </c>
       <c r="I23" t="n">
-        <v>3466.902841999996</v>
+        <v>3168.410647999997</v>
       </c>
       <c r="J23" t="n">
-        <v>18.06</v>
+        <v>16.5</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         <v>654.3200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5763</v>
+        <v>1.5561</v>
       </c>
       <c r="F24" t="n">
-        <v>1031.404616</v>
+        <v>1018.187352</v>
       </c>
       <c r="G24" t="n">
         <v>1.2226</v>
@@ -5071,10 +5071,10 @@
         <v>799.971632</v>
       </c>
       <c r="I24" t="n">
-        <v>231.432984</v>
+        <v>218.2157200000001</v>
       </c>
       <c r="J24" t="n">
-        <v>28.93</v>
+        <v>27.28</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         <v>415.34</v>
       </c>
       <c r="E26" t="n">
-        <v>6.2746</v>
+        <v>6.1871</v>
       </c>
       <c r="F26" t="n">
-        <v>2606.092364</v>
+        <v>2569.750114</v>
       </c>
       <c r="G26" t="n">
         <v>5.0561</v>
@@ -5153,10 +5153,10 @@
         <v>2100.000574</v>
       </c>
       <c r="I26" t="n">
-        <v>506.0917899999999</v>
+        <v>469.7495399999998</v>
       </c>
       <c r="J26" t="n">
-        <v>24.1</v>
+        <v>22.37</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>3858.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0366</v>
+        <v>2.0094</v>
       </c>
       <c r="F28" t="n">
-        <v>7858.83208</v>
+        <v>7753.872719999999</v>
       </c>
       <c r="G28" t="n">
         <v>1.6326</v>
@@ -5235,10 +5235,10 @@
         <v>6299.87688</v>
       </c>
       <c r="I28" t="n">
-        <v>1558.9552</v>
+        <v>1453.99584</v>
       </c>
       <c r="J28" t="n">
-        <v>24.75</v>
+        <v>23.08</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
         <v>8709.290000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0366</v>
+        <v>2.0094</v>
       </c>
       <c r="F29" t="n">
-        <v>17737.340014</v>
+        <v>17500.447326</v>
       </c>
       <c r="G29" t="n">
         <v>1.7223</v>
@@ -5276,10 +5276,10 @@
         <v>15000.010167</v>
       </c>
       <c r="I29" t="n">
-        <v>2737.329847000001</v>
+        <v>2500.437159000001</v>
       </c>
       <c r="J29" t="n">
-        <v>18.25</v>
+        <v>16.67</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>5258.09</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1255</v>
+        <v>2.0971</v>
       </c>
       <c r="F30" t="n">
-        <v>11176.070295</v>
+        <v>11026.740539</v>
       </c>
       <c r="G30" t="n">
         <v>1.6889</v>
@@ -5317,10 +5317,10 @@
         <v>8880.388201</v>
       </c>
       <c r="I30" t="n">
-        <v>2295.682094000002</v>
+        <v>2146.352338000002</v>
       </c>
       <c r="J30" t="n">
-        <v>25.85</v>
+        <v>24.17</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         <v>674.27</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1255</v>
+        <v>2.0971</v>
       </c>
       <c r="F31" t="n">
-        <v>1433.160885</v>
+        <v>1414.011617</v>
       </c>
       <c r="G31" t="n">
         <v>1.7797</v>
@@ -5358,10 +5358,10 @@
         <v>1199.998319</v>
       </c>
       <c r="I31" t="n">
-        <v>233.162566</v>
+        <v>214.0132980000001</v>
       </c>
       <c r="J31" t="n">
-        <v>19.43</v>
+        <v>17.83</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>6100</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4727</v>
+        <v>2.4365</v>
       </c>
       <c r="F33" t="n">
-        <v>15083.47</v>
+        <v>14862.65</v>
       </c>
       <c r="G33" t="n">
         <v>2.012</v>
@@ -5440,10 +5440,10 @@
         <v>12273.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2810.27</v>
+        <v>2589.450000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>22.9</v>
+        <v>21.1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>19100</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9943</v>
+        <v>1.9663</v>
       </c>
       <c r="F34" t="n">
-        <v>38091.13</v>
+        <v>37556.33</v>
       </c>
       <c r="G34" t="n">
         <v>1.632</v>
@@ -5481,10 +5481,10 @@
         <v>31171.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6919.929999999997</v>
+        <v>6385.130000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>22.2</v>
+        <v>20.48</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         <v>6086.38</v>
       </c>
       <c r="E35" t="n">
-        <v>6.8604</v>
+        <v>6.7998</v>
       </c>
       <c r="F35" t="n">
-        <v>41755.001352</v>
+        <v>41386.166724</v>
       </c>
       <c r="G35" t="n">
         <v>5.4548</v>
@@ -5522,10 +5522,10 @@
         <v>33199.985624</v>
       </c>
       <c r="I35" t="n">
-        <v>8555.015727999998</v>
+        <v>8186.181100000002</v>
       </c>
       <c r="J35" t="n">
-        <v>25.77</v>
+        <v>24.66</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         <v>2066.86</v>
       </c>
       <c r="E36" t="n">
-        <v>6.8604</v>
+        <v>6.7998</v>
       </c>
       <c r="F36" t="n">
-        <v>14179.486344</v>
+        <v>14054.234628</v>
       </c>
       <c r="G36" t="n">
         <v>5.4672</v>
@@ -5563,10 +5563,10 @@
         <v>11299.936992</v>
       </c>
       <c r="I36" t="n">
-        <v>2879.549352</v>
+        <v>2754.297636000001</v>
       </c>
       <c r="J36" t="n">
-        <v>25.48</v>
+        <v>24.37</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>15000</v>
       </c>
       <c r="E37" t="n">
-        <v>6.8604</v>
+        <v>6.7998</v>
       </c>
       <c r="F37" t="n">
-        <v>102906</v>
+        <v>101997</v>
       </c>
       <c r="G37" t="n">
         <v>5.553</v>
@@ -5604,10 +5604,10 @@
         <v>83295</v>
       </c>
       <c r="I37" t="n">
-        <v>19611</v>
+        <v>18702</v>
       </c>
       <c r="J37" t="n">
-        <v>23.54</v>
+        <v>22.45</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>7273.41</v>
       </c>
       <c r="E38" t="n">
-        <v>2.7998</v>
+        <v>2.7425</v>
       </c>
       <c r="F38" t="n">
-        <v>20364.093318</v>
+        <v>19947.326925</v>
       </c>
       <c r="G38" t="n">
         <v>2.1723</v>
@@ -5645,10 +5645,10 @@
         <v>15800.028543</v>
       </c>
       <c r="I38" t="n">
-        <v>4564.064774999999</v>
+        <v>4147.298382000001</v>
       </c>
       <c r="J38" t="n">
-        <v>28.89</v>
+        <v>26.25</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         <v>10427.91</v>
       </c>
       <c r="E39" t="n">
-        <v>2.7998</v>
+        <v>2.7425</v>
       </c>
       <c r="F39" t="n">
-        <v>29196.062418</v>
+        <v>28598.543175</v>
       </c>
       <c r="G39" t="n">
         <v>2.2056</v>
@@ -5686,10 +5686,10 @@
         <v>22999.798296</v>
       </c>
       <c r="I39" t="n">
-        <v>6196.264121999997</v>
+        <v>5598.744879000002</v>
       </c>
       <c r="J39" t="n">
-        <v>26.94</v>
+        <v>24.34</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5715,10 +5715,10 @@
         <v>6700</v>
       </c>
       <c r="E40" t="n">
-        <v>2.2779</v>
+        <v>2.2283</v>
       </c>
       <c r="F40" t="n">
-        <v>15261.93</v>
+        <v>14929.61</v>
       </c>
       <c r="G40" t="n">
         <v>1.56</v>
@@ -5727,10 +5727,10 @@
         <v>10452</v>
       </c>
       <c r="I40" t="n">
-        <v>4809.929999999998</v>
+        <v>4477.609999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>46.02</v>
+        <v>42.84</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         <v>1000</v>
       </c>
       <c r="E41" t="n">
-        <v>8.65</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>8650</v>
+        <v>8780</v>
       </c>
       <c r="G41" t="n">
         <v>7.109</v>
@@ -5768,10 +5768,10 @@
         <v>7109</v>
       </c>
       <c r="I41" t="n">
-        <v>1541</v>
+        <v>1671</v>
       </c>
       <c r="J41" t="n">
-        <v>21.68</v>
+        <v>23.51</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         <v>1100</v>
       </c>
       <c r="E42" t="n">
-        <v>7.48</v>
+        <v>7.5</v>
       </c>
       <c r="F42" t="n">
-        <v>8228</v>
+        <v>8250</v>
       </c>
       <c r="G42" t="n">
         <v>5.986</v>
@@ -5809,10 +5809,10 @@
         <v>6584.6</v>
       </c>
       <c r="I42" t="n">
-        <v>1643.4</v>
+        <v>1665.4</v>
       </c>
       <c r="J42" t="n">
-        <v>24.96</v>
+        <v>25.29</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5838,10 +5838,10 @@
         <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>42.5</v>
+        <v>43.29</v>
       </c>
       <c r="F43" t="n">
-        <v>63750</v>
+        <v>64935</v>
       </c>
       <c r="G43" t="n">
         <v>42.97</v>
@@ -5850,10 +5850,10 @@
         <v>64455</v>
       </c>
       <c r="I43" t="n">
-        <v>-705</v>
+        <v>480</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.09</v>
+        <v>0.74</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
